--- a/database_postprocessing.xlsx
+++ b/database_postprocessing.xlsx
@@ -1,41 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\TEMOA\PROJECT\Models-and-scenarios\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E864BC6-B499-4F54-BA4E-876E7184C784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Output_CapacityByPeriodAndTech" sheetId="1" r:id="rId1"/>
     <sheet name="Output_VFlow_Out" sheetId="2" r:id="rId2"/>
     <sheet name="Output_Emissions" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="37">
   <si>
     <t>file</t>
   </si>
@@ -58,10 +39,10 @@
     <t>ELC_BIO_CEN_E</t>
   </si>
   <si>
-    <t>ELC_BIO_DST_E</t>
+    <t>ELC_CHP_NGA_CC_N</t>
   </si>
   <si>
-    <t>ELC_CHP_NGA_CC_N</t>
+    <t>ELC_CHP_NGA_CC_P</t>
   </si>
   <si>
     <t>ELC_CHP_NGA_CP_N</t>
@@ -70,19 +51,16 @@
     <t>ELC_CHP_NGA_TAP_N</t>
   </si>
   <si>
+    <t>ELC_CHP_NGA_TURB_N</t>
+  </si>
+  <si>
     <t>ELC_COA_COND_E</t>
   </si>
   <si>
-    <t>ELC_COA_OIL_E</t>
+    <t>ELC_COA_STM_P</t>
   </si>
   <si>
     <t>ELC_DERGAS_CC_E</t>
-  </si>
-  <si>
-    <t>ELC_DST_TURB_E</t>
-  </si>
-  <si>
-    <t>ELC_GEO_E</t>
   </si>
   <si>
     <t>ELC_HYD_E</t>
@@ -94,6 +72,9 @@
     <t>ELC_NGA_CC_E</t>
   </si>
   <si>
+    <t>ELC_NGA_CC_N</t>
+  </si>
+  <si>
     <t>ELC_NGA_CT_N</t>
   </si>
   <si>
@@ -101,12 +82,6 @@
   </si>
   <si>
     <t>ELC_NGA_OIL_STM_E</t>
-  </si>
-  <si>
-    <t>ELC_NGA_STM_REP_E</t>
-  </si>
-  <si>
-    <t>ELC_NGA_TURB_E</t>
   </si>
   <si>
     <t>ELC_NUC_LWR_E</t>
@@ -128,6 +103,9 @@
   </si>
   <si>
     <t>ELC_WIN_P</t>
+  </si>
+  <si>
+    <t>STG_ELC_HYD_PUM_E</t>
   </si>
   <si>
     <t>output_comm</t>
@@ -154,8 +132,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,25 +192,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -270,7 +240,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -304,7 +274,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -339,10 +308,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -515,11 +483,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +546,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -589,19 +557,19 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>0.45965800967081361</v>
+        <v>0.4596580096708134</v>
       </c>
       <c r="E2">
         <v>0.5443859630190504</v>
       </c>
       <c r="F2">
-        <v>0.71384186971552466</v>
+        <v>0.7138418697155248</v>
       </c>
       <c r="G2">
-        <v>0.85975829481232147</v>
+        <v>0.8597582948123215</v>
       </c>
       <c r="H2">
-        <v>1.0056747199091181</v>
+        <v>1.005674719909118</v>
       </c>
       <c r="I2">
         <v>1.013544847793348</v>
@@ -610,34 +578,34 @@
         <v>1.021414975677577</v>
       </c>
       <c r="K2">
-        <v>1.2949550961943139</v>
+        <v>1.294955096194314</v>
       </c>
       <c r="L2">
-        <v>1.2949550961943139</v>
+        <v>1.294955096194314</v>
       </c>
       <c r="M2">
-        <v>1.2949550961943139</v>
+        <v>1.294955096194314</v>
       </c>
       <c r="N2">
-        <v>1.2949550961943139</v>
+        <v>1.294955096194314</v>
       </c>
       <c r="O2">
-        <v>1.3294134939576969</v>
+        <v>1.329413493957698</v>
       </c>
       <c r="P2">
-        <v>1.366341646567633</v>
+        <v>1.366341646567634</v>
       </c>
       <c r="Q2">
-        <v>1.40326979917757</v>
+        <v>1.403269799177569</v>
       </c>
       <c r="R2">
-        <v>1.061583812035787</v>
+        <v>3.014811269336009</v>
       </c>
       <c r="S2">
-        <v>0.48042285759599168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+        <v>6.680218180696697</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -648,55 +616,55 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="E3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="F3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="G3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="H3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="I3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="J3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="K3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="L3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="M3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="N3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="O3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="P3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="Q3">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="R3">
-        <v>8.1799999999999998E-2</v>
+        <v>0.0818</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -710,52 +678,52 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11.308034764159011</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>11.308034764159011</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>11.308034764159011</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H4">
-        <v>11.308034764159011</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="I4">
-        <v>11.308034764159011</v>
+        <v>0.4</v>
       </c>
       <c r="J4">
-        <v>11.308034764159011</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K4">
-        <v>11.308034764159011</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L4">
-        <v>11.308034764159011</v>
+        <v>0.8</v>
       </c>
       <c r="M4">
-        <v>11.308034764159011</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="N4">
-        <v>11.308034764159011</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>12.752311568241399</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>12.752311568241399</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>14.6648621494595</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>10.141648243795901</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>12.79559629320365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -775,46 +743,46 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.26666666666666672</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -834,25 +802,25 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H6">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="I6">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="J6">
-        <v>0.53333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K6">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L6">
         <v>0.8</v>
       </c>
       <c r="M6">
-        <v>0.93333333333333335</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -870,10 +838,10 @@
         <v>1</v>
       </c>
       <c r="S6">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -890,49 +858,49 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0.6218462491200849</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>3.481282314355306</v>
+        <v>1.753365862228919</v>
       </c>
       <c r="H7">
-        <v>4.211767156195612</v>
+        <v>2.617184037402559</v>
       </c>
       <c r="I7">
-        <v>4.211767156195612</v>
+        <v>2.617184037402559</v>
       </c>
       <c r="J7">
-        <v>4.5487638725697854</v>
+        <v>2.820847420443402</v>
       </c>
       <c r="K7">
-        <v>5.9686681680037923</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>12.98880895366009</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>22.678565192639631</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>22.678565192639631</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>27.36379081907236</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>29.354490187135571</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>33.994833634517533</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>31.511228777888249</v>
+        <v>4</v>
       </c>
       <c r="S7">
-        <v>25.762198769548149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -943,55 +911,55 @@
         <v>11</v>
       </c>
       <c r="D8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>11.212999999999999</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>11.212999999999999</v>
+        <v>3.930512207035269</v>
       </c>
       <c r="P8">
-        <v>11.212999999999999</v>
+        <v>3.930512207035269</v>
       </c>
       <c r="Q8">
-        <v>11.212999999999999</v>
+        <v>5.590352487959258</v>
       </c>
       <c r="R8">
-        <v>2.2425999999999999</v>
+        <v>5.590352487959258</v>
       </c>
       <c r="S8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+        <v>3.625096384441624</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1002,55 +970,55 @@
         <v>12</v>
       </c>
       <c r="D9">
-        <v>18.53465933585785</v>
+        <v>11.213</v>
       </c>
       <c r="E9">
-        <v>28.368211219222619</v>
+        <v>11.213</v>
       </c>
       <c r="F9">
-        <v>39.659891845557219</v>
+        <v>11.213</v>
       </c>
       <c r="G9">
-        <v>49.273849277357051</v>
+        <v>11.213</v>
       </c>
       <c r="H9">
-        <v>58.044338956296279</v>
+        <v>11.213</v>
       </c>
       <c r="I9">
-        <v>64.78676638980167</v>
+        <v>11.213</v>
       </c>
       <c r="J9">
-        <v>65.564179260992347</v>
+        <v>11.213</v>
       </c>
       <c r="K9">
-        <v>67.236391239745643</v>
+        <v>11.213</v>
       </c>
       <c r="L9">
-        <v>67.44240290372575</v>
+        <v>11.213</v>
       </c>
       <c r="M9">
-        <v>67.532426439753891</v>
+        <v>11.213</v>
       </c>
       <c r="N9">
-        <v>67.532426439753891</v>
+        <v>11.213</v>
       </c>
       <c r="O9">
-        <v>67.66913165656814</v>
+        <v>11.213</v>
       </c>
       <c r="P9">
-        <v>67.66913165656814</v>
+        <v>11.213</v>
       </c>
       <c r="Q9">
-        <v>67.66913165656814</v>
+        <v>11.213</v>
       </c>
       <c r="R9">
-        <v>52.614915301707534</v>
+        <v>2.2426</v>
       </c>
       <c r="S9">
-        <v>12.20332651056723</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1061,55 +1029,55 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>0.53100000000000003</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.53100000000000003</v>
+        <v>0.1069548716332221</v>
       </c>
       <c r="F10">
-        <v>0.53100000000000003</v>
+        <v>0.1069548716332221</v>
       </c>
       <c r="G10">
-        <v>0.53100000000000003</v>
+        <v>0.211332517443957</v>
       </c>
       <c r="H10">
-        <v>0.53100000000000003</v>
+        <v>0.211332517443957</v>
       </c>
       <c r="I10">
-        <v>0.53100000000000003</v>
+        <v>0.3132542186473804</v>
       </c>
       <c r="J10">
-        <v>0.53100000000000003</v>
+        <v>0.3132542186473804</v>
       </c>
       <c r="K10">
-        <v>0.53100000000000003</v>
+        <v>0.3132542186473804</v>
       </c>
       <c r="L10">
-        <v>0.53100000000000003</v>
+        <v>0.3132542186473804</v>
       </c>
       <c r="M10">
-        <v>0.53100000000000003</v>
+        <v>0.3132542186473804</v>
       </c>
       <c r="N10">
-        <v>0.53100000000000003</v>
+        <v>0.3132542186473804</v>
       </c>
       <c r="O10">
-        <v>0.53100000000000003</v>
+        <v>0.3132542186473804</v>
       </c>
       <c r="P10">
-        <v>0.53100000000000003</v>
+        <v>0.2704722699940916</v>
       </c>
       <c r="Q10">
-        <v>0.53100000000000003</v>
+        <v>0.1436727595277174</v>
       </c>
       <c r="R10">
-        <v>0.1062</v>
+        <v>0.02038434024068468</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1120,55 +1088,55 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="G11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="H11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="I11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="J11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="K11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="L11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="M11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="N11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="O11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="P11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="Q11">
-        <v>0.4201513825738199</v>
+        <v>0.531</v>
       </c>
       <c r="R11">
-        <v>0.4201513825738199</v>
+        <v>0.1062</v>
       </c>
       <c r="S11">
-        <v>8.4030276514763982E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1179,55 +1147,55 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>0.101470522583866</v>
+        <v>16.658</v>
       </c>
       <c r="E12">
-        <v>0.15945387714455761</v>
+        <v>16.658</v>
       </c>
       <c r="F12">
-        <v>0.21743723170524909</v>
+        <v>16.658</v>
       </c>
       <c r="G12">
-        <v>0.21743723170524909</v>
+        <v>16.658</v>
       </c>
       <c r="H12">
-        <v>0.21743723170524909</v>
+        <v>16.658</v>
       </c>
       <c r="I12">
-        <v>0.21743723170524909</v>
+        <v>16.658</v>
       </c>
       <c r="J12">
-        <v>0.29872875765221979</v>
+        <v>16.658</v>
       </c>
       <c r="K12">
-        <v>0.35671211221291133</v>
+        <v>16.658</v>
       </c>
       <c r="L12">
-        <v>1.3714173380515711</v>
+        <v>16.658</v>
       </c>
       <c r="M12">
-        <v>1.3714173380515711</v>
+        <v>17.85365199022801</v>
       </c>
       <c r="N12">
-        <v>1.4527088639985419</v>
+        <v>18.29287704943763</v>
       </c>
       <c r="O12">
-        <v>1.4527088639985419</v>
+        <v>28.63211863269722</v>
       </c>
       <c r="P12">
-        <v>3.4821193156758619</v>
+        <v>29.32344801801103</v>
       </c>
       <c r="Q12">
-        <v>6.5262349931918404</v>
+        <v>32.9155126590416</v>
       </c>
       <c r="R12">
-        <v>9.6938203756960757</v>
+        <v>28.36513413488287</v>
       </c>
       <c r="S12">
-        <v>13.60877679152456</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+        <v>25.03353413488287</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1238,55 +1206,55 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>16.658000000000001</v>
+        <v>1.809</v>
       </c>
       <c r="E13">
-        <v>16.658000000000001</v>
+        <v>1.809</v>
       </c>
       <c r="F13">
-        <v>21.39646176856078</v>
+        <v>1.809</v>
       </c>
       <c r="G13">
-        <v>21.39646176856078</v>
+        <v>1.809</v>
       </c>
       <c r="H13">
-        <v>21.39646176856078</v>
+        <v>1.809</v>
       </c>
       <c r="I13">
-        <v>21.39646176856078</v>
+        <v>1.809</v>
       </c>
       <c r="J13">
-        <v>21.39646176856078</v>
+        <v>1.809</v>
       </c>
       <c r="K13">
-        <v>21.39646176856078</v>
+        <v>1.809</v>
       </c>
       <c r="L13">
-        <v>21.39646176856078</v>
+        <v>1.809</v>
       </c>
       <c r="M13">
-        <v>21.39646176856078</v>
+        <v>4.851808751127283</v>
       </c>
       <c r="N13">
-        <v>21.39646176856078</v>
+        <v>4.851808751127283</v>
       </c>
       <c r="O13">
-        <v>31.719310473047891</v>
+        <v>9.002701575702346</v>
       </c>
       <c r="P13">
-        <v>31.719310473047891</v>
+        <v>9.002701575702346</v>
       </c>
       <c r="Q13">
-        <v>31.719310473047891</v>
+        <v>9.002701575702346</v>
       </c>
       <c r="R13">
-        <v>31.719310473047891</v>
+        <v>9.364501575702345</v>
       </c>
       <c r="S13">
-        <v>31.71931047304788</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+        <v>9.002701575702343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1297,55 +1265,55 @@
         <v>17</v>
       </c>
       <c r="D14">
-        <v>1.8089999999999999</v>
+        <v>16.41</v>
       </c>
       <c r="E14">
-        <v>3.621106764733705</v>
+        <v>16.41</v>
       </c>
       <c r="F14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="G14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="H14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="I14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="J14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="K14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="L14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="M14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="N14">
-        <v>4.5879339323391024</v>
+        <v>16.41</v>
       </c>
       <c r="O14">
-        <v>4.6098731220829601</v>
+        <v>16.41</v>
       </c>
       <c r="P14">
-        <v>4.6318123118268169</v>
+        <v>16.41</v>
       </c>
       <c r="Q14">
-        <v>4.6537515015706754</v>
+        <v>16.41</v>
       </c>
       <c r="R14">
-        <v>4.7892176828222732</v>
+        <v>3.282</v>
       </c>
       <c r="S14">
-        <v>4.6976298810583916</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1356,55 +1324,55 @@
         <v>18</v>
       </c>
       <c r="D15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>16.41</v>
+        <v>0.3036630581992403</v>
       </c>
       <c r="O15">
-        <v>16.41</v>
+        <v>0.3036630581992403</v>
       </c>
       <c r="P15">
-        <v>16.41</v>
+        <v>1.432984223327345</v>
       </c>
       <c r="Q15">
-        <v>16.41</v>
+        <v>3.937595259536566</v>
       </c>
       <c r="R15">
-        <v>3.282</v>
+        <v>3.937595259536566</v>
       </c>
       <c r="S15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>3.785763730436946</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1421,49 +1389,49 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.5440525151414858</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1.116208183155136</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1.116208183155136</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1.116208183155136</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1.116208183155136</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1.116208183155136</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>5.860517872611105</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>12.55839857353136</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>12.55839857353136</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>12.55839857353136</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>12.55839857353136</v>
       </c>
       <c r="Q16">
-        <v>0.10732734446224659</v>
+        <v>11.67105265758168</v>
       </c>
       <c r="R16">
-        <v>1.590348986653634</v>
+        <v>11.44219039037622</v>
       </c>
       <c r="S16">
-        <v>5.6986387776510092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+        <v>14.24484671678862</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1474,55 +1442,55 @@
         <v>20</v>
       </c>
       <c r="D17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="E17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="F17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="G17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="H17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="I17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="J17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="K17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="L17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="M17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="N17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="O17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="P17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="Q17">
-        <v>6.5469999999999997</v>
+        <v>6.547</v>
       </c>
       <c r="R17">
-        <v>1.3093999999999999</v>
+        <v>1.3094</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1533,46 +1501,46 @@
         <v>21</v>
       </c>
       <c r="D18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="E18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="F18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="G18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="H18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="I18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="J18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="K18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="L18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="M18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="N18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="O18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="P18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="Q18">
-        <v>8.3149999999999995</v>
+        <v>8.315</v>
       </c>
       <c r="R18">
         <v>1.663</v>
@@ -1581,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1592,55 +1560,55 @@
         <v>22</v>
       </c>
       <c r="D19">
-        <v>41.854747971036723</v>
+        <v>7.716</v>
       </c>
       <c r="E19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="F19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="G19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="H19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="I19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="J19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="K19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="L19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="M19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="N19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="O19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="P19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="Q19">
-        <v>79.339143575623183</v>
+        <v>7.716</v>
       </c>
       <c r="R19">
-        <v>39.232536551166561</v>
+        <v>4.718251751362141</v>
       </c>
       <c r="S19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+        <v>4.687413504621214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1651,55 +1619,55 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>110.1500176581452</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>110.1500176581452</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>110.1500176581452</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>110.1500176581452</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>110.1500176581452</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>110.1500176581452</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>44.060007063258112</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1710,55 +1678,55 @@
         <v>24</v>
       </c>
       <c r="D21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>7.7160000000000002</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>7.7160000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="N21">
-        <v>7.7160000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="O21">
-        <v>7.7160000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>7.7160000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
-        <v>7.7160000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
-        <v>1.5431999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1775,49 +1743,49 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.5893116498499628</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2.74071810375005</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>3.597888152805742</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>3.859070243059547</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>4.156702820767097</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>6.870498712883003</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>13.85636873643281</v>
       </c>
       <c r="M22">
-        <v>8</v>
+        <v>15.66285363773892</v>
       </c>
       <c r="N22">
-        <v>8</v>
+        <v>16.64406225393921</v>
       </c>
       <c r="O22">
-        <v>8</v>
+        <v>25.09535642343685</v>
       </c>
       <c r="P22">
-        <v>8</v>
+        <v>25.09069667550285</v>
       </c>
       <c r="Q22">
-        <v>8</v>
+        <v>26.26963219511951</v>
       </c>
       <c r="R22">
-        <v>8</v>
+        <v>29.10279617947654</v>
       </c>
       <c r="S22">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31.10884593146339</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1828,55 +1796,55 @@
         <v>26</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.306055879815012</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1.62754375958585</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>3.492717415705298</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="M23">
-        <v>3.2</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="N23">
-        <v>3.2</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="P23">
-        <v>3.2</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="Q23">
-        <v>3.2</v>
+        <v>3.49445508606137</v>
       </c>
       <c r="R23">
-        <v>3.2</v>
+        <v>2.754826406264027</v>
       </c>
       <c r="S23">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+        <v>0.0003475340712144501</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1887,55 +1855,55 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>11.279</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>11.279</v>
       </c>
       <c r="F24">
-        <v>0.60511903021346958</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="G24">
-        <v>2.740718103750051</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="H24">
-        <v>3.597888152805742</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="I24">
-        <v>3.8590702430595458</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="J24">
-        <v>4.1567028207670953</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="K24">
-        <v>6.8460893643835679</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="L24">
-        <v>13.807140150916879</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="M24">
-        <v>15.61634690954952</v>
+        <v>14.11596059487446</v>
       </c>
       <c r="N24">
-        <v>16.526961301760618</v>
+        <v>6.888564555229475</v>
       </c>
       <c r="O24">
-        <v>24.480159794463368</v>
+        <v>1.795803960355017</v>
       </c>
       <c r="P24">
-        <v>25.950292033343651</v>
+        <v>1.795803960355017</v>
       </c>
       <c r="Q24">
-        <v>27.215723762597499</v>
+        <v>1.795803960355017</v>
       </c>
       <c r="R24">
-        <v>28.247542089674681</v>
+        <v>1.795803960355017</v>
       </c>
       <c r="S24">
-        <v>31.108845931463389</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1.795803960355017</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1946,55 +1914,55 @@
         <v>28</v>
       </c>
       <c r="D25">
-        <v>0.30605587981501198</v>
+        <v>2.829733814529193</v>
       </c>
       <c r="E25">
-        <v>1.62754375958585</v>
+        <v>5.67972458305595</v>
       </c>
       <c r="F25">
-        <v>3.4927174157052958</v>
+        <v>11.20412699448115</v>
       </c>
       <c r="G25">
-        <v>3.494455086061369</v>
+        <v>11.20412699448115</v>
       </c>
       <c r="H25">
-        <v>3.494455086061369</v>
+        <v>12.50496248826331</v>
       </c>
       <c r="I25">
-        <v>3.494455086061369</v>
+        <v>12.50496248826331</v>
       </c>
       <c r="J25">
-        <v>3.494455086061369</v>
+        <v>12.50496248826331</v>
       </c>
       <c r="K25">
-        <v>3.494455086061369</v>
+        <v>14.77253911403659</v>
       </c>
       <c r="L25">
-        <v>3.494455086061369</v>
+        <v>18.50835331790292</v>
       </c>
       <c r="M25">
-        <v>3.494455086061369</v>
+        <v>19.24086456527085</v>
       </c>
       <c r="N25">
-        <v>3.494455086061369</v>
+        <v>29.63585000183791</v>
       </c>
       <c r="O25">
-        <v>3.494455086061369</v>
+        <v>47.78127829695371</v>
       </c>
       <c r="P25">
-        <v>3.494455086061369</v>
+        <v>58.43315855718257</v>
       </c>
       <c r="Q25">
-        <v>3.494455086061369</v>
+        <v>69.08503881741146</v>
       </c>
       <c r="R25">
-        <v>2.754826406264026</v>
+        <v>79.73691907764031</v>
       </c>
       <c r="S25">
-        <v>3.4753407121462381E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+        <v>90.38879933786922</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -2005,111 +1973,52 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>11.279</v>
+        <v>2.831092141278737</v>
       </c>
       <c r="E26">
-        <v>11.279</v>
+        <v>2.831092141278737</v>
       </c>
       <c r="F26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="G26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="H26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="I26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="J26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="K26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="L26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="M26">
-        <v>11.923196192646049</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="N26">
-        <v>4.6958001530010716</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="O26">
-        <v>1.795803960355018</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="P26">
-        <v>1.795803960355018</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="Q26">
-        <v>1.795803960355018</v>
+        <v>3.006961032555189</v>
       </c>
       <c r="R26">
-        <v>1.7958039603550171</v>
+        <v>8.305800546524347</v>
       </c>
       <c r="S26">
-        <v>1.7958039603550171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27">
-        <v>2.829733814529193</v>
-      </c>
-      <c r="E27">
-        <v>5.6797245830559504</v>
-      </c>
-      <c r="F27">
-        <v>10.73550992746341</v>
-      </c>
-      <c r="G27">
-        <v>13.396891396709551</v>
-      </c>
-      <c r="H27">
-        <v>14.69772689049171</v>
-      </c>
-      <c r="I27">
-        <v>14.69772689049171</v>
-      </c>
-      <c r="J27">
-        <v>14.69772689049171</v>
-      </c>
-      <c r="K27">
-        <v>16.965303516264999</v>
-      </c>
-      <c r="L27">
-        <v>23.199137663977378</v>
-      </c>
-      <c r="M27">
-        <v>23.199137663977378</v>
-      </c>
-      <c r="N27">
-        <v>32.316634835775019</v>
-      </c>
-      <c r="O27">
-        <v>47.781278296953708</v>
-      </c>
-      <c r="P27">
-        <v>58.433158557182587</v>
-      </c>
-      <c r="Q27">
-        <v>69.085038817411473</v>
-      </c>
-      <c r="R27">
-        <v>79.736919077640323</v>
-      </c>
-      <c r="S27">
-        <v>90.388799337869216</v>
+        <v>10.69643341259609</v>
       </c>
     </row>
   </sheetData>
@@ -2118,11 +2027,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2133,37 +2042,58 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1">
         <v>2007</v>
       </c>
       <c r="F1" s="1">
+        <v>2008</v>
+      </c>
+      <c r="G1" s="1">
         <v>2010</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
+        <v>2012</v>
+      </c>
+      <c r="I1" s="1">
         <v>2014</v>
       </c>
-      <c r="H1" s="1">
+      <c r="J1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="K1" s="1">
         <v>2018</v>
       </c>
-      <c r="I1" s="1">
+      <c r="L1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="M1" s="1">
         <v>2022</v>
       </c>
-      <c r="J1" s="1">
+      <c r="N1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="O1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="P1" s="1">
         <v>2030</v>
       </c>
-      <c r="L1" s="1">
+      <c r="Q1" s="1">
+        <v>2035</v>
+      </c>
+      <c r="R1" s="1">
         <v>2040</v>
       </c>
-      <c r="M1" s="1">
+      <c r="S1" s="1">
+        <v>2045</v>
+      </c>
+      <c r="T1" s="1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2174,37 +2104,58 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>7.3906199999999993</v>
+        <v>7.390620000000002</v>
       </c>
       <c r="F2">
-        <v>11.47751999999999</v>
+        <v>8.75292</v>
       </c>
       <c r="G2">
+        <v>11.47752</v>
+      </c>
+      <c r="H2">
+        <v>13.82364</v>
+      </c>
+      <c r="I2">
         <v>16.16976</v>
       </c>
-      <c r="H2">
-        <v>16.42283999999999</v>
-      </c>
-      <c r="I2">
-        <v>19.505970000000008</v>
-      </c>
       <c r="J2">
+        <v>16.2963</v>
+      </c>
+      <c r="K2">
+        <v>16.42284</v>
+      </c>
+      <c r="L2">
+        <v>20.82096</v>
+      </c>
+      <c r="M2">
+        <v>19.50597000000001</v>
+      </c>
+      <c r="N2">
         <v>18.19098</v>
       </c>
-      <c r="K2">
-        <v>21.374999999999989</v>
-      </c>
-      <c r="L2">
-        <v>22.562499999999989</v>
-      </c>
-      <c r="M2">
-        <v>5.7933717951093033</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O2">
+        <v>18.72165</v>
+      </c>
+      <c r="P2">
+        <v>21.375</v>
+      </c>
+      <c r="Q2">
+        <v>21.96875</v>
+      </c>
+      <c r="R2">
+        <v>22.5625</v>
+      </c>
+      <c r="S2">
+        <v>48.4737</v>
+      </c>
+      <c r="T2">
+        <v>55.00000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2227,25 +2178,46 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.369633204224</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2.739266408448001</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>4.108899612672001</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>5.478532816896005</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>6.252481255680002</v>
       </c>
       <c r="M3">
-        <v>49.206628204890713</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>7.502977506816003</v>
+      </c>
+      <c r="N3">
+        <v>8.753473757951998</v>
+      </c>
+      <c r="O3">
+        <v>9.378721883520003</v>
+      </c>
+      <c r="P3">
+        <v>5.804624013120001</v>
+      </c>
+      <c r="Q3">
+        <v>5.804624013120002</v>
+      </c>
+      <c r="R3">
+        <v>6.4181787496704</v>
+      </c>
+      <c r="S3">
+        <v>6.013112966207999</v>
+      </c>
+      <c r="T3">
+        <v>6.132994114233601</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2256,7 +2228,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -2265,28 +2237,49 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>2.7392664084480001</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>4.1088996126720003</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>3.9301941830400011</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.5727833237760018</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>8.9319583094400006</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>9.8254854576000028</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>6.5082742297919998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30.61675114629714</v>
+      </c>
+      <c r="Q4">
+        <v>32.15299048704</v>
+      </c>
+      <c r="R4">
+        <v>32.15299048703999</v>
+      </c>
+      <c r="S4">
+        <v>28.38893014285351</v>
+      </c>
+      <c r="T4">
+        <v>17.73214281216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2297,7 +2290,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2309,25 +2302,46 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>11.923865542655999</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>16.332731711133619</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>16.092006761079251</v>
+        <v>5.961932771327999</v>
       </c>
       <c r="K5">
-        <v>18.532732622619921</v>
+        <v>11.923865542656</v>
       </c>
       <c r="L5">
-        <v>18.138458556928249</v>
+        <v>13.13170517947336</v>
       </c>
       <c r="M5">
-        <v>7.1341377993215982</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>16.14149032265469</v>
+      </c>
+      <c r="N5">
+        <v>14.967744398208</v>
+      </c>
+      <c r="O5">
+        <v>16.03686899808</v>
+      </c>
+      <c r="P5">
+        <v>12.63359344032</v>
+      </c>
+      <c r="Q5">
+        <v>12.63359344032</v>
+      </c>
+      <c r="R5">
+        <v>12.63359344032</v>
+      </c>
+      <c r="S5">
+        <v>12.81510147006719</v>
+      </c>
+      <c r="T5">
+        <v>12.58002944752533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2352,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2350,25 +2364,46 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>61.425515860127703</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>174.0375236699584</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>176.39679574659201</v>
+        <v>47.90438439773663</v>
       </c>
       <c r="K6">
-        <v>240.4566559356511</v>
+        <v>50.35442498985721</v>
       </c>
       <c r="L6">
-        <v>323.21809405585572</v>
+        <v>64.93191253293078</v>
       </c>
       <c r="M6">
-        <v>281.14070738208392</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>75.67086408829832</v>
+      </c>
+      <c r="N6">
+        <v>56.08996444614699</v>
+      </c>
+      <c r="O6">
+        <v>54.78578003370982</v>
+      </c>
+      <c r="P6">
+        <v>46.87824273904454</v>
+      </c>
+      <c r="Q6">
+        <v>48.25280599414748</v>
+      </c>
+      <c r="R6">
+        <v>49.09085259148937</v>
+      </c>
+      <c r="S6">
+        <v>50.04207116921336</v>
+      </c>
+      <c r="T6">
+        <v>45.75341938467835</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2379,7 +2414,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2408,8 +2443,29 @@
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>38.24892046548935</v>
+      </c>
+      <c r="Q7">
+        <v>38.24892046548935</v>
+      </c>
+      <c r="R7">
+        <v>55.64449049335579</v>
+      </c>
+      <c r="S7">
+        <v>54.40129337425194</v>
+      </c>
+      <c r="T7">
+        <v>38.87684204236925</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2420,37 +2476,58 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>253.37450000000001</v>
+        <v>266.71</v>
       </c>
       <c r="F8">
-        <v>90.021999999999991</v>
+        <v>205.4390000000002</v>
       </c>
       <c r="G8">
-        <v>159.79</v>
+        <v>92.19383091045343</v>
       </c>
       <c r="H8">
-        <v>132.37299999999999</v>
+        <v>186.7415</v>
       </c>
       <c r="I8">
-        <v>29.73500000000001</v>
+        <v>155.0400000000001</v>
       </c>
       <c r="J8">
-        <v>11.856</v>
+        <v>120.9635000000001</v>
       </c>
       <c r="K8">
-        <v>1.9</v>
+        <v>125.2480000000001</v>
       </c>
       <c r="L8">
-        <v>0.95000000000000007</v>
+        <v>13.908</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>22.60999999999999</v>
+      </c>
+      <c r="N8">
+        <v>4.731000000000005</v>
+      </c>
+      <c r="O8">
+        <v>3.071666666666669</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2461,37 +2538,58 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.6</v>
+        <v>2.375</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="I9">
-        <v>0.29749999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="J9">
-        <v>0.27625</v>
+        <v>7.124999999999998</v>
       </c>
       <c r="K9">
-        <v>0.21249999999999999</v>
+        <v>7.125000000000001</v>
       </c>
       <c r="L9">
-        <v>0.10625</v>
+        <v>7.125</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>7.125</v>
+      </c>
+      <c r="N9">
+        <v>7.124999999999999</v>
+      </c>
+      <c r="O9">
+        <v>7.125000000000002</v>
+      </c>
+      <c r="P9">
+        <v>1.9</v>
+      </c>
+      <c r="Q9">
+        <v>1.425</v>
+      </c>
+      <c r="R9">
+        <v>0.95</v>
+      </c>
+      <c r="S9">
+        <v>0.4749999999999999</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2502,7 +2600,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -2511,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2529,10 +2627,31 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0.52999999999999992</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.2975</v>
+      </c>
+      <c r="N10">
+        <v>0.27625</v>
+      </c>
+      <c r="O10">
+        <v>0.2656250000000001</v>
+      </c>
+      <c r="P10">
+        <v>0.2125</v>
+      </c>
+      <c r="Q10">
+        <v>0.159375</v>
+      </c>
+      <c r="R10">
+        <v>0.10625</v>
+      </c>
+      <c r="S10">
+        <v>0.05312499999999998</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2543,37 +2662,58 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>64.11580297597997</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>105.0338090681663</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>105.0338090681663</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>75.58049412564222</v>
       </c>
       <c r="I11">
-        <v>0.1</v>
+        <v>105.0338090681663</v>
       </c>
       <c r="J11">
-        <v>0.1</v>
+        <v>105.0338090681663</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>105.0338090681663</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>105.0338090681663</v>
       </c>
       <c r="M11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>76.11761908726662</v>
+      </c>
+      <c r="N11">
+        <v>112.5727622950592</v>
+      </c>
+      <c r="O11">
+        <v>115.3422112689443</v>
+      </c>
+      <c r="P11">
+        <v>180.5343067405335</v>
+      </c>
+      <c r="Q11">
+        <v>184.8933509631451</v>
+      </c>
+      <c r="R11">
+        <v>197.9987056287091</v>
+      </c>
+      <c r="S11">
+        <v>175.4181222285096</v>
+      </c>
+      <c r="T11">
+        <v>152.1962495517131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2584,37 +2724,58 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>104.21285483422299</v>
+        <v>1.13617297926288</v>
       </c>
       <c r="F12">
-        <v>134.91126666666659</v>
+        <v>9.077082375110667</v>
       </c>
       <c r="G12">
-        <v>132.79641078009391</v>
+        <v>11.40630091273339</v>
       </c>
       <c r="H12">
-        <v>117.045387491673</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>64.263559361638556</v>
+        <v>11.40630091273339</v>
       </c>
       <c r="J12">
-        <v>132.75049333333331</v>
+        <v>11.34297764113917</v>
       </c>
       <c r="K12">
-        <v>200</v>
+        <v>11.40630091273339</v>
       </c>
       <c r="L12">
-        <v>200</v>
+        <v>11.40630091273339</v>
       </c>
       <c r="M12">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>11.40630091273339</v>
+      </c>
+      <c r="N12">
+        <v>30.59214515555058</v>
+      </c>
+      <c r="O12">
+        <v>30.59214515555058</v>
+      </c>
+      <c r="P12">
+        <v>56.7648</v>
+      </c>
+      <c r="Q12">
+        <v>56.7648</v>
+      </c>
+      <c r="R12">
+        <v>52.84281303497725</v>
+      </c>
+      <c r="S12">
+        <v>56.76479999999999</v>
+      </c>
+      <c r="T12">
+        <v>56.76479999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2628,34 +2789,55 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>5.6663451657770407</v>
+        <v>341.2764000000001</v>
       </c>
       <c r="F13">
-        <v>28.928333333333331</v>
+        <v>335.6477400000001</v>
       </c>
       <c r="G13">
-        <v>21.89198921990598</v>
+        <v>341.4636</v>
       </c>
       <c r="H13">
-        <v>15.908012508326969</v>
+        <v>249.3437267957759</v>
       </c>
       <c r="I13">
-        <v>23.26036063836148</v>
+        <v>176.8038935915518</v>
       </c>
       <c r="J13">
-        <v>28.900666666666659</v>
+        <v>161.0313232182629</v>
       </c>
       <c r="K13">
-        <v>29.06666666666667</v>
+        <v>130.6168566505904</v>
       </c>
       <c r="L13">
-        <v>29.34333333333333</v>
+        <v>154.1912810319155</v>
       </c>
       <c r="M13">
-        <v>29.61999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>194.7191680822315</v>
+      </c>
+      <c r="N13">
+        <v>102.3283609070353</v>
+      </c>
+      <c r="O13">
+        <v>112.3929115593683</v>
+      </c>
+      <c r="P13">
+        <v>81.36429036524567</v>
+      </c>
+      <c r="Q13">
+        <v>74.46313246134164</v>
+      </c>
+      <c r="R13">
+        <v>27.2</v>
+      </c>
+      <c r="S13">
+        <v>13.6</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2666,37 +2848,58 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14">
-        <v>218.50257999999999</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>250.01994274631099</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>176.80389359155171</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>120.9153989845439</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>129.56650465728569</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>11.906861628833861</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>4.6658379163785</v>
+      </c>
+      <c r="P14">
+        <v>3.769322158815291</v>
+      </c>
+      <c r="Q14">
+        <v>19.16146839225491</v>
+      </c>
+      <c r="R14">
+        <v>51.21648352964752</v>
+      </c>
+      <c r="S14">
+        <v>28.2993218257263</v>
+      </c>
+      <c r="T14">
+        <v>2.536203071047548</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2704,368 +2907,557 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>3.997562939903913</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>66.695244215085</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="D15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>2.5</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
         <v>21</v>
       </c>
-      <c r="D16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16">
-        <v>63.297359999999983</v>
-      </c>
-      <c r="F16">
-        <v>56.642039999999987</v>
-      </c>
-      <c r="G16">
-        <v>48.293819999999997</v>
-      </c>
-      <c r="H16">
-        <v>49.583160000000007</v>
-      </c>
-      <c r="I16">
-        <v>36.217799999999997</v>
-      </c>
-      <c r="J16">
-        <v>30.513999999999999</v>
-      </c>
-      <c r="K16">
-        <v>9.5</v>
-      </c>
-      <c r="L16">
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>66.6288</v>
+      </c>
+      <c r="F17">
+        <v>63.29987999999999</v>
+      </c>
+      <c r="G17">
+        <v>65.58552</v>
+      </c>
+      <c r="H17">
+        <v>52.39781999999999</v>
+      </c>
+      <c r="I17">
+        <v>48.29382</v>
+      </c>
+      <c r="J17">
+        <v>53.91972</v>
+      </c>
+      <c r="K17">
+        <v>49.58316</v>
+      </c>
+      <c r="L17">
+        <v>36.60768</v>
+      </c>
+      <c r="M17">
+        <v>36.2178</v>
+      </c>
+      <c r="N17">
+        <v>30.51399999999999</v>
+      </c>
+      <c r="O17">
+        <v>27.01166666666666</v>
+      </c>
+      <c r="P17">
+        <v>9.500000000000002</v>
+      </c>
+      <c r="Q17">
+        <v>7.125</v>
+      </c>
+      <c r="R17">
         <v>4.75</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="S17">
+        <v>47.1857240207088</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
         <v>22</v>
       </c>
-      <c r="D17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17">
-        <v>100.29</v>
-      </c>
-      <c r="F17">
-        <v>94.835454545454553</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18">
+        <v>198.37</v>
+      </c>
+      <c r="F18">
+        <v>202.914</v>
+      </c>
+      <c r="G18">
+        <v>218.9326798218816</v>
+      </c>
+      <c r="H18">
+        <v>210.2255</v>
+      </c>
+      <c r="I18">
+        <v>211.76298686065</v>
+      </c>
+      <c r="J18">
+        <v>200.526</v>
+      </c>
+      <c r="K18">
+        <v>196.4373620758995</v>
+      </c>
+      <c r="L18">
+        <v>203.0194694319493</v>
+      </c>
+      <c r="M18">
+        <v>218.9326798218816</v>
+      </c>
+      <c r="N18">
+        <v>215.9410000000001</v>
+      </c>
+      <c r="O18">
+        <v>202.7008333333333</v>
+      </c>
+      <c r="P18">
+        <v>136.5</v>
+      </c>
+      <c r="Q18">
+        <v>135.625</v>
+      </c>
+      <c r="R18">
+        <v>134.75</v>
+      </c>
+      <c r="S18">
+        <v>133.875</v>
+      </c>
+      <c r="T18">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
         <v>23</v>
       </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18">
-        <v>5.42</v>
-      </c>
-      <c r="F18">
-        <v>5.86</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>49.62889573056001</v>
+      </c>
+      <c r="O19">
+        <v>49.62889573056001</v>
+      </c>
+      <c r="P19">
+        <v>49.0845568381816</v>
+      </c>
+      <c r="Q19">
+        <v>49.62889573056</v>
+      </c>
+      <c r="R19">
+        <v>46.3476520218646</v>
+      </c>
+      <c r="S19">
+        <v>47.41706729872284</v>
+      </c>
+      <c r="T19">
+        <v>49.62889573056001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
         <v>24</v>
       </c>
-      <c r="D19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19">
-        <v>217.0010537154852</v>
-      </c>
-      <c r="F19">
-        <v>218.93267982188161</v>
-      </c>
-      <c r="G19">
-        <v>200.18459503119641</v>
-      </c>
-      <c r="H19">
-        <v>218.93267982188161</v>
-      </c>
-      <c r="I19">
-        <v>218.93267982188161</v>
-      </c>
-      <c r="J19">
-        <v>215.941</v>
-      </c>
-      <c r="K19">
-        <v>136.5</v>
-      </c>
-      <c r="L19">
-        <v>68.25</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>16.203395098368</v>
+      </c>
+      <c r="O20">
+        <v>13.58200280945739</v>
+      </c>
+      <c r="P20">
+        <v>12.16022991299431</v>
+      </c>
+      <c r="Q20">
+        <v>12.13366270594449</v>
+      </c>
+      <c r="R20">
+        <v>13.48791353468928</v>
+      </c>
+      <c r="S20">
+        <v>13.11200140741632</v>
+      </c>
+      <c r="T20">
+        <v>13.11200140741632</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
         <v>25</v>
       </c>
-      <c r="D20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>49.481560908852892</v>
-      </c>
-      <c r="K20">
-        <v>49.628895730560011</v>
-      </c>
-      <c r="L20">
-        <v>48.19925229350401</v>
-      </c>
-      <c r="M20">
-        <v>43.910321982336008</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>4.476119999999995</v>
+      </c>
+      <c r="H21">
+        <v>20.81714</v>
+      </c>
+      <c r="I21">
+        <v>27.32778</v>
+      </c>
+      <c r="J21">
+        <v>29.16774</v>
+      </c>
+      <c r="K21">
+        <v>31.57226000000001</v>
+      </c>
+      <c r="L21">
+        <v>50.64114</v>
+      </c>
+      <c r="M21">
+        <v>102.1326599999999</v>
+      </c>
+      <c r="N21">
+        <v>113.492669171072</v>
+      </c>
+      <c r="O21">
+        <v>122.483234793316</v>
+      </c>
+      <c r="P21">
+        <v>176.2552132488241</v>
+      </c>
+      <c r="Q21">
+        <v>180.1124415634955</v>
+      </c>
+      <c r="R21">
+        <v>196.4144344434462</v>
+      </c>
+      <c r="S21">
+        <v>210.0959312938609</v>
+      </c>
+      <c r="T21">
+        <v>222.2591028620236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
         <v>26</v>
       </c>
-      <c r="D21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>15.112139945502481</v>
-      </c>
-      <c r="K21">
-        <v>13.606246993833469</v>
-      </c>
-      <c r="L21">
-        <v>15.736658564505611</v>
-      </c>
-      <c r="M21">
-        <v>14.97894754286593</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>1.7613</v>
+      </c>
+      <c r="F22">
+        <v>9.366239999999998</v>
+      </c>
+      <c r="G22">
+        <v>20.09999999999999</v>
+      </c>
+      <c r="H22">
+        <v>20.11000000000001</v>
+      </c>
+      <c r="I22">
+        <v>20.07</v>
+      </c>
+      <c r="J22">
+        <v>20.07</v>
+      </c>
+      <c r="K22">
+        <v>20.07999999999999</v>
+      </c>
+      <c r="L22">
+        <v>20.03999999999999</v>
+      </c>
+      <c r="M22">
+        <v>20.03999999999999</v>
+      </c>
+      <c r="N22">
+        <v>20.02</v>
+      </c>
+      <c r="O22">
+        <v>20.01</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>7.499999999999999</v>
+      </c>
+      <c r="R22">
+        <v>5</v>
+      </c>
+      <c r="S22">
+        <v>2.5</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
         <v>27</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>4.4761199999999937</v>
-      </c>
-      <c r="G22">
-        <v>27.327780000000001</v>
-      </c>
-      <c r="H22">
-        <v>31.57226</v>
-      </c>
-      <c r="I22">
-        <v>102.13266</v>
-      </c>
-      <c r="J22">
-        <v>114.7312591456447</v>
-      </c>
-      <c r="K22">
-        <v>174.2648572756066</v>
-      </c>
-      <c r="L22">
-        <v>201.4853547067687</v>
-      </c>
-      <c r="M22">
-        <v>226.1107304747982</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
       </c>
       <c r="E23">
-        <v>1.7613000000000001</v>
+        <v>75.36902857327627</v>
       </c>
       <c r="F23">
-        <v>20.099999999999991</v>
+        <v>75.36902857327627</v>
       </c>
       <c r="G23">
-        <v>20.07</v>
+        <v>94.32629110863863</v>
       </c>
       <c r="H23">
-        <v>20.079999999999991</v>
+        <v>94.32629110863859</v>
       </c>
       <c r="I23">
-        <v>20.04</v>
+        <v>94.32629110863863</v>
       </c>
       <c r="J23">
-        <v>20.019999999999989</v>
+        <v>93.5333948754249</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>94.09145757952476</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>94.32629110863861</v>
       </c>
       <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <v>94.3262911086386</v>
+      </c>
+      <c r="N23">
+        <v>94.32629110863864</v>
+      </c>
+      <c r="O23">
+        <v>46.03106825001759</v>
+      </c>
+      <c r="P23">
+        <v>12</v>
+      </c>
+      <c r="Q23">
+        <v>12</v>
+      </c>
+      <c r="R23">
+        <v>12</v>
+      </c>
+      <c r="S23">
+        <v>12</v>
+      </c>
+      <c r="T23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3073,78 +3465,120 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24">
+        <v>18.90897142672372</v>
+      </c>
+      <c r="F24">
+        <v>37.95330476005707</v>
+      </c>
+      <c r="G24">
+        <v>74.86870889136141</v>
+      </c>
+      <c r="H24">
+        <v>74.86870889136144</v>
+      </c>
+      <c r="I24">
+        <v>83.56120889136145</v>
+      </c>
+      <c r="J24">
+        <v>73.72360512457513</v>
+      </c>
+      <c r="K24">
+        <v>79.97704242047527</v>
+      </c>
+      <c r="L24">
+        <v>98.71370889136146</v>
+      </c>
+      <c r="M24">
+        <v>123.6773304425319</v>
+      </c>
+      <c r="N24">
+        <v>128.5721492325948</v>
+      </c>
+      <c r="O24">
+        <v>198.0339769112379</v>
+      </c>
+      <c r="P24">
+        <v>319.286153846154</v>
+      </c>
+      <c r="Q24">
+        <v>390.4646153846155</v>
+      </c>
+      <c r="R24">
+        <v>461.643076923077</v>
+      </c>
+      <c r="S24">
+        <v>532.8215384615384</v>
+      </c>
+      <c r="T24">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24">
-        <v>75.369028573276282</v>
-      </c>
-      <c r="F24">
-        <v>79.673704630580659</v>
-      </c>
-      <c r="G24">
-        <v>79.673704630580673</v>
-      </c>
-      <c r="H24">
-        <v>78.814124698542045</v>
-      </c>
-      <c r="I24">
-        <v>79.673704630580659</v>
-      </c>
-      <c r="J24">
-        <v>79.673704630580659</v>
-      </c>
-      <c r="K24">
-        <v>12</v>
-      </c>
-      <c r="L24">
-        <v>12</v>
-      </c>
-      <c r="M24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>30</v>
-      </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25">
-        <v>18.908971426723721</v>
+        <v>44.62722404475713</v>
       </c>
       <c r="F25">
-        <v>71.737295369419343</v>
+        <v>13.75510855672302</v>
       </c>
       <c r="G25">
-        <v>98.213795369419358</v>
+        <v>47.39949001910026</v>
       </c>
       <c r="H25">
-        <v>95.974346214484584</v>
+        <v>11.40270587435776</v>
       </c>
       <c r="I25">
-        <v>155.02229536941931</v>
+        <v>38.24829001910029</v>
       </c>
       <c r="J25">
-        <v>155.02229536941931</v>
+        <v>27.13721329069454</v>
       </c>
       <c r="K25">
-        <v>319.28615384615392</v>
+        <v>16.51329001910029</v>
       </c>
       <c r="L25">
-        <v>461.64307692307727</v>
+        <v>5.952690019100295</v>
       </c>
       <c r="M25">
-        <v>603.99999999999989</v>
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>3.79069254939018</v>
+      </c>
+      <c r="O25">
+        <v>1.528643575505119</v>
+      </c>
+      <c r="P25">
+        <v>4.70089325946654</v>
+      </c>
+      <c r="Q25">
+        <v>14.09184903685494</v>
+      </c>
+      <c r="R25">
+        <v>18.65848133631355</v>
+      </c>
+      <c r="S25">
+        <v>51.06707777149017</v>
+      </c>
+      <c r="T25">
+        <v>88.03895044828677</v>
       </c>
     </row>
   </sheetData>
@@ -3153,11 +3587,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:T38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3168,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1">
         <v>2007</v>
@@ -3219,7 +3653,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3230,16 +3664,16 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>6158.8500000000022</v>
+        <v>6158.85</v>
       </c>
       <c r="F2">
-        <v>7294.1</v>
+        <v>7294.099999999999</v>
       </c>
       <c r="G2">
-        <v>9564.5999999999949</v>
+        <v>9564.599999999999</v>
       </c>
       <c r="H2">
         <v>11519.7</v>
@@ -3251,37 +3685,37 @@
         <v>13580.25</v>
       </c>
       <c r="K2">
-        <v>13685.69999999999</v>
+        <v>13685.7</v>
       </c>
       <c r="L2">
         <v>17350.8</v>
       </c>
       <c r="M2">
-        <v>16254.975000000009</v>
+        <v>16254.97500000001</v>
       </c>
       <c r="N2">
-        <v>15159.150000000011</v>
+        <v>15159.15</v>
       </c>
       <c r="O2">
-        <v>15601.375</v>
+        <v>15601.37500000001</v>
       </c>
       <c r="P2">
-        <v>17812.500000000011</v>
+        <v>17812.5</v>
       </c>
       <c r="Q2">
-        <v>18307.291666666679</v>
+        <v>18307.29166666668</v>
       </c>
       <c r="R2">
-        <v>18802.08333333335</v>
+        <v>18802.08333333334</v>
       </c>
       <c r="S2">
-        <v>10667.94529297384</v>
+        <v>40394.75000000003</v>
       </c>
       <c r="T2">
-        <v>4827.8098292577524</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+        <v>45833.33333333335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3292,58 +3726,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>82.117999999999995</v>
+        <v>82.11799999999999</v>
       </c>
       <c r="F3">
-        <v>97.254666666666637</v>
+        <v>97.25466666666665</v>
       </c>
       <c r="G3">
-        <v>127.52799999999991</v>
+        <v>127.528</v>
       </c>
       <c r="H3">
-        <v>153.59599999999989</v>
+        <v>153.5959999999999</v>
       </c>
       <c r="I3">
-        <v>179.66399999999999</v>
+        <v>179.6639999999999</v>
       </c>
       <c r="J3">
-        <v>181.06999999999991</v>
+        <v>181.0699999999999</v>
       </c>
       <c r="K3">
-        <v>182.47599999999991</v>
+        <v>182.4759999999999</v>
       </c>
       <c r="L3">
-        <v>231.34399999999999</v>
+        <v>231.344</v>
       </c>
       <c r="M3">
-        <v>216.73300000000009</v>
+        <v>216.7330000000001</v>
       </c>
       <c r="N3">
-        <v>202.1220000000001</v>
+        <v>202.122</v>
       </c>
       <c r="O3">
         <v>208.0183333333334</v>
       </c>
       <c r="P3">
-        <v>237.50000000000011</v>
+        <v>237.4999999999999</v>
       </c>
       <c r="Q3">
-        <v>244.0972222222224</v>
+        <v>244.0972222222223</v>
       </c>
       <c r="R3">
         <v>250.6944444444446</v>
       </c>
       <c r="S3">
-        <v>142.23927057298459</v>
+        <v>538.5966666666669</v>
       </c>
       <c r="T3">
-        <v>64.370797723436652</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>611.1111111111112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3354,7 +3788,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3366,46 +3800,46 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.1978359072768</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.3956718145536</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.5935077218304001</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.7913436291072001</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>0.9031361813760002</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.0837634176512</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.2643906539264</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.354704272064</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.8384456907840002</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>0.8384456907840002</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.9270702638412802</v>
       </c>
       <c r="S4">
-        <v>4116.0191132805448</v>
+        <v>0.8685607617856002</v>
       </c>
       <c r="T4">
-        <v>5677.6878697950806</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0.88587692761152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3428,46 +3862,46 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>85.37380306329601</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>170.747606126592</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>256.121409189888</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>341.495212253184</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>389.73799827072</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>467.6855979248641</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>545.6331975790081</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>584.6069974060802</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>361.82156348448</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>361.8215634844801</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>400.0664753961216</v>
       </c>
       <c r="S5">
-        <v>548.8025484374059</v>
+        <v>374.8173748936321</v>
       </c>
       <c r="T5">
-        <v>757.02504930601083</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>382.2899664538944</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3475,7 +3909,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
@@ -3490,46 +3924,46 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.1978359072768</v>
+        <v>0.8217799225344001</v>
       </c>
       <c r="I6">
-        <v>0.39567181455360001</v>
+        <v>1.6435598450688</v>
       </c>
       <c r="J6">
-        <v>0.59350772183040013</v>
+        <v>2.465339767603201</v>
       </c>
       <c r="K6">
-        <v>0.59350772183040013</v>
+        <v>3.287119690137601</v>
       </c>
       <c r="L6">
-        <v>0.55487569039022078</v>
+        <v>3.751488753408001</v>
       </c>
       <c r="M6">
-        <v>0.56769471532800009</v>
+        <v>4.5017865040896</v>
       </c>
       <c r="N6">
-        <v>0.51606870232320012</v>
+        <v>5.252084254771201</v>
       </c>
       <c r="O6">
-        <v>1.3547042720639999</v>
+        <v>5.627233130112</v>
       </c>
       <c r="P6">
-        <v>1.2901717558079999</v>
+        <v>3.482774407872</v>
       </c>
       <c r="Q6">
-        <v>1.3547042720639999</v>
+        <v>3.482774407872</v>
       </c>
       <c r="R6">
-        <v>1.4192367883200001</v>
+        <v>3.850907249802241</v>
       </c>
       <c r="S6">
-        <v>1.1348642537523199</v>
+        <v>3.6078677797248</v>
       </c>
       <c r="T6">
-        <v>0.9400840554144001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>3.679796468540161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3540,7 +3974,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3552,46 +3986,46 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>85.373803063295995</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>170.74760612659199</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>256.12140918988808</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>256.12140918988803</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>239.4502017760876</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>244.98210407616011</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>222.70349384870411</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>584.60699740608015</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>556.75873462176014</v>
+        <v>6.123350229259426</v>
       </c>
       <c r="Q7">
-        <v>584.60699740608015</v>
+        <v>6.430598097408</v>
       </c>
       <c r="R7">
-        <v>612.45526019040005</v>
+        <v>6.430598097407999</v>
       </c>
       <c r="S7">
-        <v>489.73757411927039</v>
+        <v>5.677786028570702</v>
       </c>
       <c r="T7">
-        <v>405.68242699036813</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>3.546428562431999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3614,46 +4048,46 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.82177992253440013</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1.6435598450688</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>2.4653397676032012</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>2.4653397676031998</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>2.3048682523901478</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>2.3581165098240011</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2.143669994265601</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>5.6272331301120007</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>5.3591749856640014</v>
+        <v>2642.461137395799</v>
       </c>
       <c r="Q8">
-        <v>5.6272331301120007</v>
+        <v>2775.050409727606</v>
       </c>
       <c r="R8">
-        <v>5.8952912745599999</v>
+        <v>2775.050409727606</v>
       </c>
       <c r="S8">
-        <v>4.7140515155865597</v>
+        <v>2450.183047713972</v>
       </c>
       <c r="T8">
-        <v>3.9049645378752</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1530.420325787963</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3661,7 +4095,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -3682,40 +4116,40 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.92268007175314282</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>1.8453601435062861</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.0643895707752669</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>2.527684669580204</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>2.4904296177860741</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>3.1590792898971429</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>2.8681610011197498</v>
+        <v>25.43545479846224</v>
       </c>
       <c r="Q9">
-        <v>2.4818963925599999</v>
+        <v>26.71171517384862</v>
       </c>
       <c r="R9">
-        <v>2.8071423957150849</v>
+        <v>26.71171517384862</v>
       </c>
       <c r="S9">
-        <v>2.1558457264032</v>
+        <v>23.58464965713985</v>
       </c>
       <c r="T9">
-        <v>1.1040927546569139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>14.73131864394831</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3726,7 +4160,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3744,40 +4178,40 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>398.17193865654872</v>
+        <v>0.9226800717531428</v>
       </c>
       <c r="K10">
-        <v>796.34387731309721</v>
+        <v>1.845360143506286</v>
       </c>
       <c r="L10">
-        <v>890.86349938840397</v>
+        <v>2.032287706347068</v>
       </c>
       <c r="M10">
-        <v>1090.7931535649959</v>
+        <v>2.498087788029893</v>
       </c>
       <c r="N10">
-        <v>1074.7161658292209</v>
+        <v>2.316436633056</v>
       </c>
       <c r="O10">
-        <v>1363.2642166402291</v>
+        <v>2.48189639256</v>
       </c>
       <c r="P10">
-        <v>1237.7217858678309</v>
+        <v>1.955198984811429</v>
       </c>
       <c r="Q10">
-        <v>1071.0337509431999</v>
+        <v>1.955198984811429</v>
       </c>
       <c r="R10">
-        <v>1211.3899107662801</v>
+        <v>1.955198984811429</v>
       </c>
       <c r="S10">
-        <v>930.33034808630396</v>
+        <v>1.983289513224686</v>
       </c>
       <c r="T10">
-        <v>476.45848874040689</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1.946909319259873</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3806,40 +4240,40 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>3.8326710672822859</v>
+        <v>398.1719386565486</v>
       </c>
       <c r="K11">
-        <v>7.6653421345645718</v>
+        <v>796.3438773130973</v>
       </c>
       <c r="L11">
-        <v>8.5751566786049587</v>
+        <v>877.0103102005423</v>
       </c>
       <c r="M11">
-        <v>10.49961324287162</v>
+        <v>1078.020960834438</v>
       </c>
       <c r="N11">
-        <v>10.344861489265231</v>
+        <v>999.6315008803201</v>
       </c>
       <c r="O11">
-        <v>13.122329358034291</v>
+        <v>1071.0337509432</v>
       </c>
       <c r="P11">
-        <v>11.913899543112811</v>
+        <v>843.7435619070857</v>
       </c>
       <c r="Q11">
-        <v>10.309415784480001</v>
+        <v>843.7435619070858</v>
       </c>
       <c r="R11">
-        <v>11.66043764373959</v>
+        <v>843.7435619070858</v>
       </c>
       <c r="S11">
-        <v>8.9550514789056006</v>
+        <v>855.8657053223451</v>
       </c>
       <c r="T11">
-        <v>4.5862314424210293</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>840.166252388299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3847,7 +4281,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -3868,40 +4302,40 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>9.4732282093686919</v>
+        <v>3.832671067282286</v>
       </c>
       <c r="K12">
-        <v>9.9361897337963327</v>
+        <v>7.665342134564573</v>
       </c>
       <c r="L12">
-        <v>12.78282942589564</v>
+        <v>8.44181047251859</v>
       </c>
       <c r="M12">
-        <v>28.00235467044277</v>
+        <v>10.37667235027802</v>
       </c>
       <c r="N12">
-        <v>28.317480375770351</v>
+        <v>9.622121398848002</v>
       </c>
       <c r="O12">
-        <v>30.98451173781709</v>
+        <v>10.30941578448</v>
       </c>
       <c r="P12">
-        <v>38.570408123558771</v>
+        <v>8.121595783062858</v>
       </c>
       <c r="Q12">
-        <v>43.493978954427511</v>
+        <v>8.121595783062858</v>
       </c>
       <c r="R12">
-        <v>51.68884982043555</v>
+        <v>8.121595783062858</v>
       </c>
       <c r="S12">
-        <v>50.394525177276698</v>
+        <v>8.238279516471772</v>
       </c>
       <c r="T12">
-        <v>45.016783080655671</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>8.087161787694857</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3912,7 +4346,7 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -3930,40 +4364,40 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>4088.0623272737189</v>
+        <v>7.751441131144821</v>
       </c>
       <c r="K13">
-        <v>4287.8480312767251</v>
+        <v>8.145138516469228</v>
       </c>
       <c r="L13">
-        <v>5516.282544559579</v>
+        <v>10.48456476453151</v>
       </c>
       <c r="M13">
-        <v>12084.093053937229</v>
+        <v>12.22216193989758</v>
       </c>
       <c r="N13">
-        <v>12220.081916005511</v>
+        <v>9.057587954323601</v>
       </c>
       <c r="O13">
-        <v>13371.00852685799</v>
+        <v>8.847773141070642</v>
       </c>
       <c r="P13">
-        <v>16644.61458255113</v>
+        <v>7.571427526421944</v>
       </c>
       <c r="Q13">
-        <v>18769.32476417987</v>
+        <v>7.79335222804057</v>
       </c>
       <c r="R13">
-        <v>22305.72673020334</v>
+        <v>7.928994681250924</v>
       </c>
       <c r="S13">
-        <v>21747.17586496325</v>
+        <v>8.037076684124834</v>
       </c>
       <c r="T13">
-        <v>19426.47331403679</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>7.277030904909006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -3992,40 +4426,40 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>39.350332561993042</v>
+        <v>3345.044980440188</v>
       </c>
       <c r="K14">
-        <v>41.273403509615548</v>
+        <v>3514.940544414798</v>
       </c>
       <c r="L14">
-        <v>53.097906846028039</v>
+        <v>4524.492948386291</v>
       </c>
       <c r="M14">
-        <v>116.3174732464546</v>
+        <v>5274.33296021734</v>
       </c>
       <c r="N14">
-        <v>117.6264569455076</v>
+        <v>3908.697571058107</v>
       </c>
       <c r="O14">
-        <v>128.7048949109325</v>
+        <v>3818.154409338946</v>
       </c>
       <c r="P14">
-        <v>160.2155414363211</v>
+        <v>3267.362186402085</v>
       </c>
       <c r="Q14">
-        <v>180.66729719531429</v>
+        <v>3363.13123071597</v>
       </c>
       <c r="R14">
-        <v>214.70753002334769</v>
+        <v>3421.666166293668</v>
       </c>
       <c r="S14">
-        <v>209.33110458253401</v>
+        <v>3468.307707533871</v>
       </c>
       <c r="T14">
-        <v>186.99279125810821</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>3140.318721272271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -4033,7 +4467,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
@@ -4054,40 +4488,40 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>32.1982939293708</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>33.83365229917987</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>43.55126902190013</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>50.7689803657284</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>37.62382688719035</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>36.75228843213959</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>31.4505451097527</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>32.37238617801468</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>32.93582406058076</v>
       </c>
       <c r="S15">
-        <v>7.0277777777777803</v>
+        <v>33.38478007251854</v>
       </c>
       <c r="T15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>30.22766683577587</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -4098,7 +4532,7 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4134,22 +4568,22 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>5.986600343579859</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>5.986600343579859</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>8.616163254768972</v>
       </c>
       <c r="S16">
-        <v>618.20000000000027</v>
+        <v>8.428238108857926</v>
       </c>
       <c r="T16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6.00670837036451</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -4196,22 +4630,22 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2583.448302114078</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2583.448302114078</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>3718.205835327225</v>
       </c>
       <c r="S17">
-        <v>11.67222222222223</v>
+        <v>3637.108906976382</v>
       </c>
       <c r="T17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2592.125689057299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -4219,61 +4653,61 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
         <v>35</v>
       </c>
       <c r="E18">
-        <v>732.78572500000007</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>575.30818333333343</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>260.3531000000001</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>553.81357500000001</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>462.12950000000001</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>370.44542500000011</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>382.83665000000002</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>60.829650000000022</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>85.996750000000006</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>34.288800000000009</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>29.489833333333369</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>5.4950000000000001</v>
+        <v>24.86741681179326</v>
       </c>
       <c r="Q18">
-        <v>4.1212500000000007</v>
+        <v>24.86741681179326</v>
       </c>
       <c r="R18">
-        <v>2.7475000000000001</v>
+        <v>35.79021659673266</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>35.00960445217908</v>
       </c>
       <c r="T18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>24.95094246151412</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -4284,49 +4718,49 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E19">
-        <v>65289.607837500007</v>
+        <v>851.9902777777777</v>
       </c>
       <c r="F19">
-        <v>51258.702775000012</v>
+        <v>656.2634722222226</v>
       </c>
       <c r="G19">
-        <v>23196.892650000009</v>
+        <v>294.5080709639485</v>
       </c>
       <c r="H19">
-        <v>49343.5801125</v>
+        <v>596.5353472222223</v>
       </c>
       <c r="I19">
-        <v>41174.729250000011</v>
+        <v>495.2666666666668</v>
       </c>
       <c r="J19">
-        <v>33005.878387500008</v>
+        <v>386.4111805555557</v>
       </c>
       <c r="K19">
-        <v>34109.909475000008</v>
+        <v>400.097777777778</v>
       </c>
       <c r="L19">
-        <v>5419.7889750000013</v>
+        <v>44.42833333333332</v>
       </c>
       <c r="M19">
-        <v>7662.1226250000018</v>
+        <v>72.22638888888886</v>
       </c>
       <c r="N19">
-        <v>3055.0572000000011</v>
+        <v>15.11291666666668</v>
       </c>
       <c r="O19">
-        <v>2627.4797500000041</v>
+        <v>9.812268518518525</v>
       </c>
       <c r="P19">
-        <v>489.59249999999997</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>367.19437500000009</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>244.79624999999999</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -4335,7 +4769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -4349,46 +4783,46 @@
         <v>36</v>
       </c>
       <c r="E20">
-        <v>1400.5608875</v>
+        <v>74945.51000000002</v>
       </c>
       <c r="F20">
-        <v>1099.576741666667</v>
+        <v>57728.35900000007</v>
       </c>
       <c r="G20">
-        <v>497.60845000000029</v>
+        <v>25906.46648583741</v>
       </c>
       <c r="H20">
-        <v>1058.4944625000001</v>
+        <v>52474.36150000001</v>
       </c>
       <c r="I20">
-        <v>883.26025000000004</v>
+        <v>43566.24000000001</v>
       </c>
       <c r="J20">
-        <v>708.02603750000026</v>
+        <v>33990.74350000002</v>
       </c>
       <c r="K20">
-        <v>731.70917499999996</v>
+        <v>35194.68800000002</v>
       </c>
       <c r="L20">
-        <v>116.262675</v>
+        <v>3908.147999999999</v>
       </c>
       <c r="M20">
-        <v>164.36412500000009</v>
+        <v>6353.409999999997</v>
       </c>
       <c r="N20">
-        <v>65.535600000000017</v>
+        <v>1329.411000000001</v>
       </c>
       <c r="O20">
-        <v>56.363416666666737</v>
+        <v>863.138333333334</v>
       </c>
       <c r="P20">
-        <v>10.5025</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>7.8768750000000018</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>5.2512500000000024</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -4397,7 +4831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -4405,43 +4839,43 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
         <v>35</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1415.044722222222</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1089.968027777779</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>489.1394917749057</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>990.767402777778</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>822.5733333333336</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>641.7785694444448</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>664.5102222222226</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>73.78966666666665</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>119.9586111111111</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>25.10058333333335</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>16.29689814814816</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4456,10 +4890,10 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>1.2265714285714291</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -4467,61 +4901,61 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>6.50297619047619</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>6.502976190476191</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>13.00595238095238</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>13.00595238095238</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>19.50892857142858</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>19.50892857142858</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>5.202380952380953</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.901785714285714</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.601190476190477</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.300595238095238</v>
       </c>
       <c r="T22">
-        <v>120.4614285714286</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -4529,7 +4963,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
         <v>36</v>
@@ -4538,52 +4972,52 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>572.0357142857141</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>572.0357142857141</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1144.071428571428</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1144.071428571428</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>457.6285714285714</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>343.2214285714285</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>228.8142857142858</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>114.4071428571429</v>
       </c>
       <c r="T23">
-        <v>4.8154285714285709</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -4591,61 +5025,61 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
       </c>
       <c r="E24">
-        <v>51.64606436363637</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>57.065469730144642</v>
+        <v>10.80059523809524</v>
       </c>
       <c r="G24">
-        <v>59.095622830946247</v>
+        <v>10.80059523809523</v>
       </c>
       <c r="H24">
-        <v>61.729949140103351</v>
+        <v>21.60119047619047</v>
       </c>
       <c r="I24">
-        <v>41.790011212548592</v>
+        <v>21.60119047619047</v>
       </c>
       <c r="J24">
-        <v>35.549561809868678</v>
+        <v>32.4017857142857</v>
       </c>
       <c r="K24">
-        <v>28.58000339634674</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="L24">
-        <v>35.046443614945417</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="M24">
-        <v>30.624810191722069</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="P24">
-        <v>2.814349112269821</v>
+        <v>8.640476190476189</v>
       </c>
       <c r="Q24">
-        <v>7.4481903891407431</v>
+        <v>6.480357142857142</v>
       </c>
       <c r="R24">
-        <v>6.4290909090909087</v>
+        <v>4.320238095238096</v>
       </c>
       <c r="S24">
-        <v>3.2145454545454548</v>
+        <v>2.160119047619047</v>
       </c>
       <c r="T24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -4653,61 +5087,61 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E25">
-        <v>22287.263159999999</v>
+        <v>80.66533090909091</v>
       </c>
       <c r="F25">
-        <v>24625.945014316261</v>
+        <v>79.3349203636364</v>
       </c>
       <c r="G25">
-        <v>25502.03416012372</v>
+        <v>80.70957818181817</v>
       </c>
       <c r="H25">
-        <v>26638.847282767671</v>
+        <v>58.93578996991064</v>
       </c>
       <c r="I25">
-        <v>18033.997146338279</v>
+        <v>41.7900112125486</v>
       </c>
       <c r="J25">
-        <v>15341.00321179718</v>
+        <v>38.0619491243167</v>
       </c>
       <c r="K25">
-        <v>12333.370696423481</v>
+        <v>30.87307520832137</v>
       </c>
       <c r="L25">
-        <v>15123.888359987979</v>
+        <v>36.44521188027093</v>
       </c>
       <c r="M25">
-        <v>13215.783475043139</v>
+        <v>46.02453063761835</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>24.18670348711744</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>26.56559727766887</v>
       </c>
       <c r="P25">
-        <v>1214.499886141054</v>
+        <v>19.23155954087625</v>
       </c>
       <c r="Q25">
-        <v>3214.180621775351</v>
+        <v>17.60037676358984</v>
       </c>
       <c r="R25">
-        <v>2774.4</v>
+        <v>6.42909090909091</v>
       </c>
       <c r="S25">
-        <v>1387.2</v>
+        <v>3.214545454545454</v>
       </c>
       <c r="T25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -4715,61 +5149,61 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
       </c>
       <c r="E26">
-        <v>214.5298058181819</v>
+        <v>34810.1928</v>
       </c>
       <c r="F26">
-        <v>237.04118195598551</v>
+        <v>34236.06948000001</v>
       </c>
       <c r="G26">
-        <v>245.474125605469</v>
+        <v>34829.28719999999</v>
       </c>
       <c r="H26">
-        <v>256.41671181273699</v>
+        <v>25433.06013316914</v>
       </c>
       <c r="I26">
-        <v>173.58927734443259</v>
+        <v>18033.99714633828</v>
       </c>
       <c r="J26">
-        <v>147.6674105948392</v>
+        <v>16425.19496826282</v>
       </c>
       <c r="K26">
-        <v>118.7169371848249</v>
+        <v>13322.91937836022</v>
       </c>
       <c r="L26">
-        <v>145.57753501592711</v>
+        <v>15727.51066525538</v>
       </c>
       <c r="M26">
-        <v>127.2107500271532</v>
+        <v>19861.35514438761</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>10437.4928125176</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>11464.07697905557</v>
       </c>
       <c r="P26">
-        <v>11.69037323558234</v>
+        <v>8299.157617255058</v>
       </c>
       <c r="Q26">
-        <v>30.93863700104616</v>
+        <v>7595.239511056849</v>
       </c>
       <c r="R26">
-        <v>26.70545454545454</v>
+        <v>2774.4</v>
       </c>
       <c r="S26">
-        <v>13.35272727272727</v>
+        <v>1387.2</v>
       </c>
       <c r="T26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -4777,61 +5211,61 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
         <v>35</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>335.0713745454546</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>329.5450538181819</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>335.2551709090909</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>244.8102044903981</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>173.5892773444326</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>158.1034809779309</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>128.2420047114888</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>151.3878031949716</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>191.1788195716454</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100.4678452541801</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>110.3494040764707</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>79.88493963133212</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>73.10925732568089</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>26.70545454545454</v>
       </c>
       <c r="S27">
-        <v>0.77380952380952384</v>
+        <v>13.35272727272727</v>
       </c>
       <c r="T27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -4839,10 +5273,10 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4875,25 +5309,25 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.080511756141994</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>0.872897211236099</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.359059843780464</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>11.53411946174977</v>
       </c>
       <c r="S28">
-        <v>333.92857142857139</v>
+        <v>6.337488091893917</v>
       </c>
       <c r="T28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0.58733228272047</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -4901,7 +5335,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
         <v>36</v>
@@ -4937,25 +5371,25 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>466.2823809197375</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>376.6887196180396</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1881.101978739108</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4977.416167724323</v>
       </c>
       <c r="S29">
-        <v>3.214285714285714</v>
+        <v>2734.869861194221</v>
       </c>
       <c r="T29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>253.4564696970644</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -4963,61 +5397,61 @@
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
         <v>35</v>
       </c>
       <c r="E30">
-        <v>128.177154</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>123.68481300000001</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>114.700131</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>106.1055855</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>97.794985499999981</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>109.187433</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>100.40589900000001</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>74.130551999999994</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>73.341045000000022</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>61.790849999999992</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>54.698624999999993</v>
+        <v>4.488279602435977</v>
       </c>
       <c r="P30">
-        <v>19.237500000000001</v>
+        <v>3.625880723596104</v>
       </c>
       <c r="Q30">
-        <v>14.428125</v>
+        <v>18.1068639664727</v>
       </c>
       <c r="R30">
-        <v>9.6187500000000004</v>
+        <v>47.91095776419135</v>
       </c>
       <c r="S30">
-        <v>95.551091141935302</v>
+        <v>26.32495053555935</v>
       </c>
       <c r="T30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2.439687943608107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -5025,61 +5459,61 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E31">
-        <v>12588.26247</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>12147.070215</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>11264.685705</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>10420.6164525</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>9604.4334524999977</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>10723.284315000001</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>9860.850945000002</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>7280.3523599999962</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>7202.8149750000011</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>6068.4717499999988</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>5371.9452083333317</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>1889.3125</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>1416.984375</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>944.65625</v>
+        <v>1.469113435601052</v>
       </c>
       <c r="S31">
-        <v>9384.0608646184592</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>23.91867806584329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -5087,61 +5521,61 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
         <v>36</v>
       </c>
       <c r="E32">
-        <v>503.21401199999991</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>485.57741399999992</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>450.30421799999988</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>416.56266899999991</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>383.93586899999991</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>428.66177399999998</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>394.18612200000013</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>291.03105599999992</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>287.93151000000012</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>242.58630000000011</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>214.74275</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>75.52500000000002</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>56.643750000000018</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>37.762500000000003</v>
+        <v>633.9789518247616</v>
       </c>
       <c r="S32">
-        <v>375.12650596463487</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>10321.82953456776</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -5149,19 +5583,19 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
         <v>35</v>
       </c>
       <c r="E33">
-        <v>28.972666666666669</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>28.44741414141415</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>27.396909090909091</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -5194,16 +5628,16 @@
         <v>0</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>6.102471194035139</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="T33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>99.35450888888754</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -5211,19 +5645,19 @@
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E34">
-        <v>12502.82</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>12276.15333333333</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>11822.82</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -5259,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="T34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -5273,19 +5707,19 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
         <v>36</v>
       </c>
       <c r="E35">
-        <v>120.348</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>118.1661818181818</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>113.80254545454549</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -5321,13 +5755,13 @@
         <v>0</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>333.9285714285714</v>
       </c>
       <c r="T35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -5335,19 +5769,19 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
         <v>35</v>
       </c>
       <c r="E36">
-        <v>1.5657777777777779</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>1.6928888888888891</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>1.6928888888888891</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -5383,13 +5817,13 @@
         <v>0</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="T36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -5397,61 +5831,61 @@
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E37">
-        <v>675.69333333333338</v>
+        <v>134.92332</v>
       </c>
       <c r="F37">
-        <v>730.54666666666674</v>
+        <v>128.182257</v>
       </c>
       <c r="G37">
-        <v>730.54666666666674</v>
+        <v>132.810678</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>106.1055855</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>97.7949855</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>109.187433</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100.405899</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>74.13055199999998</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>73.34104500000001</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>61.79084999999999</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>54.698625</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>19.2375</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>14.428125</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>9.61875</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>95.55109114193532</v>
       </c>
       <c r="T37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -5459,57 +5893,119 @@
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
         <v>36</v>
       </c>
       <c r="E38">
-        <v>6.5039999999999996</v>
+        <v>13250.8026</v>
       </c>
       <c r="F38">
-        <v>7.032</v>
+        <v>12588.763635</v>
       </c>
       <c r="G38">
-        <v>7.032</v>
+        <v>13043.32029</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>10420.6164525</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>9604.433452499998</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>10723.284315</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>9860.850945</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>7280.352359999998</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>7202.814974999998</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>6068.471749999998</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>5371.945208333332</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1889.3125</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1416.984375</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>944.65625</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>9384.060864618459</v>
       </c>
       <c r="T38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="A39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39">
+        <v>529.6989599999999</v>
+      </c>
+      <c r="F39">
+        <v>503.2340459999999</v>
+      </c>
+      <c r="G39">
+        <v>521.404884</v>
+      </c>
+      <c r="H39">
+        <v>416.562669</v>
+      </c>
+      <c r="I39">
+        <v>383.935869</v>
+      </c>
+      <c r="J39">
+        <v>428.661774</v>
+      </c>
+      <c r="K39">
+        <v>394.186122</v>
+      </c>
+      <c r="L39">
+        <v>291.031056</v>
+      </c>
+      <c r="M39">
+        <v>287.9315100000001</v>
+      </c>
+      <c r="N39">
+        <v>242.5863</v>
+      </c>
+      <c r="O39">
+        <v>214.7427499999999</v>
+      </c>
+      <c r="P39">
+        <v>75.52500000000001</v>
+      </c>
+      <c r="Q39">
+        <v>56.64375000000001</v>
+      </c>
+      <c r="R39">
+        <v>37.7625</v>
+      </c>
+      <c r="S39">
+        <v>375.1265059646349</v>
+      </c>
+      <c r="T39">
         <v>0</v>
       </c>
     </row>

--- a/database_postprocessing.xlsx
+++ b/database_postprocessing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="41">
   <si>
     <t>file</t>
   </si>
@@ -36,6 +36,9 @@
     <t>ELC_BGS_E</t>
   </si>
   <si>
+    <t>ELC_BGS_LAN_N</t>
+  </si>
+  <si>
     <t>ELC_BIO_CEN_E</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
   </si>
   <si>
     <t>ELC_CHP_NGA_TURB_N</t>
+  </si>
+  <si>
+    <t>ELC_CHP_NGA_TURB_P</t>
   </si>
   <si>
     <t>ELC_COA_COND_E</t>
@@ -75,6 +81,9 @@
     <t>ELC_NGA_CC_N</t>
   </si>
   <si>
+    <t>ELC_NGA_CC_P</t>
+  </si>
+  <si>
     <t>ELC_NGA_CT_N</t>
   </si>
   <si>
@@ -82,6 +91,9 @@
   </si>
   <si>
     <t>ELC_NGA_OIL_STM_E</t>
+  </si>
+  <si>
+    <t>ELC_NGA_OIL_STM_N</t>
   </si>
   <si>
     <t>ELC_NUC_LWR_E</t>
@@ -484,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -557,52 +569,52 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>0.4596580096708134</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="E2">
-        <v>0.5443859630190504</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="F2">
-        <v>0.7138418697155248</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="G2">
-        <v>0.8597582948123215</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="H2">
-        <v>1.005674719909118</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="I2">
-        <v>1.013544847793348</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="J2">
-        <v>1.021414975677577</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="K2">
-        <v>1.294955096194314</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="L2">
-        <v>1.294955096194314</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="M2">
-        <v>1.294955096194314</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="N2">
-        <v>1.294955096194314</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="O2">
-        <v>1.329413493957698</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="P2">
-        <v>1.366341646567634</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="Q2">
-        <v>1.403269799177569</v>
+        <v>0.2919404283294496</v>
       </c>
       <c r="R2">
-        <v>3.014811269336009</v>
+        <v>0.08477617133177981</v>
       </c>
       <c r="S2">
-        <v>6.680218180696697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -616,52 +628,52 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.409</v>
+        <v>0.1156140475741612</v>
       </c>
       <c r="I3">
-        <v>0.409</v>
+        <v>0.1845041074831423</v>
       </c>
       <c r="J3">
-        <v>0.409</v>
+        <v>0.2792587022639487</v>
       </c>
       <c r="K3">
-        <v>0.409</v>
+        <v>0.5681202808173806</v>
       </c>
       <c r="L3">
-        <v>0.409</v>
+        <v>0.5187749950934094</v>
       </c>
       <c r="M3">
-        <v>0.409</v>
+        <v>0.4742593652774342</v>
       </c>
       <c r="N3">
-        <v>0.409</v>
+        <v>0.5441516755335334</v>
       </c>
       <c r="O3">
-        <v>0.409</v>
+        <v>0.8435864027666037</v>
       </c>
       <c r="P3">
-        <v>0.409</v>
+        <v>1.002976572934977</v>
       </c>
       <c r="Q3">
-        <v>0.409</v>
+        <v>1.115153929707553</v>
       </c>
       <c r="R3">
-        <v>0.0818</v>
+        <v>1.275111733751409</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.50685402533556</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -675,52 +687,52 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="G4">
-        <v>0.1333333333333333</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="H4">
-        <v>0.2666666666666667</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="I4">
-        <v>0.4</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="J4">
-        <v>0.5333333333333333</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="K4">
-        <v>0.6666666666666666</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="L4">
-        <v>0.8</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="M4">
-        <v>0.9333333333333333</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.5834923847918516</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>0.2562923847918516</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>0.03489847695837033</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -743,40 +755,40 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5">
         <v>1</v>
@@ -802,40 +814,40 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.5333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0.9333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>1</v>
@@ -861,43 +873,43 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1.753365862228919</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H7">
-        <v>2.617184037402559</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="I7">
-        <v>2.617184037402559</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="J7">
-        <v>2.820847420443402</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -914,49 +926,49 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.8648733377620116</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.8648733377620116</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2.828846074642624</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3.613428927490221</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3.613428927490221</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>3.613428927490221</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>3.930512207035269</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>3.930512207035269</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>5.590352487959258</v>
+        <v>4</v>
       </c>
       <c r="R8">
-        <v>5.590352487959258</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>3.625096384441624</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -970,52 +982,52 @@
         <v>12</v>
       </c>
       <c r="D9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>11.213</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>11.213</v>
+        <v>2.516272640526505</v>
       </c>
       <c r="P9">
-        <v>11.213</v>
+        <v>2.516272640526505</v>
       </c>
       <c r="Q9">
-        <v>11.213</v>
+        <v>3.377926192120482</v>
       </c>
       <c r="R9">
-        <v>2.2426</v>
+        <v>3.377926192120482</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.119789871857229</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1032,49 +1044,49 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.1069548716332221</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0.1069548716332221</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.211332517443957</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.211332517443957</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.3132542186473804</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.3132542186473804</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.3132542186473804</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0.3132542186473804</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.3132542186473804</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>0.3132542186473804</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0.3132542186473804</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>0.2704722699940916</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.1436727595277174</v>
+        <v>2.326435820985384</v>
       </c>
       <c r="R10">
-        <v>0.02038434024068468</v>
+        <v>2.326435820985384</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.326435820985384</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1088,49 +1100,49 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="E11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="F11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="G11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="H11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="I11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="J11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="K11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="L11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="M11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="N11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="O11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="P11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="Q11">
-        <v>0.531</v>
+        <v>11.213</v>
       </c>
       <c r="R11">
-        <v>0.1062</v>
+        <v>2.2426</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1147,52 +1159,52 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>16.658</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>16.658</v>
+        <v>0.1069603282524054</v>
       </c>
       <c r="F12">
-        <v>16.658</v>
+        <v>0.1069603282524054</v>
       </c>
       <c r="G12">
-        <v>16.658</v>
+        <v>0.2113432991975239</v>
       </c>
       <c r="H12">
-        <v>16.658</v>
+        <v>0.2113432991975239</v>
       </c>
       <c r="I12">
-        <v>16.658</v>
+        <v>0.3132702002380513</v>
       </c>
       <c r="J12">
-        <v>16.658</v>
+        <v>0.3132702002380513</v>
       </c>
       <c r="K12">
-        <v>16.658</v>
+        <v>0.3132702002380513</v>
       </c>
       <c r="L12">
-        <v>16.658</v>
+        <v>0.3132702002380513</v>
       </c>
       <c r="M12">
-        <v>17.85365199022801</v>
+        <v>0.3132702002380513</v>
       </c>
       <c r="N12">
-        <v>18.29287704943763</v>
+        <v>0.3132702002380513</v>
       </c>
       <c r="O12">
-        <v>28.63211863269722</v>
+        <v>0.3132702002380513</v>
       </c>
       <c r="P12">
-        <v>29.32344801801103</v>
+        <v>0.2704860689370892</v>
       </c>
       <c r="Q12">
-        <v>32.9155126590416</v>
+        <v>0.1436800894185749</v>
       </c>
       <c r="R12">
-        <v>28.36513413488287</v>
+        <v>0.02038538020810549</v>
       </c>
       <c r="S12">
-        <v>25.03353413488287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1206,52 +1218,52 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="E13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="F13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="G13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="H13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="I13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="J13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="K13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="L13">
-        <v>1.809</v>
+        <v>0.531</v>
       </c>
       <c r="M13">
-        <v>4.851808751127283</v>
+        <v>0.531</v>
       </c>
       <c r="N13">
-        <v>4.851808751127283</v>
+        <v>0.531</v>
       </c>
       <c r="O13">
-        <v>9.002701575702346</v>
+        <v>0.531</v>
       </c>
       <c r="P13">
-        <v>9.002701575702346</v>
+        <v>0.531</v>
       </c>
       <c r="Q13">
-        <v>9.002701575702346</v>
+        <v>0.531</v>
       </c>
       <c r="R13">
-        <v>9.364501575702345</v>
+        <v>0.1062</v>
       </c>
       <c r="S13">
-        <v>9.002701575702343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1265,52 +1277,52 @@
         <v>17</v>
       </c>
       <c r="D14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="E14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="F14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="G14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="H14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="I14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="J14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="K14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="L14">
-        <v>16.41</v>
+        <v>16.658</v>
       </c>
       <c r="M14">
-        <v>16.41</v>
+        <v>21.09062205417134</v>
       </c>
       <c r="N14">
-        <v>16.41</v>
+        <v>21.09062205417134</v>
       </c>
       <c r="O14">
-        <v>16.41</v>
+        <v>34.09985098436238</v>
       </c>
       <c r="P14">
-        <v>16.41</v>
+        <v>34.577727799774</v>
       </c>
       <c r="Q14">
-        <v>16.41</v>
+        <v>36.17972016417378</v>
       </c>
       <c r="R14">
-        <v>3.282</v>
+        <v>36.54362212131757</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>33.21202212131757</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1324,52 +1336,52 @@
         <v>18</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="N15">
-        <v>0.3036630581992403</v>
+        <v>3.852969260786626</v>
       </c>
       <c r="O15">
-        <v>0.3036630581992403</v>
+        <v>3.852969260786626</v>
       </c>
       <c r="P15">
-        <v>1.432984223327345</v>
+        <v>3.852969260786626</v>
       </c>
       <c r="Q15">
-        <v>3.937595259536566</v>
+        <v>3.852969260786626</v>
       </c>
       <c r="R15">
-        <v>3.937595259536566</v>
+        <v>2.405769260786626</v>
       </c>
       <c r="S15">
-        <v>3.785763730436946</v>
+        <v>2.043969260786626</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1383,52 +1395,52 @@
         <v>19</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>16.41</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>16.41</v>
       </c>
       <c r="F16">
-        <v>0.5440525151414858</v>
+        <v>16.41</v>
       </c>
       <c r="G16">
-        <v>1.116208183155136</v>
+        <v>16.41</v>
       </c>
       <c r="H16">
-        <v>1.116208183155136</v>
+        <v>16.41</v>
       </c>
       <c r="I16">
-        <v>1.116208183155136</v>
+        <v>16.41</v>
       </c>
       <c r="J16">
-        <v>1.116208183155136</v>
+        <v>16.41</v>
       </c>
       <c r="K16">
-        <v>1.116208183155136</v>
+        <v>16.41</v>
       </c>
       <c r="L16">
-        <v>5.860517872611105</v>
+        <v>16.41</v>
       </c>
       <c r="M16">
-        <v>12.55839857353136</v>
+        <v>16.41</v>
       </c>
       <c r="N16">
-        <v>12.55839857353136</v>
+        <v>16.41</v>
       </c>
       <c r="O16">
-        <v>12.55839857353136</v>
+        <v>16.41</v>
       </c>
       <c r="P16">
-        <v>12.55839857353136</v>
+        <v>16.41</v>
       </c>
       <c r="Q16">
-        <v>11.67105265758168</v>
+        <v>16.41</v>
       </c>
       <c r="R16">
-        <v>11.44219039037622</v>
+        <v>3.282</v>
       </c>
       <c r="S16">
-        <v>14.24484671678862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1442,52 +1454,52 @@
         <v>20</v>
       </c>
       <c r="D17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>6.547</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>6.547</v>
+        <v>1.012974740602063</v>
       </c>
       <c r="Q17">
-        <v>6.547</v>
+        <v>4.536111897423965</v>
       </c>
       <c r="R17">
-        <v>1.3094</v>
+        <v>4.536111897423965</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>4.536111897423965</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -1501,49 +1513,49 @@
         <v>21</v>
       </c>
       <c r="D18">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="G18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="H18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="I18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="J18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="K18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="L18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="M18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="N18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="O18">
-        <v>8.315</v>
+        <v>0.8816959667563359</v>
       </c>
       <c r="P18">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1.663</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -1560,52 +1572,52 @@
         <v>22</v>
       </c>
       <c r="D19">
-        <v>7.716</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>7.716</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>7.716</v>
+        <v>1.85596319472604</v>
       </c>
       <c r="G19">
-        <v>7.716</v>
+        <v>2.289187884556547</v>
       </c>
       <c r="H19">
-        <v>7.716</v>
+        <v>2.289187884556547</v>
       </c>
       <c r="I19">
-        <v>7.716</v>
+        <v>2.365488334819183</v>
       </c>
       <c r="J19">
-        <v>7.716</v>
+        <v>2.365488334819183</v>
       </c>
       <c r="K19">
-        <v>7.716</v>
+        <v>2.365488334819183</v>
       </c>
       <c r="L19">
-        <v>7.716</v>
+        <v>7.315935266156991</v>
       </c>
       <c r="M19">
-        <v>7.716</v>
+        <v>14.17285026697301</v>
       </c>
       <c r="N19">
-        <v>7.716</v>
+        <v>14.17285026697301</v>
       </c>
       <c r="O19">
-        <v>7.716</v>
+        <v>14.17285026697301</v>
       </c>
       <c r="P19">
-        <v>7.716</v>
+        <v>14.17285026697301</v>
       </c>
       <c r="Q19">
-        <v>7.716</v>
+        <v>12.05695225834867</v>
       </c>
       <c r="R19">
-        <v>4.718251751362141</v>
+        <v>12.72149569146447</v>
       </c>
       <c r="S19">
-        <v>4.687413504621214</v>
+        <v>13.53054673997953</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -1619,52 +1631,52 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="M20">
-        <v>8</v>
+        <v>6.547</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>6.547</v>
       </c>
       <c r="O20">
-        <v>8</v>
+        <v>6.547</v>
       </c>
       <c r="P20">
-        <v>8</v>
+        <v>6.547</v>
       </c>
       <c r="Q20">
-        <v>8</v>
+        <v>6.547</v>
       </c>
       <c r="R20">
-        <v>8</v>
+        <v>1.3094</v>
       </c>
       <c r="S20">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -1678,52 +1690,52 @@
         <v>24</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>8.315</v>
       </c>
       <c r="M21">
-        <v>3.2</v>
+        <v>8.315</v>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>8.315</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>8.315</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>8.315</v>
       </c>
       <c r="Q21">
-        <v>3.2</v>
+        <v>8.315</v>
       </c>
       <c r="R21">
-        <v>3.2</v>
+        <v>1.663</v>
       </c>
       <c r="S21">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -1743,46 +1755,46 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0.5893116498499628</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2.74071810375005</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>3.597888152805742</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>3.859070243059547</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>4.156702820767097</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>6.870498712883003</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>13.85636873643281</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>15.66285363773892</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>16.64406225393921</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>25.09535642343685</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>25.09069667550285</v>
+        <v>0.2658962635839847</v>
       </c>
       <c r="Q22">
-        <v>26.26963219511951</v>
+        <v>0.2658962635839847</v>
       </c>
       <c r="R22">
-        <v>29.10279617947654</v>
+        <v>0.2658962635839847</v>
       </c>
       <c r="S22">
-        <v>31.10884593146339</v>
+        <v>0.2658962635839847</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -1796,52 +1808,52 @@
         <v>26</v>
       </c>
       <c r="D23">
-        <v>0.306055879815012</v>
+        <v>7.716</v>
       </c>
       <c r="E23">
-        <v>1.62754375958585</v>
+        <v>7.716</v>
       </c>
       <c r="F23">
-        <v>3.492717415705298</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="G23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="H23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="I23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="J23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="K23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="L23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="M23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="N23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="O23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="P23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="Q23">
-        <v>3.49445508606137</v>
+        <v>7.799478603231965</v>
       </c>
       <c r="R23">
-        <v>2.754826406264027</v>
+        <v>4.718492466933343</v>
       </c>
       <c r="S23">
-        <v>0.0003475340712144501</v>
+        <v>4.687652646888027</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -1855,52 +1867,52 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>11.279</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>11.279</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>14.11596059487446</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>14.11596059487446</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>14.11596059487446</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>14.11596059487446</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>14.11596059487446</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>14.11596059487446</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>14.11596059487446</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>14.11596059487446</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>6.888564555229475</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>1.795803960355017</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>1.795803960355017</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>1.795803960355017</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>1.795803960355017</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>1.795803960355017</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -1914,52 +1926,52 @@
         <v>28</v>
       </c>
       <c r="D25">
-        <v>2.829733814529193</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>5.67972458305595</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>11.20412699448115</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>11.20412699448115</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>12.50496248826331</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>12.50496248826331</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>12.50496248826331</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>14.77253911403659</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>18.50835331790292</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>19.24086456527085</v>
+        <v>3.2</v>
       </c>
       <c r="N25">
-        <v>29.63585000183791</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
-        <v>47.78127829695371</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>58.43315855718257</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>69.08503881741146</v>
+        <v>3.2</v>
       </c>
       <c r="R25">
-        <v>79.73691907764031</v>
+        <v>3.2</v>
       </c>
       <c r="S25">
-        <v>90.38879933786922</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -1973,52 +1985,288 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>2.831092141278737</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>2.831092141278737</v>
+        <v>0.65577484449026</v>
       </c>
       <c r="F26">
-        <v>3.006961032555189</v>
+        <v>2.666133590943942</v>
       </c>
       <c r="G26">
-        <v>3.006961032555189</v>
+        <v>4.826740471699576</v>
       </c>
       <c r="H26">
-        <v>3.006961032555189</v>
+        <v>5.686447672140506</v>
       </c>
       <c r="I26">
-        <v>3.006961032555189</v>
+        <v>5.940341828104529</v>
       </c>
       <c r="J26">
-        <v>3.006961032555189</v>
+        <v>6.262115036677836</v>
       </c>
       <c r="K26">
-        <v>3.006961032555189</v>
+        <v>9.042830358519804</v>
       </c>
       <c r="L26">
-        <v>3.006961032555189</v>
+        <v>15.98015258734092</v>
       </c>
       <c r="M26">
-        <v>3.006961032555189</v>
+        <v>17.78880412100943</v>
       </c>
       <c r="N26">
-        <v>3.006961032555189</v>
+        <v>18.87938163622366</v>
       </c>
       <c r="O26">
-        <v>3.006961032555189</v>
+        <v>24.48233196999114</v>
       </c>
       <c r="P26">
-        <v>3.006961032555189</v>
+        <v>26.1396121191418</v>
       </c>
       <c r="Q26">
-        <v>3.006961032555189</v>
+        <v>27.16515154036342</v>
       </c>
       <c r="R26">
-        <v>8.305800546524347</v>
+        <v>28.9177559773951</v>
       </c>
       <c r="S26">
-        <v>10.69643341259609</v>
+        <v>31.11145256659376</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <v>0.3060747959710572</v>
+      </c>
+      <c r="E27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="F27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="G27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="H27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="I27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="J27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="K27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="L27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="M27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="N27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="O27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="P27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="Q27">
+        <v>0.7621209243680023</v>
+      </c>
+      <c r="R27">
+        <v>0.3686575954265898</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28">
+        <v>11.279</v>
+      </c>
+      <c r="E28">
+        <v>11.279</v>
+      </c>
+      <c r="F28">
+        <v>11.84457220001526</v>
+      </c>
+      <c r="G28">
+        <v>11.84457220001526</v>
+      </c>
+      <c r="H28">
+        <v>11.84457220001526</v>
+      </c>
+      <c r="I28">
+        <v>11.84457220001526</v>
+      </c>
+      <c r="J28">
+        <v>11.84457220001526</v>
+      </c>
+      <c r="K28">
+        <v>14.11219283137281</v>
+      </c>
+      <c r="L28">
+        <v>14.11219283137281</v>
+      </c>
+      <c r="M28">
+        <v>14.11219283137281</v>
+      </c>
+      <c r="N28">
+        <v>13.08696300585639</v>
+      </c>
+      <c r="O28">
+        <v>10.26559080584112</v>
+      </c>
+      <c r="P28">
+        <v>10.26559080584112</v>
+      </c>
+      <c r="Q28">
+        <v>7.997970174483577</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <v>2.830007614791413</v>
+      </c>
+      <c r="E29">
+        <v>5.680053691486149</v>
+      </c>
+      <c r="F29">
+        <v>13.47600676203987</v>
+      </c>
+      <c r="G29">
+        <v>13.47600676203987</v>
+      </c>
+      <c r="H29">
+        <v>14.77686750040485</v>
+      </c>
+      <c r="I29">
+        <v>14.77686750040485</v>
+      </c>
+      <c r="J29">
+        <v>14.77686750040485</v>
+      </c>
+      <c r="K29">
+        <v>14.77686750040485</v>
+      </c>
+      <c r="L29">
+        <v>19.66300221522456</v>
+      </c>
+      <c r="M29">
+        <v>20.02616531141269</v>
+      </c>
+      <c r="N29">
+        <v>23.35874837643161</v>
+      </c>
+      <c r="O29">
+        <v>39.31245356602023</v>
+      </c>
+      <c r="P29">
+        <v>49.96454054129855</v>
+      </c>
+      <c r="Q29">
+        <v>62.88424814793446</v>
+      </c>
+      <c r="R29">
+        <v>81.53430529769638</v>
+      </c>
+      <c r="S29">
+        <v>92.18639227297471</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30">
+        <v>2.546</v>
+      </c>
+      <c r="E30">
+        <v>2.546</v>
+      </c>
+      <c r="F30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="G30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="H30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="I30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="J30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="K30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="L30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="M30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="N30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="O30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="P30">
+        <v>3.007504380262247</v>
+      </c>
+      <c r="Q30">
+        <v>3.37256509749842</v>
+      </c>
+      <c r="R30">
+        <v>7.597955988518064</v>
+      </c>
+      <c r="S30">
+        <v>11.52941866508463</v>
       </c>
     </row>
   </sheetData>
@@ -2028,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2042,7 +2290,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1">
         <v>2007</v>
@@ -2104,55 +2352,55 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>7.390620000000002</v>
+        <v>4.693730232558139</v>
       </c>
       <c r="F2">
-        <v>8.75292</v>
+        <v>4.69373023255814</v>
       </c>
       <c r="G2">
-        <v>11.47752</v>
+        <v>4.69373023255814</v>
       </c>
       <c r="H2">
-        <v>13.82364</v>
+        <v>4.459043720930232</v>
       </c>
       <c r="I2">
-        <v>16.16976</v>
+        <v>4.224357209302326</v>
       </c>
       <c r="J2">
-        <v>16.2963</v>
+        <v>3.989670697674418</v>
       </c>
       <c r="K2">
-        <v>16.42284</v>
+        <v>3.754984186046511</v>
       </c>
       <c r="L2">
-        <v>20.82096</v>
+        <v>3.520297674418604</v>
       </c>
       <c r="M2">
-        <v>19.50597000000001</v>
+        <v>3.285611162790699</v>
       </c>
       <c r="N2">
-        <v>18.19098</v>
+        <v>3.050924651162791</v>
       </c>
       <c r="O2">
-        <v>18.72165</v>
+        <v>2.933581395348838</v>
       </c>
       <c r="P2">
-        <v>21.375</v>
+        <v>2.34686511627907</v>
       </c>
       <c r="Q2">
-        <v>21.96875</v>
+        <v>1.760148837209302</v>
       </c>
       <c r="R2">
-        <v>22.5625</v>
+        <v>1.173432558139535</v>
       </c>
       <c r="S2">
-        <v>48.4737</v>
+        <v>0.5867162790697673</v>
       </c>
       <c r="T2">
-        <v>55.00000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -2163,10 +2411,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2178,43 +2426,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1.369633204224</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>2.739266408448001</v>
+        <v>1.828406511627907</v>
       </c>
       <c r="J3">
-        <v>4.108899612672001</v>
+        <v>2.937792558139537</v>
       </c>
       <c r="K3">
-        <v>5.478532816896005</v>
+        <v>4.491075348837207</v>
       </c>
       <c r="L3">
-        <v>6.252481255680002</v>
+        <v>8.499918139534886</v>
       </c>
       <c r="M3">
-        <v>7.502977506816003</v>
+        <v>8.006330930232563</v>
       </c>
       <c r="N3">
-        <v>8.753473757951998</v>
+        <v>7.512743720930238</v>
       </c>
       <c r="O3">
-        <v>9.378721883520003</v>
+        <v>8.454115116279073</v>
       </c>
       <c r="P3">
-        <v>5.804624013120001</v>
+        <v>13.16097209302326</v>
       </c>
       <c r="Q3">
-        <v>5.804624013120002</v>
+        <v>15.80822906976745</v>
       </c>
       <c r="R3">
-        <v>6.4181787496704</v>
+        <v>18.45548604651162</v>
       </c>
       <c r="S3">
-        <v>6.013112966207999</v>
+        <v>21.10274302325582</v>
       </c>
       <c r="T3">
-        <v>6.132994114233601</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -2225,58 +2473,58 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2.69688976744186</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4.059189767441858</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>6.783789767441862</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>10.11699627906977</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>10.11699627906977</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>9.974176744186048</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>9.387460465116281</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>8.800744186046511</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>8.214027906976746</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>7.627311627906979</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>7.333953488372093</v>
       </c>
       <c r="P4">
-        <v>30.61675114629714</v>
+        <v>5.867162790697676</v>
       </c>
       <c r="Q4">
-        <v>32.15299048704</v>
+        <v>4.400372093023256</v>
       </c>
       <c r="R4">
-        <v>32.15299048703999</v>
+        <v>2.933581395348838</v>
       </c>
       <c r="S4">
-        <v>28.38893014285351</v>
+        <v>1.466790697674419</v>
       </c>
       <c r="T4">
-        <v>17.73214281216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -2287,10 +2535,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2302,43 +2550,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1.369560292992</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2.739120585984</v>
       </c>
       <c r="J5">
-        <v>5.961932771327999</v>
+        <v>4.108680878976</v>
       </c>
       <c r="K5">
-        <v>11.923865542656</v>
+        <v>5.478241171968</v>
       </c>
       <c r="L5">
-        <v>13.13170517947336</v>
+        <v>6.167233169702405</v>
       </c>
       <c r="M5">
-        <v>16.14149032265469</v>
+        <v>7.502540039424002</v>
       </c>
       <c r="N5">
-        <v>14.967744398208</v>
+        <v>8.752963379328005</v>
       </c>
       <c r="O5">
-        <v>16.03686899808</v>
+        <v>9.378175049279999</v>
       </c>
       <c r="P5">
-        <v>12.63359344032</v>
+        <v>5.804087901120001</v>
       </c>
       <c r="Q5">
-        <v>12.63359344032</v>
+        <v>5.80408790112</v>
       </c>
       <c r="R5">
-        <v>12.63359344032</v>
+        <v>5.9947058823552</v>
       </c>
       <c r="S5">
-        <v>12.81510147006719</v>
+        <v>6.066695079408805</v>
       </c>
       <c r="T5">
-        <v>12.58002944752533</v>
+        <v>6.106395667910397</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -2349,10 +2597,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2370,37 +2618,37 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>47.90438439773663</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>50.35442498985721</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>64.93191253293078</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>75.67086408829832</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>56.08996444614699</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>54.78578003370982</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>46.87824273904454</v>
+        <v>30.46801590775935</v>
       </c>
       <c r="Q6">
-        <v>48.25280599414748</v>
+        <v>32.15071989504</v>
       </c>
       <c r="R6">
-        <v>49.09085259148937</v>
+        <v>32.15071989504</v>
       </c>
       <c r="S6">
-        <v>50.04207116921336</v>
+        <v>28.61959070957422</v>
       </c>
       <c r="T6">
-        <v>45.75341938467835</v>
+        <v>17.5388342774551</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -2411,10 +2659,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2432,37 +2680,37 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>5.961615393024</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>11.923230786048</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>12.95930292479999</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>16.12422656591962</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>14.966633574144</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>16.03567882944</v>
       </c>
       <c r="P7">
-        <v>38.24892046548935</v>
+        <v>12.63242660832</v>
       </c>
       <c r="Q7">
-        <v>38.24892046548935</v>
+        <v>12.63242660832</v>
       </c>
       <c r="R7">
-        <v>55.64449049335579</v>
+        <v>12.63242660832</v>
       </c>
       <c r="S7">
-        <v>54.40129337425194</v>
+        <v>13.1769469636992</v>
       </c>
       <c r="T7">
-        <v>38.87684204236925</v>
+        <v>12.45677381746239</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -2473,58 +2721,58 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>266.71</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>205.4390000000002</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>92.19383091045343</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>186.7415</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>155.0400000000001</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>120.9635000000001</v>
+        <v>69.91550227437651</v>
       </c>
       <c r="K8">
-        <v>125.2480000000001</v>
+        <v>68.49892239729242</v>
       </c>
       <c r="L8">
-        <v>13.908</v>
+        <v>69.64252986226985</v>
       </c>
       <c r="M8">
-        <v>22.60999999999999</v>
+        <v>76.44595287110909</v>
       </c>
       <c r="N8">
-        <v>4.731000000000005</v>
+        <v>55.27158701562642</v>
       </c>
       <c r="O8">
-        <v>3.071666666666669</v>
+        <v>54.19554097789611</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>48.60425445890759</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>48.83306601413146</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>50.45401344321652</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>55.26041734603275</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>44.09075790409101</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -2535,58 +2783,58 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2.375</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2.375</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>7.124999999999998</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>7.125000000000001</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>7.125</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>7.125</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>7.124999999999999</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>7.125000000000002</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>1.9</v>
+        <v>24.48429566357507</v>
       </c>
       <c r="Q9">
-        <v>1.425</v>
+        <v>24.48429566357507</v>
       </c>
       <c r="R9">
-        <v>0.95</v>
+        <v>32.86851443900241</v>
       </c>
       <c r="S9">
-        <v>0.4749999999999999</v>
+        <v>32.86851443900241</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>23.11906448890412</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -2597,10 +2845,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -2609,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2627,28 +2875,28 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0.2975</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>0.27625</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0.2656250000000001</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>0.2125</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.159375</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>0.10625</v>
+        <v>32.20408582587422</v>
       </c>
       <c r="S10">
-        <v>0.05312499999999998</v>
+        <v>32.20408582587422</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>16.10220211819882</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -2659,58 +2907,58 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>64.11580297597997</v>
+        <v>266.71</v>
       </c>
       <c r="F11">
-        <v>105.0338090681663</v>
+        <v>177.5278</v>
       </c>
       <c r="G11">
-        <v>105.0338090681663</v>
+        <v>92.38500000000008</v>
       </c>
       <c r="H11">
-        <v>75.58049412564222</v>
+        <v>186.7415000000001</v>
       </c>
       <c r="I11">
-        <v>105.0338090681663</v>
+        <v>155.0399999999999</v>
       </c>
       <c r="J11">
-        <v>105.0338090681663</v>
+        <v>120.9635000000001</v>
       </c>
       <c r="K11">
-        <v>105.0338090681663</v>
+        <v>125.2479999999999</v>
       </c>
       <c r="L11">
-        <v>105.0338090681663</v>
+        <v>13.90799999999998</v>
       </c>
       <c r="M11">
-        <v>76.11761908726662</v>
+        <v>22.60999999999998</v>
       </c>
       <c r="N11">
-        <v>112.5727622950592</v>
+        <v>4.730999999999997</v>
       </c>
       <c r="O11">
-        <v>115.3422112689443</v>
+        <v>3.07166666666667</v>
       </c>
       <c r="P11">
-        <v>180.5343067405335</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>184.8933509631451</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>197.9987056287091</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>175.4181222285096</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>152.1962495517131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -2721,58 +2969,58 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E12">
-        <v>1.13617297926288</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>9.077082375110667</v>
+        <v>2.375</v>
       </c>
       <c r="G12">
-        <v>11.40630091273339</v>
+        <v>2.375</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>4.749999999999999</v>
       </c>
       <c r="I12">
-        <v>11.40630091273339</v>
+        <v>4.75</v>
       </c>
       <c r="J12">
-        <v>11.34297764113917</v>
+        <v>7.125</v>
       </c>
       <c r="K12">
-        <v>11.40630091273339</v>
+        <v>7.124999999999999</v>
       </c>
       <c r="L12">
-        <v>11.40630091273339</v>
+        <v>7.124999999999999</v>
       </c>
       <c r="M12">
-        <v>11.40630091273339</v>
+        <v>7.124999999999999</v>
       </c>
       <c r="N12">
-        <v>30.59214515555058</v>
+        <v>7.124999999999997</v>
       </c>
       <c r="O12">
-        <v>30.59214515555058</v>
+        <v>7.124999999999996</v>
       </c>
       <c r="P12">
-        <v>56.7648</v>
+        <v>1.9</v>
       </c>
       <c r="Q12">
-        <v>56.7648</v>
+        <v>1.425</v>
       </c>
       <c r="R12">
-        <v>52.84281303497725</v>
+        <v>0.9500000000000002</v>
       </c>
       <c r="S12">
-        <v>56.76479999999999</v>
+        <v>0.4749999999999999</v>
       </c>
       <c r="T12">
-        <v>56.76479999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -2783,55 +3031,55 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>341.2764000000001</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>335.6477400000001</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>341.4636</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="H13">
-        <v>249.3437267957759</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>176.8038935915518</v>
+        <v>0.1294208905299551</v>
       </c>
       <c r="J13">
-        <v>161.0313232182629</v>
+        <v>0.405</v>
       </c>
       <c r="K13">
-        <v>130.6168566505904</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>154.1912810319155</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>194.7191680822315</v>
+        <v>0.2975000000000001</v>
       </c>
       <c r="N13">
-        <v>102.3283609070353</v>
+        <v>0.27625</v>
       </c>
       <c r="O13">
-        <v>112.3929115593683</v>
+        <v>0.265625</v>
       </c>
       <c r="P13">
-        <v>81.36429036524567</v>
+        <v>0.2125</v>
       </c>
       <c r="Q13">
-        <v>74.46313246134164</v>
+        <v>0.159375</v>
       </c>
       <c r="R13">
-        <v>27.2</v>
+        <v>0.10625</v>
       </c>
       <c r="S13">
-        <v>13.6</v>
+        <v>0.05312499999999998</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -2845,58 +3093,58 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>72.32802628789788</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>56.0292097927943</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>105.0282647703012</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>65.58621572204257</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>105.0282647703012</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>105.0282647703012</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>105.0282647703011</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>105.0282647703012</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>76.11822117844432</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>132.9758336700601</v>
       </c>
       <c r="O14">
-        <v>4.6658379163785</v>
+        <v>132.9758336700601</v>
       </c>
       <c r="P14">
-        <v>3.769322158815291</v>
+        <v>214.9986899875992</v>
       </c>
       <c r="Q14">
-        <v>19.16146839225491</v>
+        <v>218.0116911099812</v>
       </c>
       <c r="R14">
-        <v>51.21648352964752</v>
+        <v>225.3915382780063</v>
       </c>
       <c r="S14">
-        <v>28.2993218257263</v>
+        <v>226.4438195255677</v>
       </c>
       <c r="T14">
-        <v>2.536203071047548</v>
+        <v>202.996334111434</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -2907,10 +3155,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2919,46 +3167,46 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>11.4056988215557</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>11.4056988215557</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>11.4056988215557</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>11.40569882155569</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>11.4056988215557</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>11.4056988215557</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>11.4056988215557</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>24.29287283429759</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>24.29287283429759</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>24.2928728342976</v>
       </c>
       <c r="R15">
-        <v>3.997562939903913</v>
+        <v>22.5303245337787</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>14.04498299352233</v>
       </c>
       <c r="T15">
-        <v>66.695244215085</v>
+        <v>11.76384322921119</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -2969,55 +3217,55 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>341.2764</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>434.8728</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>341.4636</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>262.539239707008</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>176.8040394140158</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>112.4059584919081</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>112.4732856446914</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>149.7383140432277</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>193.9617805235479</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>106.0658062231972</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>116.6292104219248</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>106.0344357859483</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>104.3628487501016</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="S16">
-        <v>2.5</v>
+        <v>13.6</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -3031,58 +3279,58 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E17">
-        <v>66.6288</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>63.29987999999999</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>65.58552</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>52.39781999999999</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>48.29382</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>53.91972</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>49.58316</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>36.60768</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>36.2178</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>30.51399999999999</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>27.01166666666666</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>9.500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>7.125</v>
+        <v>14.06806889656661</v>
       </c>
       <c r="R17">
-        <v>4.75</v>
+        <v>59.26144083700451</v>
       </c>
       <c r="S17">
-        <v>47.1857240207088</v>
+        <v>59.87843604488208</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>18.17601190730787</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -3093,58 +3341,58 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>198.37</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>202.914</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>218.9326798218816</v>
+        <v>13.77683883151423</v>
       </c>
       <c r="H18">
-        <v>210.2255</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>211.76298686065</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>200.526</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>196.4373620758995</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>203.0194694319493</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>218.9326798218816</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>215.9410000000001</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>202.7008333333333</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>135.625</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>134.75</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>133.875</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -3155,10 +3403,10 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3188,25 +3436,25 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>49.62889573056001</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>49.62889573056001</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>49.0845568381816</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>49.62889573056</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>46.3476520218646</v>
+        <v>2.810294672560148</v>
       </c>
       <c r="S19">
-        <v>47.41706729872284</v>
+        <v>0.3808218712862951</v>
       </c>
       <c r="T19">
-        <v>49.62889573056001</v>
+        <v>69.08056777162764</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -3217,10 +3465,10 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3250,25 +3498,25 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>16.203395098368</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>13.58200280945739</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>12.16022991299431</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>12.13366270594449</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>13.48791353468928</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>13.11200140741632</v>
+        <v>2.5</v>
       </c>
       <c r="T20">
-        <v>13.11200140741632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -3279,58 +3527,58 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>66.62880000000001</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>63.29987999999999</v>
       </c>
       <c r="G21">
-        <v>4.476119999999995</v>
+        <v>59.6232</v>
       </c>
       <c r="H21">
-        <v>20.81714</v>
+        <v>52.39782</v>
       </c>
       <c r="I21">
-        <v>27.32778</v>
+        <v>48.29382</v>
       </c>
       <c r="J21">
-        <v>29.16774</v>
+        <v>57.86981999999999</v>
       </c>
       <c r="K21">
-        <v>31.57226000000001</v>
+        <v>49.58316000000001</v>
       </c>
       <c r="L21">
-        <v>50.64114</v>
+        <v>36.60767999999998</v>
       </c>
       <c r="M21">
-        <v>102.1326599999999</v>
+        <v>36.2178</v>
       </c>
       <c r="N21">
-        <v>113.492669171072</v>
+        <v>30.514</v>
       </c>
       <c r="O21">
-        <v>122.483234793316</v>
+        <v>27.01166666666666</v>
       </c>
       <c r="P21">
-        <v>176.2552132488241</v>
+        <v>9.5</v>
       </c>
       <c r="Q21">
-        <v>180.1124415634955</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>196.4144344434462</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>210.0959312938609</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>222.2591028620236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -3341,55 +3589,55 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>1.7613</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>9.366239999999998</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>20.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>20.11000000000001</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>20.07</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>20.07</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>20.07999999999999</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>20.03999999999999</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>20.03999999999999</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>20.02</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>20.01</v>
+        <v>0</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>7.499999999999999</v>
+        <v>7.124999999999999</v>
       </c>
       <c r="R22">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="S22">
-        <v>2.5</v>
+        <v>2.375</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -3403,58 +3651,58 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>75.36902857327627</v>
+        <v>198.37</v>
       </c>
       <c r="F23">
-        <v>75.36902857327627</v>
+        <v>212.3028</v>
       </c>
       <c r="G23">
-        <v>94.32629110863863</v>
+        <v>221.29</v>
       </c>
       <c r="H23">
-        <v>94.32629110863859</v>
+        <v>221.2899999999999</v>
       </c>
       <c r="I23">
-        <v>94.32629110863863</v>
+        <v>221.2900000000001</v>
       </c>
       <c r="J23">
-        <v>93.5333948754249</v>
+        <v>221.2900000000002</v>
       </c>
       <c r="K23">
-        <v>94.09145757952476</v>
+        <v>205.4115272458197</v>
       </c>
       <c r="L23">
-        <v>94.32629110863861</v>
+        <v>212.505649514577</v>
       </c>
       <c r="M23">
-        <v>94.3262911086386</v>
+        <v>221.2899999999997</v>
       </c>
       <c r="N23">
-        <v>94.32629110863864</v>
+        <v>215.941</v>
       </c>
       <c r="O23">
-        <v>46.03106825001759</v>
+        <v>202.7008333333333</v>
       </c>
       <c r="P23">
-        <v>12</v>
+        <v>136.5</v>
       </c>
       <c r="Q23">
-        <v>12</v>
+        <v>135.625</v>
       </c>
       <c r="R23">
-        <v>12</v>
+        <v>134.75</v>
       </c>
       <c r="S23">
-        <v>12</v>
+        <v>133.875</v>
       </c>
       <c r="T23">
-        <v>12</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -3465,58 +3713,58 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E24">
-        <v>18.90897142672372</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>37.95330476005707</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>74.86870889136141</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>74.86870889136144</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>83.56120889136145</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>73.72360512457513</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>79.97704242047527</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>98.71370889136146</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>123.6773304425319</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>128.5721492325948</v>
+        <v>49.62017517679446</v>
       </c>
       <c r="O24">
-        <v>198.0339769112379</v>
+        <v>48.98144201845167</v>
       </c>
       <c r="P24">
-        <v>319.286153846154</v>
+        <v>49.62582992678401</v>
       </c>
       <c r="Q24">
-        <v>390.4646153846155</v>
+        <v>49.625829926784</v>
       </c>
       <c r="R24">
-        <v>461.643076923077</v>
+        <v>46.42550076672656</v>
       </c>
       <c r="S24">
-        <v>532.8215384615384</v>
+        <v>44.25394663631532</v>
       </c>
       <c r="T24">
-        <v>604</v>
+        <v>47.40821113674779</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -3527,58 +3775,368 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>15.58723706620975</v>
+      </c>
+      <c r="O25">
+        <v>13.90062091985343</v>
+      </c>
+      <c r="P25">
+        <v>13.58754800342453</v>
+      </c>
+      <c r="Q25">
+        <v>11.9891499065856</v>
+      </c>
+      <c r="R25">
+        <v>14.59881279911453</v>
+      </c>
+      <c r="S25">
+        <v>13.11099952131072</v>
+      </c>
+      <c r="T25">
+        <v>11.8298379703314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
         <v>29</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>4.980633600000002</v>
+      </c>
+      <c r="G26">
+        <v>20.2493808</v>
+      </c>
+      <c r="H26">
+        <v>36.659268</v>
+      </c>
+      <c r="I26">
+        <v>43.18877519999998</v>
+      </c>
+      <c r="J26">
+        <v>45.08760239999997</v>
+      </c>
+      <c r="K26">
+        <v>47.56098960000001</v>
+      </c>
+      <c r="L26">
+        <v>66.64873679999998</v>
+      </c>
+      <c r="M26">
+        <v>118.199124</v>
+      </c>
+      <c r="N26">
+        <v>130.4583477569958</v>
+      </c>
+      <c r="O26">
+        <v>139.2900383950282</v>
+      </c>
+      <c r="P26">
+        <v>174.2866220697915</v>
+      </c>
+      <c r="Q26">
+        <v>187.7600201666303</v>
+      </c>
+      <c r="R26">
+        <v>200.2256864341591</v>
+      </c>
+      <c r="S26">
+        <v>215.760053842374</v>
+      </c>
+      <c r="T26">
+        <v>225.7619508929208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27">
+        <v>1.761299999999999</v>
+      </c>
+      <c r="F27">
+        <v>4.385606399999999</v>
+      </c>
+      <c r="G27">
+        <v>4.3267392</v>
+      </c>
+      <c r="H27">
+        <v>4.267872000000001</v>
+      </c>
+      <c r="I27">
+        <v>4.209004799999998</v>
+      </c>
+      <c r="J27">
+        <v>4.1501376</v>
+      </c>
+      <c r="K27">
+        <v>4.091270399999999</v>
+      </c>
+      <c r="L27">
+        <v>4.0324032</v>
+      </c>
+      <c r="M27">
+        <v>3.973535999999999</v>
+      </c>
+      <c r="N27">
+        <v>3.679199999999999</v>
+      </c>
+      <c r="O27">
+        <v>3.532032</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28">
+        <v>75.36756595731134</v>
+      </c>
+      <c r="F28">
+        <v>75.36756595731134</v>
+      </c>
+      <c r="G28">
+        <v>79.14678398091911</v>
+      </c>
+      <c r="H28">
+        <v>79.1467839809191</v>
+      </c>
+      <c r="I28">
+        <v>79.1467839809191</v>
+      </c>
+      <c r="J28">
+        <v>79.1467839809191</v>
+      </c>
+      <c r="K28">
+        <v>78.43625203512701</v>
+      </c>
+      <c r="L28">
+        <v>94.29928398091911</v>
+      </c>
+      <c r="M28">
+        <v>94.2992839809191</v>
+      </c>
+      <c r="N28">
+        <v>94.29928398091909</v>
+      </c>
+      <c r="O28">
+        <v>87.44858121507005</v>
+      </c>
+      <c r="P28">
+        <v>68.59585</v>
+      </c>
+      <c r="Q28">
+        <v>68.59585</v>
+      </c>
+      <c r="R28">
+        <v>53.44335</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
         <v>32</v>
       </c>
-      <c r="E25">
-        <v>44.62722404475713</v>
-      </c>
-      <c r="F25">
-        <v>13.75510855672302</v>
-      </c>
-      <c r="G25">
-        <v>47.39949001910026</v>
-      </c>
-      <c r="H25">
-        <v>11.40270587435776</v>
-      </c>
-      <c r="I25">
-        <v>38.24829001910029</v>
-      </c>
-      <c r="J25">
-        <v>27.13721329069454</v>
-      </c>
-      <c r="K25">
-        <v>16.51329001910029</v>
-      </c>
-      <c r="L25">
-        <v>5.952690019100295</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>3.79069254939018</v>
-      </c>
-      <c r="O25">
-        <v>1.528643575505119</v>
-      </c>
-      <c r="P25">
-        <v>4.70089325946654</v>
-      </c>
-      <c r="Q25">
-        <v>14.09184903685494</v>
-      </c>
-      <c r="R25">
-        <v>18.65848133631355</v>
-      </c>
-      <c r="S25">
-        <v>51.06707777149017</v>
-      </c>
-      <c r="T25">
-        <v>88.03895044828677</v>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29">
+        <v>18.91043404268865</v>
+      </c>
+      <c r="F29">
+        <v>37.954767376022</v>
+      </c>
+      <c r="G29">
+        <v>90.0482160190809</v>
+      </c>
+      <c r="H29">
+        <v>90.0482160190809</v>
+      </c>
+      <c r="I29">
+        <v>98.74071601908091</v>
+      </c>
+      <c r="J29">
+        <v>98.74071601908086</v>
+      </c>
+      <c r="K29">
+        <v>95.63224796487297</v>
+      </c>
+      <c r="L29">
+        <v>98.74071601908089</v>
+      </c>
+      <c r="M29">
+        <v>131.3904261348254</v>
+      </c>
+      <c r="N29">
+        <v>133.8171234134158</v>
+      </c>
+      <c r="O29">
+        <v>156.0858240039852</v>
+      </c>
+      <c r="P29">
+        <v>262.6903038461538</v>
+      </c>
+      <c r="Q29">
+        <v>333.8687653846153</v>
+      </c>
+      <c r="R29">
+        <v>420.1997269230768</v>
+      </c>
+      <c r="S29">
+        <v>544.8215384615386</v>
+      </c>
+      <c r="T29">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30">
+        <v>37.5511737121021</v>
+      </c>
+      <c r="F30">
+        <v>38.08919020720569</v>
+      </c>
+      <c r="G30">
+        <v>47.40563640814317</v>
+      </c>
+      <c r="H30">
+        <v>21.39698427795743</v>
+      </c>
+      <c r="I30">
+        <v>38.25443640814321</v>
+      </c>
+      <c r="J30">
+        <v>27.08003640814319</v>
+      </c>
+      <c r="K30">
+        <v>16.51943640814314</v>
+      </c>
+      <c r="L30">
+        <v>5.95883640814314</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>2.574067508384238</v>
+      </c>
+      <c r="O30">
+        <v>0.5103424752242287</v>
+      </c>
+      <c r="P30">
+        <v>2.708437178103269</v>
+      </c>
+      <c r="Q30">
+        <v>13.44543605572133</v>
+      </c>
+      <c r="R30">
+        <v>21.57813718821487</v>
+      </c>
+      <c r="S30">
+        <v>42.76119748090997</v>
+      </c>
+      <c r="T30">
+        <v>82.2398226593549</v>
       </c>
     </row>
   </sheetData>
@@ -3588,7 +4146,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -3602,7 +4160,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1">
         <v>2007</v>
@@ -3664,55 +4222,55 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>6158.85</v>
+        <v>3911.441860465116</v>
       </c>
       <c r="F2">
-        <v>7294.099999999999</v>
+        <v>3911.441860465116</v>
       </c>
       <c r="G2">
-        <v>9564.599999999999</v>
+        <v>3911.441860465116</v>
       </c>
       <c r="H2">
-        <v>11519.7</v>
+        <v>3715.869767441859</v>
       </c>
       <c r="I2">
-        <v>13474.8</v>
+        <v>3520.297674418604</v>
       </c>
       <c r="J2">
-        <v>13580.25</v>
+        <v>3324.725581395348</v>
       </c>
       <c r="K2">
-        <v>13685.7</v>
+        <v>3129.153488372092</v>
       </c>
       <c r="L2">
-        <v>17350.8</v>
+        <v>2933.581395348837</v>
       </c>
       <c r="M2">
-        <v>16254.97500000001</v>
+        <v>2738.009302325582</v>
       </c>
       <c r="N2">
-        <v>15159.15</v>
+        <v>2542.437209302326</v>
       </c>
       <c r="O2">
-        <v>15601.37500000001</v>
+        <v>2444.651162790698</v>
       </c>
       <c r="P2">
-        <v>17812.5</v>
+        <v>1955.720930232558</v>
       </c>
       <c r="Q2">
-        <v>18307.29166666668</v>
+        <v>1466.790697674419</v>
       </c>
       <c r="R2">
-        <v>18802.08333333334</v>
+        <v>977.8604651162793</v>
       </c>
       <c r="S2">
-        <v>40394.75000000003</v>
+        <v>488.9302325581395</v>
       </c>
       <c r="T2">
-        <v>45833.33333333335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -3726,55 +4284,55 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>82.11799999999999</v>
+        <v>52.15255813953488</v>
       </c>
       <c r="F3">
-        <v>97.25466666666665</v>
+        <v>52.15255813953488</v>
       </c>
       <c r="G3">
-        <v>127.528</v>
+        <v>52.15255813953488</v>
       </c>
       <c r="H3">
-        <v>153.5959999999999</v>
+        <v>49.54493023255813</v>
       </c>
       <c r="I3">
-        <v>179.6639999999999</v>
+        <v>46.93730232558138</v>
       </c>
       <c r="J3">
-        <v>181.0699999999999</v>
+        <v>44.32967441860464</v>
       </c>
       <c r="K3">
-        <v>182.4759999999999</v>
+        <v>41.72204651162789</v>
       </c>
       <c r="L3">
-        <v>231.344</v>
+        <v>39.11441860465115</v>
       </c>
       <c r="M3">
-        <v>216.7330000000001</v>
+        <v>36.50679069767443</v>
       </c>
       <c r="N3">
-        <v>202.122</v>
+        <v>33.89916279069768</v>
       </c>
       <c r="O3">
-        <v>208.0183333333334</v>
+        <v>32.5953488372093</v>
       </c>
       <c r="P3">
-        <v>237.4999999999999</v>
+        <v>26.07627906976744</v>
       </c>
       <c r="Q3">
-        <v>244.0972222222223</v>
+        <v>19.55720930232558</v>
       </c>
       <c r="R3">
-        <v>250.6944444444446</v>
+        <v>13.03813953488372</v>
       </c>
       <c r="S3">
-        <v>538.5966666666669</v>
+        <v>6.519069767441859</v>
       </c>
       <c r="T3">
-        <v>611.1111111111112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -3785,10 +4343,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3800,43 +4358,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1978359072768</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.3956718145536</v>
+        <v>1641.410391120507</v>
       </c>
       <c r="J4">
-        <v>0.5935077218304001</v>
+        <v>2624.729841437635</v>
       </c>
       <c r="K4">
-        <v>0.7913436291072001</v>
+        <v>3983.852283298094</v>
       </c>
       <c r="L4">
-        <v>0.9031361813760002</v>
+        <v>7436.883751536159</v>
       </c>
       <c r="M4">
-        <v>1.0837634176512</v>
+        <v>6981.943674737231</v>
       </c>
       <c r="N4">
-        <v>1.2643906539264</v>
+        <v>6522.730744549133</v>
       </c>
       <c r="O4">
-        <v>1.354704272064</v>
+        <v>7187.083120536255</v>
       </c>
       <c r="P4">
-        <v>0.8384456907840002</v>
+        <v>10710.88250493541</v>
       </c>
       <c r="Q4">
-        <v>0.8384456907840002</v>
+        <v>12531.37002521546</v>
       </c>
       <c r="R4">
-        <v>0.9270702638412802</v>
+        <v>14028.93554282017</v>
       </c>
       <c r="S4">
-        <v>0.8685607617856002</v>
+        <v>15827.05726744186</v>
       </c>
       <c r="T4">
-        <v>0.88587692761152</v>
+        <v>17812.5</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3847,10 +4405,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3862,43 +4420,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>85.37380306329601</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>170.747606126592</v>
+        <v>21.88547188160676</v>
       </c>
       <c r="J5">
-        <v>256.121409189888</v>
+        <v>34.99639788583513</v>
       </c>
       <c r="K5">
-        <v>341.495212253184</v>
+        <v>53.1180304439746</v>
       </c>
       <c r="L5">
-        <v>389.73799827072</v>
+        <v>99.15845002048214</v>
       </c>
       <c r="M5">
-        <v>467.6855979248641</v>
+        <v>93.09258232982975</v>
       </c>
       <c r="N5">
-        <v>545.6331975790081</v>
+        <v>86.96974326065511</v>
       </c>
       <c r="O5">
-        <v>584.6069974060802</v>
+        <v>95.82777494048339</v>
       </c>
       <c r="P5">
-        <v>361.82156348448</v>
+        <v>142.8117667324721</v>
       </c>
       <c r="Q5">
-        <v>361.8215634844801</v>
+        <v>167.0849336695395</v>
       </c>
       <c r="R5">
-        <v>400.0664753961216</v>
+        <v>187.052473904269</v>
       </c>
       <c r="S5">
-        <v>374.8173748936321</v>
+        <v>211.0274302325581</v>
       </c>
       <c r="T5">
-        <v>382.2899664538944</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -3912,55 +4470,55 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>311.1795885509839</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>468.3680500894451</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>782.7449731663684</v>
       </c>
       <c r="H6">
-        <v>0.8217799225344001</v>
+        <v>1167.34572450805</v>
       </c>
       <c r="I6">
-        <v>1.6435598450688</v>
+        <v>1167.34572450805</v>
       </c>
       <c r="J6">
-        <v>2.465339767603201</v>
+        <v>1150.866547406082</v>
       </c>
       <c r="K6">
-        <v>3.287119690137601</v>
+        <v>1083.168515205724</v>
       </c>
       <c r="L6">
-        <v>3.751488753408001</v>
+        <v>1015.470483005367</v>
       </c>
       <c r="M6">
-        <v>4.5017865040896</v>
+        <v>947.7724508050087</v>
       </c>
       <c r="N6">
-        <v>5.252084254771201</v>
+        <v>880.0744186046511</v>
       </c>
       <c r="O6">
-        <v>5.627233130112</v>
+        <v>846.2254025044722</v>
       </c>
       <c r="P6">
-        <v>3.482774407872</v>
+        <v>676.9803220035777</v>
       </c>
       <c r="Q6">
-        <v>3.482774407872</v>
+        <v>507.7352415026835</v>
       </c>
       <c r="R6">
-        <v>3.850907249802241</v>
+        <v>338.490161001789</v>
       </c>
       <c r="S6">
-        <v>3.6078677797248</v>
+        <v>169.2450805008945</v>
       </c>
       <c r="T6">
-        <v>3.679796468540161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -3971,58 +4529,58 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>41.49061180679784</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>62.44907334525934</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>104.3659964221824</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>155.6460966010733</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>155.6460966010734</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>153.4488729874776</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>144.4224686940966</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>135.3960644007155</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>126.3696601073345</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>117.3432558139535</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>112.8300536672629</v>
       </c>
       <c r="P7">
-        <v>6.123350229259426</v>
+        <v>90.26404293381036</v>
       </c>
       <c r="Q7">
-        <v>6.430598097408</v>
+        <v>67.6980322003578</v>
       </c>
       <c r="R7">
-        <v>6.430598097407999</v>
+        <v>45.13202146690521</v>
       </c>
       <c r="S7">
-        <v>5.677786028570702</v>
+        <v>22.5660107334526</v>
       </c>
       <c r="T7">
-        <v>3.546428562431999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -4036,7 +4594,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4048,43 +4606,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.1978253756544</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.3956507513088</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.5934761269632002</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.7913015026176001</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>0.8908225689570139</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.0837002279168</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.2643169325696</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.354625284896</v>
       </c>
       <c r="P8">
-        <v>2642.461137395799</v>
+        <v>0.8383682523840003</v>
       </c>
       <c r="Q8">
-        <v>2775.050409727606</v>
+        <v>0.8383682523840001</v>
       </c>
       <c r="R8">
-        <v>2775.050409727606</v>
+        <v>0.8659019607846401</v>
       </c>
       <c r="S8">
-        <v>2450.183047713972</v>
+        <v>0.8763004003590501</v>
       </c>
       <c r="T8">
-        <v>1530.420325787963</v>
+        <v>0.8820349298092802</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -4098,7 +4656,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4110,43 +4668,43 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>85.36925826316801</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>170.738516526336</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>256.107774789504</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>341.477033052672</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>384.4242009114499</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>467.6583291240961</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>545.601383978112</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>584.5729114051201</v>
       </c>
       <c r="P9">
-        <v>25.43545479846224</v>
+        <v>361.7881458364801</v>
       </c>
       <c r="Q9">
-        <v>26.71171517384862</v>
+        <v>361.7881458364801</v>
       </c>
       <c r="R9">
-        <v>26.71171517384862</v>
+        <v>373.6700000001408</v>
       </c>
       <c r="S9">
-        <v>23.58464965713985</v>
+        <v>378.1573266164824</v>
       </c>
       <c r="T9">
-        <v>14.73131864394831</v>
+        <v>380.6319966330816</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -4157,10 +4715,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4172,43 +4730,43 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.8217361757952001</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1.6434723515904</v>
       </c>
       <c r="J10">
-        <v>0.9226800717531428</v>
+        <v>2.465208527385601</v>
       </c>
       <c r="K10">
-        <v>1.845360143506286</v>
+        <v>3.286944703180801</v>
       </c>
       <c r="L10">
-        <v>2.032287706347068</v>
+        <v>3.700339901821443</v>
       </c>
       <c r="M10">
-        <v>2.498087788029893</v>
+        <v>4.501524023654401</v>
       </c>
       <c r="N10">
-        <v>2.316436633056</v>
+        <v>5.2517780275968</v>
       </c>
       <c r="O10">
-        <v>2.48189639256</v>
+        <v>5.626905029568</v>
       </c>
       <c r="P10">
-        <v>1.955198984811429</v>
+        <v>3.482452740672001</v>
       </c>
       <c r="Q10">
-        <v>1.955198984811429</v>
+        <v>3.482452740672</v>
       </c>
       <c r="R10">
-        <v>1.955198984811429</v>
+        <v>3.59682352941312</v>
       </c>
       <c r="S10">
-        <v>1.983289513224686</v>
+        <v>3.640017047645284</v>
       </c>
       <c r="T10">
-        <v>1.946909319259873</v>
+        <v>3.66383740074624</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -4222,7 +4780,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4240,37 +4798,37 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>398.1719386565486</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>796.3438773130973</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>877.0103102005423</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>1078.020960834438</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>999.6315008803201</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1071.0337509432</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>843.7435619070857</v>
+        <v>6.093603181551871</v>
       </c>
       <c r="Q11">
-        <v>843.7435619070858</v>
+        <v>6.430143979007999</v>
       </c>
       <c r="R11">
-        <v>843.7435619070858</v>
+        <v>6.430143979007999</v>
       </c>
       <c r="S11">
-        <v>855.8657053223451</v>
+        <v>5.723918141914843</v>
       </c>
       <c r="T11">
-        <v>840.166252388299</v>
+        <v>3.50776685549102</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -4284,7 +4842,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4302,37 +4860,37 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>3.832671067282286</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>7.665342134564573</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>8.44181047251859</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>10.37667235027802</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>9.622121398848002</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>10.30941578448</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>8.121595783062858</v>
+        <v>2629.624142192768</v>
       </c>
       <c r="Q12">
-        <v>8.121595783062858</v>
+        <v>2774.854440171914</v>
       </c>
       <c r="R12">
-        <v>8.121595783062858</v>
+        <v>2774.854440171914</v>
       </c>
       <c r="S12">
-        <v>8.238279516471772</v>
+        <v>2470.09082893402</v>
       </c>
       <c r="T12">
-        <v>8.087161787694857</v>
+        <v>1513.736312254201</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -4343,10 +4901,10 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4364,37 +4922,37 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>7.751441131144821</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>8.145138516469228</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>10.48456476453151</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>12.22216193989758</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>9.057587954323601</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>8.847773141070642</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>7.571427526421944</v>
+        <v>25.31189013875392</v>
       </c>
       <c r="Q13">
-        <v>7.79335222804057</v>
+        <v>26.70982883587938</v>
       </c>
       <c r="R13">
-        <v>7.928994681250924</v>
+        <v>26.70982883587939</v>
       </c>
       <c r="S13">
-        <v>8.037076684124834</v>
+        <v>23.7762753587232</v>
       </c>
       <c r="T13">
-        <v>7.277030904909006</v>
+        <v>14.57072386127039</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -4408,7 +4966,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4426,37 +4984,37 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>3345.044980440188</v>
+        <v>0.9226309536822856</v>
       </c>
       <c r="K14">
-        <v>3514.940544414798</v>
+        <v>1.845261907364572</v>
       </c>
       <c r="L14">
-        <v>4524.492948386291</v>
+        <v>2.005606405028571</v>
       </c>
       <c r="M14">
-        <v>5274.33296021734</v>
+        <v>2.495416016154228</v>
       </c>
       <c r="N14">
-        <v>3908.697571058107</v>
+        <v>2.316264719808</v>
       </c>
       <c r="O14">
-        <v>3818.154409338946</v>
+        <v>2.481712199794286</v>
       </c>
       <c r="P14">
-        <v>3267.362186402085</v>
+        <v>1.955018403668572</v>
       </c>
       <c r="Q14">
-        <v>3363.13123071597</v>
+        <v>1.955018403668572</v>
       </c>
       <c r="R14">
-        <v>3421.666166293668</v>
+        <v>1.955018403668571</v>
       </c>
       <c r="S14">
-        <v>3468.307707533871</v>
+        <v>2.039289411048685</v>
       </c>
       <c r="T14">
-        <v>3140.318721272271</v>
+        <v>1.927834043178703</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -4470,7 +5028,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4488,37 +5046,37 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>32.1982939293708</v>
+        <v>398.1507423198172</v>
       </c>
       <c r="K15">
-        <v>33.83365229917987</v>
+        <v>796.3014846396345</v>
       </c>
       <c r="L15">
-        <v>43.55126902190013</v>
+        <v>865.4963024777144</v>
       </c>
       <c r="M15">
-        <v>50.7689803657284</v>
+        <v>1076.867988509632</v>
       </c>
       <c r="N15">
-        <v>37.62382688719035</v>
+        <v>999.5573137017601</v>
       </c>
       <c r="O15">
-        <v>36.75228843213959</v>
+        <v>1070.954264680457</v>
       </c>
       <c r="P15">
-        <v>31.4505451097527</v>
+        <v>843.6656341985145</v>
       </c>
       <c r="Q15">
-        <v>32.37238617801468</v>
+        <v>843.6656341985145</v>
       </c>
       <c r="R15">
-        <v>32.93582406058076</v>
+        <v>843.6656341985145</v>
       </c>
       <c r="S15">
-        <v>33.38478007251854</v>
+        <v>880.0318150756252</v>
       </c>
       <c r="T15">
-        <v>30.22766683577587</v>
+        <v>831.9345370948095</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -4529,10 +5087,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4550,37 +5108,37 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>3.832467038372571</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>7.664934076745144</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>8.330980451657144</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>10.36557422094833</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>9.621407297664</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>10.30865067606857</v>
       </c>
       <c r="P16">
-        <v>5.986600343579859</v>
+        <v>8.120845676777144</v>
       </c>
       <c r="Q16">
-        <v>5.986600343579859</v>
+        <v>8.120845676777144</v>
       </c>
       <c r="R16">
-        <v>8.616163254768972</v>
+        <v>8.120845676777146</v>
       </c>
       <c r="S16">
-        <v>8.428238108857926</v>
+        <v>8.470894476663771</v>
       </c>
       <c r="T16">
-        <v>6.00670837036451</v>
+        <v>8.007926025511534</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -4594,7 +5152,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4612,37 +5170,37 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>11.32223129584008</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>11.09295948627192</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>11.27042800295305</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>12.37324915605593</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>8.944894848879834</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>8.770577400429302</v>
       </c>
       <c r="P17">
-        <v>2583.448302114078</v>
+        <v>7.866675404639901</v>
       </c>
       <c r="Q17">
-        <v>2583.448302114078</v>
+        <v>7.903719877050682</v>
       </c>
       <c r="R17">
-        <v>3718.205835327225</v>
+        <v>8.150086327859128</v>
       </c>
       <c r="S17">
-        <v>3637.108906976382</v>
+        <v>8.847515703148753</v>
       </c>
       <c r="T17">
-        <v>2592.125689057299</v>
+        <v>6.996653288665027</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -4656,7 +5214,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4674,37 +5232,37 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>4885.978274589448</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>4787.038670614266</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>4863.623161274355</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>5339.532905036442</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3860.066161708913</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3784.84147818526</v>
       </c>
       <c r="P18">
-        <v>24.86741681179326</v>
+        <v>3394.773001540757</v>
       </c>
       <c r="Q18">
-        <v>24.86741681179326</v>
+        <v>3410.75911617341</v>
       </c>
       <c r="R18">
-        <v>35.79021659673266</v>
+        <v>3517.075715329977</v>
       </c>
       <c r="S18">
-        <v>35.00960445217908</v>
+        <v>3818.043314974193</v>
       </c>
       <c r="T18">
-        <v>24.95094246151412</v>
+        <v>3019.324996108524</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -4715,58 +5273,58 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>851.9902777777777</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>656.2634722222226</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>294.5080709639485</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>596.5353472222223</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>495.2666666666668</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>386.4111805555557</v>
+        <v>47.03080692118187</v>
       </c>
       <c r="K19">
-        <v>400.097777777778</v>
+        <v>46.07844709682182</v>
       </c>
       <c r="L19">
-        <v>44.42833333333332</v>
+        <v>46.81562401226652</v>
       </c>
       <c r="M19">
-        <v>72.22638888888886</v>
+        <v>51.39657341746309</v>
       </c>
       <c r="N19">
-        <v>15.11291666666668</v>
+        <v>37.15571706457777</v>
       </c>
       <c r="O19">
-        <v>9.812268518518525</v>
+        <v>36.43162920178326</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>32.67695937311959</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>32.83083641236437</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>33.85420474649177</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>36.75121907461791</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>29.06302135291627</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -4780,55 +5338,55 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E20">
-        <v>74945.51000000002</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>57728.35900000007</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>25906.46648583741</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>52474.36150000001</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>43566.24000000001</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>33990.74350000002</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>35194.68800000002</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>3908.147999999999</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>6353.409999999997</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>1329.411000000001</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>863.138333333334</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.832204701414286</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.832204701414286</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>5.099586609327721</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>5.099586609327722</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.577945679091131</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -4842,55 +5400,55 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E21">
-        <v>1415.044722222222</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>1089.968027777779</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>489.1394917749057</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>990.767402777778</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>822.5733333333336</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>641.7785694444448</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>664.5102222222226</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>73.78966666666665</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>119.9586111111111</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>25.10058333333335</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>16.29689814814816</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1653.74372114878</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1653.74372114878</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2200.667759871424</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2200.667759871424</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1544.021173823173</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -4901,58 +5459,58 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>6.50297619047619</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>6.502976190476191</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>13.00595238095238</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>13.00595238095238</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>19.50892857142857</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>19.50892857142857</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>19.50892857142858</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>19.50892857142857</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>19.50892857142858</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>19.50892857142857</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>5.202380952380953</v>
+        <v>15.91838875972088</v>
       </c>
       <c r="Q22">
-        <v>3.901785714285714</v>
+        <v>15.91838875972088</v>
       </c>
       <c r="R22">
-        <v>2.601190476190477</v>
+        <v>21.18289822336131</v>
       </c>
       <c r="S22">
-        <v>1.300595238095238</v>
+        <v>21.1828982233613</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>14.86223589776316</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -4966,55 +5524,55 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>572.0357142857141</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>572.0357142857141</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>1144.071428571428</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>1144.071428571428</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>1716.107142857143</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>1716.107142857143</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>1716.107142857143</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>1716.107142857143</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>1716.107142857143</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>1716.107142857143</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>457.6285714285714</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>343.2214285714285</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>228.8142857142858</v>
+        <v>6.2485539662144</v>
       </c>
       <c r="S23">
-        <v>114.4071428571429</v>
+        <v>6.2485539662144</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.124307873680368</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -5028,55 +5586,55 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>10.80059523809524</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>10.80059523809523</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>21.60119047619047</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>21.60119047619047</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>32.4017857142857</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>32.40178571428571</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>32.40178571428571</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>32.40178571428571</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>32.40178571428571</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>32.40178571428571</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>8.640476190476189</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>6.480357142857142</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>4.320238095238096</v>
+        <v>2696.491365420214</v>
       </c>
       <c r="S24">
-        <v>2.160119047619047</v>
+        <v>2696.491365420214</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1348.259013180528</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -5087,58 +5645,58 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E25">
-        <v>80.66533090909091</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>79.3349203636364</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>80.70957818181817</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>58.93578996991064</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>41.7900112125486</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>38.0619491243167</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>30.87307520832137</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>36.44521188027093</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>46.02453063761835</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>24.18670348711744</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>26.56559727766887</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>19.23155954087625</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>17.60037676358984</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>6.42909090909091</v>
+        <v>25.95553185965981</v>
       </c>
       <c r="S25">
-        <v>3.214545454545454</v>
+        <v>25.95553185965981</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>12.97789424451845</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -5149,55 +5707,55 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E26">
-        <v>34810.1928</v>
+        <v>851.9902777777778</v>
       </c>
       <c r="F26">
-        <v>34236.06948000001</v>
+        <v>567.1026944444445</v>
       </c>
       <c r="G26">
-        <v>34829.28719999999</v>
+        <v>295.1187500000003</v>
       </c>
       <c r="H26">
-        <v>25433.06013316914</v>
+        <v>596.5353472222224</v>
       </c>
       <c r="I26">
-        <v>18033.99714633828</v>
+        <v>495.2666666666664</v>
       </c>
       <c r="J26">
-        <v>16425.19496826282</v>
+        <v>386.4111805555558</v>
       </c>
       <c r="K26">
-        <v>13322.91937836022</v>
+        <v>400.0977777777774</v>
       </c>
       <c r="L26">
-        <v>15727.51066525538</v>
+        <v>44.42833333333327</v>
       </c>
       <c r="M26">
-        <v>19861.35514438761</v>
+        <v>72.22638888888881</v>
       </c>
       <c r="N26">
-        <v>10437.4928125176</v>
+        <v>15.11291666666666</v>
       </c>
       <c r="O26">
-        <v>11464.07697905557</v>
+        <v>9.812268518518531</v>
       </c>
       <c r="P26">
-        <v>8299.157617255058</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>7595.239511056849</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2774.4</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1387.2</v>
+        <v>0</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -5211,55 +5769,55 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E27">
-        <v>335.0713745454546</v>
+        <v>74945.51000000001</v>
       </c>
       <c r="F27">
-        <v>329.5450538181819</v>
+        <v>49885.31180000001</v>
       </c>
       <c r="G27">
-        <v>335.2551709090909</v>
+        <v>25960.18500000002</v>
       </c>
       <c r="H27">
-        <v>244.8102044903981</v>
+        <v>52474.36150000001</v>
       </c>
       <c r="I27">
-        <v>173.5892773444326</v>
+        <v>43566.23999999996</v>
       </c>
       <c r="J27">
-        <v>158.1034809779309</v>
+        <v>33990.74350000003</v>
       </c>
       <c r="K27">
-        <v>128.2420047114888</v>
+        <v>35194.68799999997</v>
       </c>
       <c r="L27">
-        <v>151.3878031949716</v>
+        <v>3908.147999999994</v>
       </c>
       <c r="M27">
-        <v>191.1788195716454</v>
+        <v>6353.409999999993</v>
       </c>
       <c r="N27">
-        <v>100.4678452541801</v>
+        <v>1329.410999999999</v>
       </c>
       <c r="O27">
-        <v>110.3494040764707</v>
+        <v>863.1383333333347</v>
       </c>
       <c r="P27">
-        <v>79.88493963133212</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>73.10925732568089</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>26.70545454545454</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>13.35272727272727</v>
+        <v>0</v>
       </c>
       <c r="T27">
         <v>0</v>
@@ -5273,58 +5831,58 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1415.044722222222</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>941.8836055555555</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>490.1537500000004</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>990.7674027777782</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>822.5733333333327</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>641.7785694444451</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>664.5102222222216</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>73.78966666666653</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>119.958611111111</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>25.10058333333332</v>
       </c>
       <c r="O28">
-        <v>1.080511756141994</v>
+        <v>16.29689814814817</v>
       </c>
       <c r="P28">
-        <v>0.872897211236099</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>4.359059843780464</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>11.53411946174977</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>6.337488091893917</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>0.58733228272047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -5335,58 +5893,58 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>6.50297619047619</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>6.502976190476191</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>13.00595238095238</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>13.00595238095238</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="O29">
-        <v>466.2823809197375</v>
+        <v>19.50892857142857</v>
       </c>
       <c r="P29">
-        <v>376.6887196180396</v>
+        <v>5.202380952380952</v>
       </c>
       <c r="Q29">
-        <v>1881.101978739108</v>
+        <v>3.901785714285713</v>
       </c>
       <c r="R29">
-        <v>4977.416167724323</v>
+        <v>2.601190476190477</v>
       </c>
       <c r="S29">
-        <v>2734.869861194221</v>
+        <v>1.300595238095238</v>
       </c>
       <c r="T29">
-        <v>253.4564696970644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -5397,58 +5955,58 @@
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>572.0357142857143</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>572.0357142857143</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1144.071428571428</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1144.071428571428</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1716.107142857142</v>
       </c>
       <c r="O30">
-        <v>4.488279602435977</v>
+        <v>1716.107142857142</v>
       </c>
       <c r="P30">
-        <v>3.625880723596104</v>
+        <v>457.6285714285714</v>
       </c>
       <c r="Q30">
-        <v>18.1068639664727</v>
+        <v>343.2214285714286</v>
       </c>
       <c r="R30">
-        <v>47.91095776419135</v>
+        <v>228.8142857142858</v>
       </c>
       <c r="S30">
-        <v>26.32495053555935</v>
+        <v>114.4071428571428</v>
       </c>
       <c r="T30">
-        <v>2.439687943608107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -5459,58 +6017,58 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>10.80059523809524</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>10.80059523809524</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>21.60119047619047</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>21.60119047619047</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>32.40178571428572</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>8.640476190476189</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>6.480357142857143</v>
       </c>
       <c r="R31">
-        <v>1.469113435601052</v>
+        <v>4.320238095238096</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2.160119047619047</v>
       </c>
       <c r="T31">
-        <v>23.91867806584329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -5524,55 +6082,55 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>80.66533090909091</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>102.7881163636363</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>80.70957818181819</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>62.0547293852928</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>41.79004567967649</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>26.56868109808735</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>26.58459478874525</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>35.39269241021745</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>45.84551176011134</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>25.07009965275569</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>27.56690428154585</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>25.06268482213323</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>24.66758243184219</v>
       </c>
       <c r="R32">
-        <v>633.9789518247616</v>
+        <v>6.429090909090908</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>3.214545454545454</v>
       </c>
       <c r="T32">
-        <v>10321.82953456776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -5586,55 +6144,55 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>34810.1928</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>44357.0256</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>34829.28720000001</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>26779.00245011482</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>18034.01202022962</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>11465.40776617462</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>11472.27513575853</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>15273.30803240922</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>19784.10161340189</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>10818.71223476611</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>11896.17946303633</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>10815.51245016673</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>10645.01057251036</v>
       </c>
       <c r="R33">
-        <v>6.102471194035139</v>
+        <v>2774.4</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1387.2</v>
       </c>
       <c r="T33">
-        <v>99.35450888888754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -5645,55 +6203,55 @@
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>335.0713745454545</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>426.966021818182</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>335.2551709090909</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>257.7657989850624</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>173.5894205155792</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>110.3622137920552</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>110.428316814788</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>147.0157992424417</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>190.4352026958471</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>104.137337019139</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>114.5086793233443</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>104.1065369534765</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>102.4653424091906</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>26.70545454545454</v>
       </c>
       <c r="S34">
-        <v>0.7738095238095238</v>
+        <v>13.35272727272727</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -5710,7 +6268,7 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5749,16 +6307,16 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.186272749457279</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>13.30329217972297</v>
       </c>
       <c r="S35">
-        <v>333.9285714285714</v>
+        <v>13.44146509449314</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>4.070424716537508</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -5772,7 +6330,7 @@
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5811,16 +6369,16 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1374.999240342718</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>5740.882240634295</v>
       </c>
       <c r="S36">
-        <v>3.214285714285714</v>
+        <v>5800.5091677005</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>1756.544819982725</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -5831,58 +6389,58 @@
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E37">
-        <v>134.92332</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>128.182257</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>132.810678</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>106.1055855</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>97.7949855</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>109.187433</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>100.405899</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>74.13055199999998</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>73.34104500000001</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>61.79084999999999</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>54.698625</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>19.2375</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>14.428125</v>
+        <v>13.23528680543793</v>
       </c>
       <c r="R37">
-        <v>9.61875</v>
+        <v>55.25982905423386</v>
       </c>
       <c r="S37">
-        <v>95.55109114193532</v>
+        <v>55.83377808481767</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>16.90791805330965</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -5896,52 +6454,52 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E38">
-        <v>13250.8026</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>12588.763635</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>13043.32029</v>
+        <v>3.810614995950744</v>
       </c>
       <c r="H38">
-        <v>10420.6164525</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>9604.433452499998</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>10723.284315</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>9860.850945</v>
+        <v>0</v>
       </c>
       <c r="L38">
-        <v>7280.352359999998</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>7202.814974999998</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>6068.471749999998</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>5371.945208333332</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>1889.3125</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1416.984375</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>944.65625</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>9384.060864618459</v>
+        <v>0</v>
       </c>
       <c r="T38">
         <v>0</v>
@@ -5958,54 +6516,860 @@
         <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E39">
-        <v>529.6989599999999</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>503.2340459999999</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>521.404884</v>
+        <v>1644.426932867975</v>
       </c>
       <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>15.82870844471847</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>1.032789657979821</v>
+      </c>
+      <c r="S41">
+        <v>0.1387567216912674</v>
+      </c>
+      <c r="T41">
+        <v>24.77511423223991</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="A42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>445.688460097446</v>
+      </c>
+      <c r="S42">
+        <v>59.87886220677002</v>
+      </c>
+      <c r="T42">
+        <v>10691.41468022045</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>4.290049348531567</v>
+      </c>
+      <c r="S43">
+        <v>0.5763740747175724</v>
+      </c>
+      <c r="T43">
+        <v>102.9120129646889</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0.7738095238095238</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="A45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>333.9285714285714</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>3.214285714285714</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="A47" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47">
+        <v>134.92332</v>
+      </c>
+      <c r="F47">
+        <v>128.182257</v>
+      </c>
+      <c r="G47">
+        <v>120.73698</v>
+      </c>
+      <c r="H47">
+        <v>106.1055855</v>
+      </c>
+      <c r="I47">
+        <v>97.79498549999997</v>
+      </c>
+      <c r="J47">
+        <v>117.1863855</v>
+      </c>
+      <c r="K47">
+        <v>100.405899</v>
+      </c>
+      <c r="L47">
+        <v>74.13055199999999</v>
+      </c>
+      <c r="M47">
+        <v>73.34104500000001</v>
+      </c>
+      <c r="N47">
+        <v>61.79084999999999</v>
+      </c>
+      <c r="O47">
+        <v>54.69862499999999</v>
+      </c>
+      <c r="P47">
+        <v>19.2375</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
+      <c r="A48" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48">
+        <v>13250.8026</v>
+      </c>
+      <c r="F48">
+        <v>12588.763635</v>
+      </c>
+      <c r="G48">
+        <v>11857.5639</v>
+      </c>
+      <c r="H48">
+        <v>10420.61645249999</v>
+      </c>
+      <c r="I48">
+        <v>9604.433452499998</v>
+      </c>
+      <c r="J48">
+        <v>11508.8604525</v>
+      </c>
+      <c r="K48">
+        <v>9860.850945000002</v>
+      </c>
+      <c r="L48">
+        <v>7280.352359999997</v>
+      </c>
+      <c r="M48">
+        <v>7202.814975</v>
+      </c>
+      <c r="N48">
+        <v>6068.471749999999</v>
+      </c>
+      <c r="O48">
+        <v>5371.945208333332</v>
+      </c>
+      <c r="P48">
+        <v>1889.3125</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="A49" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49">
+        <v>529.6989599999998</v>
+      </c>
+      <c r="F49">
+        <v>503.234046</v>
+      </c>
+      <c r="G49">
+        <v>474.00444</v>
+      </c>
+      <c r="H49">
         <v>416.562669</v>
       </c>
-      <c r="I39">
+      <c r="I49">
         <v>383.935869</v>
       </c>
-      <c r="J39">
-        <v>428.661774</v>
-      </c>
-      <c r="K39">
-        <v>394.186122</v>
-      </c>
-      <c r="L39">
+      <c r="J49">
+        <v>460.0650689999999</v>
+      </c>
+      <c r="K49">
+        <v>394.1861220000001</v>
+      </c>
+      <c r="L49">
         <v>291.031056</v>
       </c>
-      <c r="M39">
-        <v>287.9315100000001</v>
-      </c>
-      <c r="N39">
+      <c r="M49">
+        <v>287.93151</v>
+      </c>
+      <c r="N49">
         <v>242.5863</v>
       </c>
-      <c r="O39">
-        <v>214.7427499999999</v>
-      </c>
-      <c r="P39">
+      <c r="O49">
+        <v>214.74275</v>
+      </c>
+      <c r="P49">
         <v>75.52500000000001</v>
       </c>
-      <c r="Q39">
-        <v>56.64375000000001</v>
-      </c>
-      <c r="R39">
-        <v>37.7625</v>
-      </c>
-      <c r="S39">
-        <v>375.1265059646349</v>
-      </c>
-      <c r="T39">
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="A50" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>13.57402880549683</v>
+      </c>
+      <c r="R50">
+        <v>9.049352536997885</v>
+      </c>
+      <c r="S50">
+        <v>4.524676268498942</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="A51" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>1333.103693181818</v>
+      </c>
+      <c r="R51">
+        <v>888.7357954545452</v>
+      </c>
+      <c r="S51">
+        <v>444.3678977272726</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>53.29063160676532</v>
+      </c>
+      <c r="R52">
+        <v>35.52708773784354</v>
+      </c>
+      <c r="S52">
+        <v>17.76354386892177</v>
+      </c>
+      <c r="T52">
         <v>0</v>
       </c>
     </row>

--- a/database_postprocessing.xlsx
+++ b/database_postprocessing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="40">
   <si>
     <t>file</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>ELC_NGA_CC_N</t>
-  </si>
-  <si>
-    <t>ELC_NGA_CC_P</t>
   </si>
   <si>
     <t>ELC_NGA_CT_N</t>
@@ -496,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -640,34 +637,34 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1156140475741612</v>
+        <v>0.1156140475741613</v>
       </c>
       <c r="I3">
-        <v>0.1845041074831423</v>
+        <v>0.1845041074831422</v>
       </c>
       <c r="J3">
-        <v>0.2792587022639487</v>
+        <v>0.2765267107956052</v>
       </c>
       <c r="K3">
-        <v>0.5681202808173806</v>
+        <v>0.568072954980921</v>
       </c>
       <c r="L3">
-        <v>0.5187749950934094</v>
+        <v>0.5187276692569499</v>
       </c>
       <c r="M3">
-        <v>0.4742593652774342</v>
+        <v>0.4958910540372594</v>
       </c>
       <c r="N3">
-        <v>0.5441516755335334</v>
+        <v>0.5443572975042028</v>
       </c>
       <c r="O3">
-        <v>0.8435864027666037</v>
+        <v>0.8434902016956519</v>
       </c>
       <c r="P3">
         <v>1.002976572934977</v>
       </c>
       <c r="Q3">
-        <v>1.115153929707553</v>
+        <v>1.115153929707554</v>
       </c>
       <c r="R3">
         <v>1.275111733751409</v>
@@ -693,46 +690,46 @@
         <v>0.409</v>
       </c>
       <c r="F4">
-        <v>0.409</v>
+        <v>0.4957714493898755</v>
       </c>
       <c r="G4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="H4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="I4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="J4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="K4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="L4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="M4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="N4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="O4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="P4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="Q4">
-        <v>0.5834923847918516</v>
+        <v>0.5834923847918515</v>
       </c>
       <c r="R4">
         <v>0.2562923847918516</v>
       </c>
       <c r="S4">
-        <v>0.03489847695837033</v>
+        <v>0.0175441870803952</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -755,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0.2666666666666667</v>
@@ -764,7 +761,7 @@
         <v>0.4</v>
       </c>
       <c r="J5">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="K5">
         <v>0.6666666666666666</v>
@@ -873,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.5333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0.6666666666666666</v>
@@ -932,43 +929,43 @@
         <v>0.8648733377620116</v>
       </c>
       <c r="G8">
-        <v>2.828846074642624</v>
+        <v>0.8648733377620116</v>
       </c>
       <c r="H8">
-        <v>3.613428927490221</v>
+        <v>0.8648733377620116</v>
       </c>
       <c r="I8">
-        <v>3.613428927490221</v>
+        <v>0.8648733377620116</v>
       </c>
       <c r="J8">
-        <v>3.613428927490221</v>
+        <v>0.8648733377620116</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1015,19 +1012,19 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>2.516272640526505</v>
+        <v>3.035394749369558</v>
       </c>
       <c r="P9">
-        <v>2.516272640526505</v>
+        <v>3.035394749369558</v>
       </c>
       <c r="Q9">
-        <v>3.377926192120482</v>
+        <v>6.949064499903466</v>
       </c>
       <c r="R9">
-        <v>3.377926192120482</v>
+        <v>6.949064499903466</v>
       </c>
       <c r="S9">
-        <v>2.119789871857229</v>
+        <v>5.431367125218687</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1077,16 +1074,16 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>0.7122314397278249</v>
       </c>
       <c r="Q10">
-        <v>2.326435820985384</v>
+        <v>2.035601024190283</v>
       </c>
       <c r="R10">
-        <v>2.326435820985384</v>
+        <v>2.035601024190283</v>
       </c>
       <c r="S10">
-        <v>2.326435820985384</v>
+        <v>2.035601024190283</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1283,46 +1280,46 @@
         <v>16.658</v>
       </c>
       <c r="F14">
-        <v>16.658</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="G14">
-        <v>16.658</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="H14">
-        <v>16.658</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="I14">
-        <v>16.658</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="J14">
-        <v>16.658</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="K14">
-        <v>16.658</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="L14">
-        <v>16.658</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="M14">
-        <v>21.09062205417134</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="N14">
-        <v>21.09062205417134</v>
+        <v>17.4497687288999</v>
       </c>
       <c r="O14">
-        <v>34.09985098436238</v>
+        <v>28.95452681388147</v>
       </c>
       <c r="P14">
-        <v>34.577727799774</v>
+        <v>29.43558985099927</v>
       </c>
       <c r="Q14">
-        <v>36.17972016417378</v>
+        <v>31.36736098960356</v>
       </c>
       <c r="R14">
-        <v>36.54362212131757</v>
+        <v>32.0889268983459</v>
       </c>
       <c r="S14">
-        <v>33.21202212131757</v>
+        <v>27.965558169446</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1342,46 +1339,46 @@
         <v>1.809</v>
       </c>
       <c r="F15">
-        <v>1.809</v>
+        <v>2.409869185902577</v>
       </c>
       <c r="G15">
-        <v>1.809</v>
+        <v>2.409869185902577</v>
       </c>
       <c r="H15">
-        <v>1.809</v>
+        <v>2.409869185902577</v>
       </c>
       <c r="I15">
-        <v>1.809</v>
+        <v>2.409869185902577</v>
       </c>
       <c r="J15">
-        <v>1.809</v>
+        <v>2.409869185902577</v>
       </c>
       <c r="K15">
-        <v>1.809</v>
+        <v>2.409869185902577</v>
       </c>
       <c r="L15">
-        <v>1.809</v>
+        <v>2.409869185902577</v>
       </c>
       <c r="M15">
-        <v>1.809</v>
+        <v>5.533770155920489</v>
       </c>
       <c r="N15">
-        <v>3.852969260786626</v>
+        <v>8.819308832566001</v>
       </c>
       <c r="O15">
-        <v>3.852969260786626</v>
+        <v>9.003176815955396</v>
       </c>
       <c r="P15">
-        <v>3.852969260786626</v>
+        <v>9.003176815955396</v>
       </c>
       <c r="Q15">
-        <v>3.852969260786626</v>
+        <v>9.003176815955396</v>
       </c>
       <c r="R15">
-        <v>2.405769260786626</v>
+        <v>7.555976815955395</v>
       </c>
       <c r="S15">
-        <v>2.043969260786626</v>
+        <v>6.593307630052818</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1490,16 +1487,16 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.012974740602063</v>
+        <v>1.01292664006659</v>
       </c>
       <c r="Q17">
-        <v>4.536111897423965</v>
+        <v>4.023562698678884</v>
       </c>
       <c r="R17">
-        <v>4.536111897423965</v>
+        <v>4.023562698678884</v>
       </c>
       <c r="S17">
-        <v>4.536111897423965</v>
+        <v>4.023562698678884</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -1519,46 +1516,46 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0.8816959667563359</v>
+        <v>1.855963194726039</v>
       </c>
       <c r="G18">
-        <v>0.8816959667563359</v>
+        <v>4.112468086760503</v>
       </c>
       <c r="H18">
-        <v>0.8816959667563359</v>
+        <v>4.112468086760503</v>
       </c>
       <c r="I18">
-        <v>0.8816959667563359</v>
+        <v>4.502873388431286</v>
       </c>
       <c r="J18">
-        <v>0.8816959667563359</v>
+        <v>4.502873388431286</v>
       </c>
       <c r="K18">
-        <v>0.8816959667563359</v>
+        <v>4.633408597248515</v>
       </c>
       <c r="L18">
-        <v>0.8816959667563359</v>
+        <v>9.415958929075218</v>
       </c>
       <c r="M18">
-        <v>0.8816959667563359</v>
+        <v>15.90951289131835</v>
       </c>
       <c r="N18">
-        <v>0.8816959667563359</v>
+        <v>15.90951289131835</v>
       </c>
       <c r="O18">
-        <v>0.8816959667563359</v>
+        <v>15.90951289131835</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>15.90951289131835</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>12.69964676137163</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>12.83424807476145</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>13.82499186137159</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -1572,52 +1569,52 @@
         <v>22</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="F19">
-        <v>1.85596319472604</v>
+        <v>6.547</v>
       </c>
       <c r="G19">
-        <v>2.289187884556547</v>
+        <v>6.547</v>
       </c>
       <c r="H19">
-        <v>2.289187884556547</v>
+        <v>6.547</v>
       </c>
       <c r="I19">
-        <v>2.365488334819183</v>
+        <v>6.547</v>
       </c>
       <c r="J19">
-        <v>2.365488334819183</v>
+        <v>6.547</v>
       </c>
       <c r="K19">
-        <v>2.365488334819183</v>
+        <v>6.547</v>
       </c>
       <c r="L19">
-        <v>7.315935266156991</v>
+        <v>6.547</v>
       </c>
       <c r="M19">
-        <v>14.17285026697301</v>
+        <v>6.547</v>
       </c>
       <c r="N19">
-        <v>14.17285026697301</v>
+        <v>6.547</v>
       </c>
       <c r="O19">
-        <v>14.17285026697301</v>
+        <v>6.547</v>
       </c>
       <c r="P19">
-        <v>14.17285026697301</v>
+        <v>6.547</v>
       </c>
       <c r="Q19">
-        <v>12.05695225834867</v>
+        <v>6.547</v>
       </c>
       <c r="R19">
-        <v>12.72149569146447</v>
+        <v>1.3094</v>
       </c>
       <c r="S19">
-        <v>13.53054673997953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -1631,49 +1628,49 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="E20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="F20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="G20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="H20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="I20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="J20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="K20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="L20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="M20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="N20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="O20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="P20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="Q20">
-        <v>6.547</v>
+        <v>8.315</v>
       </c>
       <c r="R20">
-        <v>1.3094</v>
+        <v>1.663</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -1690,52 +1687,52 @@
         <v>24</v>
       </c>
       <c r="D21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>8.315</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>8.315</v>
+        <v>0.2658962635839847</v>
       </c>
       <c r="Q21">
-        <v>8.315</v>
+        <v>0.2658962635839847</v>
       </c>
       <c r="R21">
-        <v>1.663</v>
+        <v>0.2658962635839847</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>0.2658962635839847</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -1749,52 +1746,52 @@
         <v>25</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>7.716</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>7.716</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="P22">
-        <v>0.2658962635839847</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="Q22">
-        <v>0.2658962635839847</v>
+        <v>7.874005231215762</v>
       </c>
       <c r="R22">
-        <v>0.2658962635839847</v>
+        <v>4.718492466933343</v>
       </c>
       <c r="S22">
-        <v>0.2658962635839847</v>
+        <v>4.687652646888027</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -1808,52 +1805,52 @@
         <v>26</v>
       </c>
       <c r="D23">
-        <v>7.716</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>7.716</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>7.799478603231965</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>7.799478603231965</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>7.799478603231965</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>7.799478603231965</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>7.799478603231965</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>7.799478603231965</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>7.799478603231965</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>7.799478603231965</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>7.799478603231965</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>7.799478603231965</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>7.799478603231965</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>7.799478603231965</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>4.718492466933343</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>4.687652646888027</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -1894,25 +1891,25 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="N24">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="O24">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="Q24">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="R24">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="S24">
-        <v>8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -1929,49 +1926,49 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>0.65577484449026</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2.666133590943942</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>5.110354661171913</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>5.728218218302898</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>5.936456649270218</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>5.936456649270218</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>9.651165434743177</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>15.98015258734092</v>
       </c>
       <c r="M25">
-        <v>3.2</v>
+        <v>17.91834212651418</v>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>19.07915656765207</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>24.48233196999114</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>26.13961211914179</v>
       </c>
       <c r="Q25">
-        <v>3.2</v>
+        <v>26.87368932578686</v>
       </c>
       <c r="R25">
-        <v>3.2</v>
+        <v>28.9177559773951</v>
       </c>
       <c r="S25">
-        <v>3.2</v>
+        <v>31.11145256659376</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -1985,52 +1982,52 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.3060747959710572</v>
       </c>
       <c r="E26">
-        <v>0.65577484449026</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="F26">
-        <v>2.666133590943942</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="G26">
-        <v>4.826740471699576</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="H26">
-        <v>5.686447672140506</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="I26">
-        <v>5.940341828104529</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="J26">
-        <v>6.262115036677836</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="K26">
-        <v>9.042830358519804</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="L26">
-        <v>15.98015258734092</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="M26">
-        <v>17.78880412100943</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="N26">
-        <v>18.87938163622366</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="O26">
-        <v>24.48233196999114</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="P26">
-        <v>26.1396121191418</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="Q26">
-        <v>27.16515154036342</v>
+        <v>0.7621209243680023</v>
       </c>
       <c r="R26">
-        <v>28.9177559773951</v>
+        <v>0.3686575954265899</v>
       </c>
       <c r="S26">
-        <v>31.11145256659376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2044,49 +2041,49 @@
         <v>30</v>
       </c>
       <c r="D27">
-        <v>0.3060747959710572</v>
+        <v>11.279</v>
       </c>
       <c r="E27">
-        <v>0.7621209243680023</v>
+        <v>11.279</v>
       </c>
       <c r="F27">
-        <v>0.7621209243680023</v>
+        <v>11.40687415366328</v>
       </c>
       <c r="G27">
-        <v>0.7621209243680023</v>
+        <v>11.40687415366328</v>
       </c>
       <c r="H27">
-        <v>0.7621209243680023</v>
+        <v>11.40687415366328</v>
       </c>
       <c r="I27">
-        <v>0.7621209243680023</v>
+        <v>11.40687415366328</v>
       </c>
       <c r="J27">
-        <v>0.7621209243680023</v>
+        <v>11.40687415366328</v>
       </c>
       <c r="K27">
-        <v>0.7621209243680023</v>
+        <v>13.67449478502083</v>
       </c>
       <c r="L27">
-        <v>0.7621209243680023</v>
+        <v>13.67449478502083</v>
       </c>
       <c r="M27">
-        <v>0.7621209243680023</v>
+        <v>13.67449478502083</v>
       </c>
       <c r="N27">
-        <v>0.7621209243680023</v>
+        <v>12.64926495950441</v>
       </c>
       <c r="O27">
-        <v>0.7621209243680023</v>
+        <v>10.26559080584113</v>
       </c>
       <c r="P27">
-        <v>0.7621209243680023</v>
+        <v>10.26559080584113</v>
       </c>
       <c r="Q27">
-        <v>0.7621209243680023</v>
+        <v>7.99797017448358</v>
       </c>
       <c r="R27">
-        <v>0.3686575954265898</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -2103,52 +2100,52 @@
         <v>31</v>
       </c>
       <c r="D28">
-        <v>11.279</v>
+        <v>2.830007614791414</v>
       </c>
       <c r="E28">
-        <v>11.279</v>
+        <v>5.680053691486149</v>
       </c>
       <c r="F28">
-        <v>11.84457220001526</v>
+        <v>12.44485831462683</v>
       </c>
       <c r="G28">
-        <v>11.84457220001526</v>
+        <v>13.91370480839185</v>
       </c>
       <c r="H28">
-        <v>11.84457220001526</v>
+        <v>15.21456554675684</v>
       </c>
       <c r="I28">
-        <v>11.84457220001526</v>
+        <v>15.21456554675684</v>
       </c>
       <c r="J28">
-        <v>11.84457220001526</v>
+        <v>15.21456554675684</v>
       </c>
       <c r="K28">
-        <v>14.11219283137281</v>
+        <v>15.21456554675684</v>
       </c>
       <c r="L28">
-        <v>14.11219283137281</v>
+        <v>19.78425849784081</v>
       </c>
       <c r="M28">
-        <v>14.11219283137281</v>
+        <v>20.4897523999587</v>
       </c>
       <c r="N28">
-        <v>13.08696300585639</v>
+        <v>23.19628458227889</v>
       </c>
       <c r="O28">
-        <v>10.26559080584112</v>
+        <v>39.31245356602022</v>
       </c>
       <c r="P28">
-        <v>10.26559080584112</v>
+        <v>49.96454054129856</v>
       </c>
       <c r="Q28">
-        <v>7.997970174483577</v>
+        <v>62.88424814793445</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>81.53430529769638</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>92.18639227297471</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2162,111 +2159,52 @@
         <v>32</v>
       </c>
       <c r="D29">
-        <v>2.830007614791413</v>
+        <v>2.546</v>
       </c>
       <c r="E29">
-        <v>5.680053691486149</v>
+        <v>2.546</v>
       </c>
       <c r="F29">
-        <v>13.47600676203987</v>
+        <v>2.546</v>
       </c>
       <c r="G29">
-        <v>13.47600676203987</v>
+        <v>2.546</v>
       </c>
       <c r="H29">
-        <v>14.77686750040485</v>
+        <v>2.546</v>
       </c>
       <c r="I29">
-        <v>14.77686750040485</v>
+        <v>2.546</v>
       </c>
       <c r="J29">
-        <v>14.77686750040485</v>
+        <v>2.546</v>
       </c>
       <c r="K29">
-        <v>14.77686750040485</v>
+        <v>2.546</v>
       </c>
       <c r="L29">
-        <v>19.66300221522456</v>
+        <v>2.546</v>
       </c>
       <c r="M29">
-        <v>20.02616531141269</v>
+        <v>2.546</v>
       </c>
       <c r="N29">
-        <v>23.35874837643161</v>
+        <v>2.546</v>
       </c>
       <c r="O29">
-        <v>39.31245356602023</v>
+        <v>2.546</v>
       </c>
       <c r="P29">
-        <v>49.96454054129855</v>
+        <v>2.546</v>
       </c>
       <c r="Q29">
-        <v>62.88424814793446</v>
+        <v>3.262665277411847</v>
       </c>
       <c r="R29">
-        <v>81.53430529769638</v>
+        <v>7.270594127561734</v>
       </c>
       <c r="S29">
-        <v>92.18639227297471</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30">
-        <v>2.546</v>
-      </c>
-      <c r="E30">
-        <v>2.546</v>
-      </c>
-      <c r="F30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="G30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="H30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="I30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="J30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="K30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="L30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="M30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="N30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="O30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="P30">
-        <v>3.007504380262247</v>
-      </c>
-      <c r="Q30">
-        <v>3.37256509749842</v>
-      </c>
-      <c r="R30">
-        <v>7.597955988518064</v>
-      </c>
-      <c r="S30">
-        <v>11.52941866508463</v>
+        <v>11.82483959941497</v>
       </c>
     </row>
   </sheetData>
@@ -2276,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2290,7 +2228,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1">
         <v>2007</v>
@@ -2352,10 +2290,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>4.693730232558139</v>
+        <v>4.693730232558141</v>
       </c>
       <c r="F2">
         <v>4.69373023255814</v>
@@ -2367,10 +2305,10 @@
         <v>4.459043720930232</v>
       </c>
       <c r="I2">
-        <v>4.224357209302326</v>
+        <v>4.224357209302324</v>
       </c>
       <c r="J2">
-        <v>3.989670697674418</v>
+        <v>3.989670697674419</v>
       </c>
       <c r="K2">
         <v>3.754984186046511</v>
@@ -2385,19 +2323,19 @@
         <v>3.050924651162791</v>
       </c>
       <c r="O2">
-        <v>2.933581395348838</v>
+        <v>2.933581395348837</v>
       </c>
       <c r="P2">
         <v>2.34686511627907</v>
       </c>
       <c r="Q2">
-        <v>1.760148837209302</v>
+        <v>1.760148837209303</v>
       </c>
       <c r="R2">
         <v>1.173432558139535</v>
       </c>
       <c r="S2">
-        <v>0.5867162790697673</v>
+        <v>0.5867162790697675</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -2414,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2429,37 +2367,37 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>1.828406511627907</v>
+        <v>1.828406511627908</v>
       </c>
       <c r="J3">
         <v>2.937792558139537</v>
       </c>
       <c r="K3">
-        <v>4.491075348837207</v>
+        <v>4.491075348837205</v>
       </c>
       <c r="L3">
-        <v>8.499918139534886</v>
+        <v>8.499918139534888</v>
       </c>
       <c r="M3">
-        <v>8.006330930232563</v>
+        <v>8.00633093023256</v>
       </c>
       <c r="N3">
-        <v>7.512743720930238</v>
+        <v>7.512743720930233</v>
       </c>
       <c r="O3">
-        <v>8.454115116279073</v>
+        <v>8.454115116279075</v>
       </c>
       <c r="P3">
-        <v>13.16097209302326</v>
+        <v>13.16097209302327</v>
       </c>
       <c r="Q3">
         <v>15.80822906976745</v>
       </c>
       <c r="R3">
-        <v>18.45548604651162</v>
+        <v>18.45548604651163</v>
       </c>
       <c r="S3">
-        <v>21.10274302325582</v>
+        <v>21.10274302325581</v>
       </c>
       <c r="T3">
         <v>23.75</v>
@@ -2476,7 +2414,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>2.69688976744186</v>
@@ -2485,10 +2423,10 @@
         <v>4.059189767441858</v>
       </c>
       <c r="G4">
-        <v>6.783789767441862</v>
+        <v>8.596029767441864</v>
       </c>
       <c r="H4">
-        <v>10.11699627906977</v>
+        <v>10.11699627906978</v>
       </c>
       <c r="I4">
         <v>10.11699627906977</v>
@@ -2500,7 +2438,7 @@
         <v>9.387460465116281</v>
       </c>
       <c r="L4">
-        <v>8.800744186046511</v>
+        <v>8.800744186046515</v>
       </c>
       <c r="M4">
         <v>8.214027906976746</v>
@@ -2509,13 +2447,13 @@
         <v>7.627311627906979</v>
       </c>
       <c r="O4">
-        <v>7.333953488372093</v>
+        <v>7.333953488372096</v>
       </c>
       <c r="P4">
-        <v>5.867162790697676</v>
+        <v>5.867162790697673</v>
       </c>
       <c r="Q4">
-        <v>4.400372093023256</v>
+        <v>4.400372093023257</v>
       </c>
       <c r="R4">
         <v>2.933581395348838</v>
@@ -2538,7 +2476,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2550,43 +2488,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>1.369560292992</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>2.739120585984</v>
+        <v>2.739120585984001</v>
       </c>
       <c r="J5">
         <v>4.108680878976</v>
       </c>
       <c r="K5">
-        <v>5.478241171968</v>
+        <v>4.108680878976</v>
       </c>
       <c r="L5">
-        <v>6.167233169702405</v>
+        <v>5.954274316799999</v>
       </c>
       <c r="M5">
         <v>7.502540039424002</v>
       </c>
       <c r="N5">
-        <v>8.752963379328005</v>
+        <v>8.752963379328003</v>
       </c>
       <c r="O5">
-        <v>9.378175049279999</v>
+        <v>8.868883637905149</v>
       </c>
       <c r="P5">
+        <v>5.804087901119999</v>
+      </c>
+      <c r="Q5">
         <v>5.804087901120001</v>
       </c>
-      <c r="Q5">
-        <v>5.80408790112</v>
-      </c>
       <c r="R5">
-        <v>5.9947058823552</v>
+        <v>6.250851475199999</v>
       </c>
       <c r="S5">
-        <v>6.066695079408805</v>
+        <v>5.996235756500161</v>
       </c>
       <c r="T5">
-        <v>6.106395667910397</v>
+        <v>6.1324567870464</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -2600,7 +2538,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2636,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>30.46801590775935</v>
+        <v>30.46801590775926</v>
       </c>
       <c r="Q6">
         <v>32.15071989504</v>
       </c>
       <c r="R6">
-        <v>32.15071989504</v>
+        <v>31.95156305509294</v>
       </c>
       <c r="S6">
-        <v>28.61959070957422</v>
+        <v>28.36636962048</v>
       </c>
       <c r="T6">
-        <v>17.5388342774551</v>
+        <v>16.93600512188185</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -2662,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2680,16 +2618,16 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>5.961615393024</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>11.923230786048</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>12.95930292479999</v>
+        <v>12.9593029248</v>
       </c>
       <c r="M7">
-        <v>16.12422656591962</v>
+        <v>16.12422656591963</v>
       </c>
       <c r="N7">
         <v>14.966633574144</v>
@@ -2707,10 +2645,10 @@
         <v>12.63242660832</v>
       </c>
       <c r="S7">
-        <v>13.1769469636992</v>
+        <v>12.63242660832</v>
       </c>
       <c r="T7">
-        <v>12.45677381746239</v>
+        <v>12.87807637991754</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -2724,7 +2662,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2742,37 +2680,37 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>69.91550227437651</v>
+        <v>19.3351582628177</v>
       </c>
       <c r="K8">
-        <v>68.49892239729242</v>
+        <v>19.3351582628177</v>
       </c>
       <c r="L8">
-        <v>69.64252986226985</v>
+        <v>19.33960928195146</v>
       </c>
       <c r="M8">
-        <v>76.44595287110909</v>
+        <v>19.4389543872</v>
       </c>
       <c r="N8">
-        <v>55.27158701562642</v>
+        <v>16.03567882944</v>
       </c>
       <c r="O8">
-        <v>54.19554097789611</v>
+        <v>16.03567882944</v>
       </c>
       <c r="P8">
-        <v>48.60425445890759</v>
+        <v>12.63242660832</v>
       </c>
       <c r="Q8">
-        <v>48.83306601413146</v>
+        <v>12.63242660832</v>
       </c>
       <c r="R8">
-        <v>50.45401344321652</v>
+        <v>12.55322332533456</v>
       </c>
       <c r="S8">
-        <v>55.26041734603275</v>
+        <v>12.22061239232301</v>
       </c>
       <c r="T8">
-        <v>44.09075790409101</v>
+        <v>10.59932802311156</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -2786,7 +2724,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2822,19 +2760,19 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>24.48429566357507</v>
+        <v>29.53555242872131</v>
       </c>
       <c r="Q9">
-        <v>24.48429566357507</v>
+        <v>29.53555242872131</v>
       </c>
       <c r="R9">
-        <v>32.86851443900241</v>
+        <v>67.61705669751635</v>
       </c>
       <c r="S9">
-        <v>32.86851443900241</v>
+        <v>67.61705669751635</v>
       </c>
       <c r="T9">
-        <v>23.11906448890412</v>
+        <v>53.16959587682167</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -2848,7 +2786,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -2887,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>9.859185542958906</v>
       </c>
       <c r="R10">
-        <v>32.20408582587422</v>
+        <v>28.17815539931596</v>
       </c>
       <c r="S10">
-        <v>32.20408582587422</v>
+        <v>27.05693844000935</v>
       </c>
       <c r="T10">
-        <v>16.10220211819882</v>
+        <v>13.92031415296697</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -2910,7 +2848,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11">
         <v>266.71</v>
@@ -2919,31 +2857,31 @@
         <v>177.5278</v>
       </c>
       <c r="G11">
-        <v>92.38500000000008</v>
+        <v>92.38500000000006</v>
       </c>
       <c r="H11">
-        <v>186.7415000000001</v>
+        <v>186.7415</v>
       </c>
       <c r="I11">
-        <v>155.0399999999999</v>
+        <v>155.0399999999998</v>
       </c>
       <c r="J11">
-        <v>120.9635000000001</v>
+        <v>120.9635000000002</v>
       </c>
       <c r="K11">
-        <v>125.2479999999999</v>
+        <v>125.248</v>
       </c>
       <c r="L11">
-        <v>13.90799999999998</v>
+        <v>13.90799999999996</v>
       </c>
       <c r="M11">
-        <v>22.60999999999998</v>
+        <v>22.60999999999996</v>
       </c>
       <c r="N11">
-        <v>4.730999999999997</v>
+        <v>4.731000000000003</v>
       </c>
       <c r="O11">
-        <v>3.07166666666667</v>
+        <v>3.071666666666673</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -2972,7 +2910,7 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2984,28 +2922,28 @@
         <v>2.375</v>
       </c>
       <c r="H12">
-        <v>4.749999999999999</v>
+        <v>4.749999999999994</v>
       </c>
       <c r="I12">
         <v>4.75</v>
       </c>
       <c r="J12">
-        <v>7.125</v>
+        <v>7.124999999999999</v>
       </c>
       <c r="K12">
-        <v>7.124999999999999</v>
+        <v>7.124999999999998</v>
       </c>
       <c r="L12">
         <v>7.124999999999999</v>
       </c>
       <c r="M12">
+        <v>7.124999999999998</v>
+      </c>
+      <c r="N12">
         <v>7.124999999999999</v>
       </c>
-      <c r="N12">
-        <v>7.124999999999997</v>
-      </c>
       <c r="O12">
-        <v>7.124999999999996</v>
+        <v>7.124999999999999</v>
       </c>
       <c r="P12">
         <v>1.9</v>
@@ -3014,7 +2952,7 @@
         <v>1.425</v>
       </c>
       <c r="R12">
-        <v>0.9500000000000002</v>
+        <v>0.95</v>
       </c>
       <c r="S12">
         <v>0.4749999999999999</v>
@@ -3034,7 +2972,7 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -3043,16 +2981,16 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.6000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.1294208905299551</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.405</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -3096,55 +3034,55 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14">
-        <v>72.32802628789788</v>
+        <v>72.32802628789786</v>
       </c>
       <c r="F14">
-        <v>56.0292097927943</v>
+        <v>56.02920979279438</v>
       </c>
       <c r="G14">
-        <v>105.0282647703012</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="H14">
-        <v>65.58621572204257</v>
+        <v>62.40370348647316</v>
       </c>
       <c r="I14">
-        <v>105.0282647703012</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="J14">
-        <v>105.0282647703012</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="K14">
-        <v>105.0282647703011</v>
+        <v>108.2110601577593</v>
       </c>
       <c r="L14">
-        <v>105.0282647703012</v>
+        <v>95.50650857339303</v>
       </c>
       <c r="M14">
-        <v>76.11822117844432</v>
+        <v>75.74088043391299</v>
       </c>
       <c r="N14">
-        <v>132.9758336700601</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="O14">
-        <v>132.9758336700601</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="P14">
-        <v>214.9986899875992</v>
+        <v>182.5575524376953</v>
       </c>
       <c r="Q14">
-        <v>218.0116911099812</v>
+        <v>185.5906426065999</v>
       </c>
       <c r="R14">
-        <v>225.3915382780063</v>
+        <v>194.1164835816791</v>
       </c>
       <c r="S14">
-        <v>226.4438195255677</v>
+        <v>196.1099103224376</v>
       </c>
       <c r="T14">
-        <v>202.996334111434</v>
+        <v>169.8844483526271</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -3158,7 +3096,7 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -3167,46 +3105,46 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>11.4056988215557</v>
+        <v>15.19416370025009</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1.739292035569433</v>
       </c>
       <c r="I15">
-        <v>11.4056988215557</v>
+        <v>15.19416370025009</v>
       </c>
       <c r="J15">
-        <v>11.4056988215557</v>
+        <v>15.19416370025009</v>
       </c>
       <c r="K15">
-        <v>11.40569882155569</v>
+        <v>8.250706072470551</v>
       </c>
       <c r="L15">
-        <v>11.4056988215557</v>
+        <v>11.81783815455584</v>
       </c>
       <c r="M15">
-        <v>11.4056988215557</v>
+        <v>11.78303956608702</v>
       </c>
       <c r="N15">
-        <v>11.4056988215557</v>
+        <v>34.89027957221803</v>
       </c>
       <c r="O15">
-        <v>24.29287283429759</v>
+        <v>55.6055170583382</v>
       </c>
       <c r="P15">
-        <v>24.29287283429759</v>
+        <v>56.76479999999999</v>
       </c>
       <c r="Q15">
-        <v>24.2928728342976</v>
+        <v>56.76480000000002</v>
       </c>
       <c r="R15">
-        <v>22.5303245337787</v>
+        <v>54.44098437834263</v>
       </c>
       <c r="S15">
-        <v>14.04498299352233</v>
+        <v>45.8223473171245</v>
       </c>
       <c r="T15">
-        <v>11.76384322921119</v>
+        <v>41.57063629974991</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -3220,10 +3158,10 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16">
-        <v>341.2764</v>
+        <v>341.2764000000001</v>
       </c>
       <c r="F16">
         <v>434.8728</v>
@@ -3232,34 +3170,34 @@
         <v>341.4636</v>
       </c>
       <c r="H16">
-        <v>262.539239707008</v>
+        <v>263.9088</v>
       </c>
       <c r="I16">
-        <v>176.8040394140158</v>
+        <v>176.8040394140159</v>
       </c>
       <c r="J16">
-        <v>112.4059584919081</v>
+        <v>157.2005608582062</v>
       </c>
       <c r="K16">
-        <v>112.4732856446914</v>
+        <v>185.3705608582064</v>
       </c>
       <c r="L16">
-        <v>149.7383140432277</v>
+        <v>212.8072134764487</v>
       </c>
       <c r="M16">
-        <v>193.9617805235479</v>
+        <v>250.9687790074566</v>
       </c>
       <c r="N16">
-        <v>106.0658062231972</v>
+        <v>144.3979826126466</v>
       </c>
       <c r="O16">
-        <v>116.6292104219248</v>
+        <v>150.9254978651995</v>
       </c>
       <c r="P16">
-        <v>106.0344357859483</v>
+        <v>136.9639618498347</v>
       </c>
       <c r="Q16">
-        <v>104.3628487501016</v>
+        <v>124.21</v>
       </c>
       <c r="R16">
         <v>27.2</v>
@@ -3282,7 +3220,7 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3321,16 +3259,16 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>14.06806889656661</v>
+        <v>15.52603883088634</v>
       </c>
       <c r="R17">
-        <v>59.26144083700451</v>
+        <v>52.83391106439111</v>
       </c>
       <c r="S17">
-        <v>59.87843604488208</v>
+        <v>53.72128810615413</v>
       </c>
       <c r="T17">
-        <v>18.17601190730787</v>
+        <v>18.68429514838492</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -3344,7 +3282,7 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3353,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>13.77683883151423</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -3386,13 +3324,13 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>14.88026064009495</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.948545218679582</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>65.84765355607043</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -3406,7 +3344,7 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3448,13 +3386,13 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>2.810294672560148</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>0.3808218712862951</v>
+        <v>2.5</v>
       </c>
       <c r="T19">
-        <v>69.08056777162764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -3468,43 +3406,43 @@
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>66.6288</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>63.29987999999999</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>59.6232</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>52.39781999999997</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>48.29382</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>57.86981999999999</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>49.58316</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>36.60768</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>36.21780000000001</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>30.514</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>27.01166666666667</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3513,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -3530,52 +3468,52 @@
         <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21">
-        <v>66.62880000000001</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>63.29987999999999</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>59.6232</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>52.39782</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>48.29382</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>57.86981999999999</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>49.58316000000001</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>36.60767999999998</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>36.2178</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>30.514</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>27.01166666666666</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>7.125</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -3592,55 +3530,55 @@
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>198.37</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>212.3028</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>223.4045000000002</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>221.29</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>208.5023220590161</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>223.2995988529451</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>200.76</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>209.8800000000001</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>223.4045</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>215.9410000000001</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>202.7008333333334</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="Q22">
-        <v>7.124999999999999</v>
+        <v>135.625</v>
       </c>
       <c r="R22">
-        <v>4.75</v>
+        <v>134.75</v>
       </c>
       <c r="S22">
-        <v>2.375</v>
+        <v>133.875</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -3654,55 +3592,55 @@
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>198.37</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>212.3028</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>221.29</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>221.2899999999999</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>221.2900000000001</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>221.2900000000002</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>205.4115272458197</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>212.505649514577</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>221.2899999999997</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>215.941</v>
+        <v>49.625829926784</v>
       </c>
       <c r="O23">
-        <v>202.7008333333333</v>
+        <v>49.62582992678401</v>
       </c>
       <c r="P23">
-        <v>136.5</v>
+        <v>49.62582992678401</v>
       </c>
       <c r="Q23">
-        <v>135.625</v>
+        <v>49.62582992678401</v>
       </c>
       <c r="R23">
-        <v>134.75</v>
+        <v>48.19618648972801</v>
       </c>
       <c r="S23">
-        <v>133.875</v>
+        <v>49.62582992678401</v>
       </c>
       <c r="T23">
-        <v>133</v>
+        <v>48.72973020596243</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -3716,7 +3654,7 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -3746,25 +3684,25 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>49.62017517679446</v>
+        <v>16.2023932122624</v>
       </c>
       <c r="O24">
-        <v>48.98144201845167</v>
+        <v>16.2023932122624</v>
       </c>
       <c r="P24">
-        <v>49.62582992678401</v>
+        <v>13.07812930848913</v>
       </c>
       <c r="Q24">
-        <v>49.625829926784</v>
+        <v>16.2023932122624</v>
       </c>
       <c r="R24">
-        <v>46.42550076672656</v>
+        <v>15.7356566784</v>
       </c>
       <c r="S24">
-        <v>44.25394663631532</v>
+        <v>13.11099952131072</v>
       </c>
       <c r="T24">
-        <v>47.40821113674779</v>
+        <v>13.11099952131072</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -3778,55 +3716,55 @@
         <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>4.980633600000001</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>20.2493808</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>38.813328</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>43.1887752</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>45.08760239999999</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>45.08760239999999</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>70.36879679999998</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>118.1991239999999</v>
       </c>
       <c r="N25">
-        <v>15.58723706620975</v>
+        <v>129.8375368609536</v>
       </c>
       <c r="O25">
-        <v>13.90062091985343</v>
+        <v>136.343878194287</v>
       </c>
       <c r="P25">
-        <v>13.58754800342453</v>
+        <v>174.7960407647269</v>
       </c>
       <c r="Q25">
-        <v>11.9891499065856</v>
+        <v>183.5467768609535</v>
       </c>
       <c r="R25">
-        <v>14.59881279911453</v>
+        <v>197.318156831872</v>
       </c>
       <c r="S25">
-        <v>13.11099952131072</v>
+        <v>210.3881705519052</v>
       </c>
       <c r="T25">
-        <v>11.8298379703314</v>
+        <v>223.1592702727268</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -3840,55 +3778,55 @@
         <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1.7613</v>
       </c>
       <c r="F26">
-        <v>4.980633600000002</v>
+        <v>4.385606399999999</v>
       </c>
       <c r="G26">
-        <v>20.2493808</v>
+        <v>4.3267392</v>
       </c>
       <c r="H26">
-        <v>36.659268</v>
+        <v>4.267872</v>
       </c>
       <c r="I26">
-        <v>43.18877519999998</v>
+        <v>4.209004800000001</v>
       </c>
       <c r="J26">
-        <v>45.08760239999997</v>
+        <v>4.1501376</v>
       </c>
       <c r="K26">
-        <v>47.56098960000001</v>
+        <v>0.7907975999999987</v>
       </c>
       <c r="L26">
-        <v>66.64873679999998</v>
+        <v>4.032403199999998</v>
       </c>
       <c r="M26">
-        <v>118.199124</v>
+        <v>3.973536000000001</v>
       </c>
       <c r="N26">
-        <v>130.4583477569958</v>
+        <v>3.679200000000001</v>
       </c>
       <c r="O26">
-        <v>139.2900383950282</v>
+        <v>3.532032000000001</v>
       </c>
       <c r="P26">
-        <v>174.2866220697915</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>187.7600201666303</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>200.2256864341591</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>215.760053842374</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>225.7619508929208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -3905,46 +3843,46 @@
         <v>35</v>
       </c>
       <c r="E27">
-        <v>1.761299999999999</v>
+        <v>75.36756595731136</v>
       </c>
       <c r="F27">
-        <v>4.385606399999999</v>
+        <v>75.36756595731134</v>
       </c>
       <c r="G27">
-        <v>4.3267392</v>
+        <v>76.22203565413311</v>
       </c>
       <c r="H27">
-        <v>4.267872000000001</v>
+        <v>76.22203565413311</v>
       </c>
       <c r="I27">
-        <v>4.209004799999998</v>
+        <v>76.22203565413312</v>
       </c>
       <c r="J27">
-        <v>4.1501376</v>
+        <v>76.13486918761564</v>
       </c>
       <c r="K27">
-        <v>4.091270399999999</v>
+        <v>76.07720951066777</v>
       </c>
       <c r="L27">
-        <v>4.0324032</v>
+        <v>91.3745356541331</v>
       </c>
       <c r="M27">
-        <v>3.973535999999999</v>
+        <v>91.3745356541331</v>
       </c>
       <c r="N27">
-        <v>3.679199999999999</v>
+        <v>91.37453565413313</v>
       </c>
       <c r="O27">
-        <v>3.532032</v>
+        <v>84.52383288828406</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>68.59585000000006</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>68.59585000000003</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>53.44335000000001</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3964,55 +3902,55 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28">
-        <v>75.36756595731134</v>
+        <v>18.91043404268865</v>
       </c>
       <c r="F28">
-        <v>75.36756595731134</v>
+        <v>37.95476737602201</v>
       </c>
       <c r="G28">
-        <v>79.14678398091911</v>
+        <v>83.15796434586686</v>
       </c>
       <c r="H28">
-        <v>79.1467839809191</v>
+        <v>92.97296434586687</v>
       </c>
       <c r="I28">
-        <v>79.1467839809191</v>
+        <v>101.6654643458669</v>
       </c>
       <c r="J28">
-        <v>79.1467839809191</v>
+        <v>98.97829016620976</v>
       </c>
       <c r="K28">
-        <v>78.43625203512701</v>
+        <v>97.99129048933217</v>
       </c>
       <c r="L28">
-        <v>94.29928398091911</v>
+        <v>101.6654643458669</v>
       </c>
       <c r="M28">
-        <v>94.2992839809191</v>
+        <v>132.2006744616114</v>
       </c>
       <c r="N28">
-        <v>94.29928398091909</v>
+        <v>136.9148652764311</v>
       </c>
       <c r="O28">
-        <v>87.44858121507005</v>
+        <v>155.0002223795964</v>
       </c>
       <c r="P28">
-        <v>68.59585</v>
+        <v>262.6903038461538</v>
       </c>
       <c r="Q28">
-        <v>68.59585</v>
+        <v>333.8687653846152</v>
       </c>
       <c r="R28">
-        <v>53.44335</v>
+        <v>420.1997269230769</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>544.8215384615384</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>616</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -4026,117 +3964,55 @@
         <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29">
-        <v>18.91043404268865</v>
+        <v>37.55117371210213</v>
       </c>
       <c r="F29">
-        <v>37.954767376022</v>
+        <v>38.08919020720561</v>
       </c>
       <c r="G29">
-        <v>90.0482160190809</v>
+        <v>38.62508990525956</v>
       </c>
       <c r="H29">
-        <v>90.0482160190809</v>
+        <v>22.84020447795741</v>
       </c>
       <c r="I29">
-        <v>98.74071601908091</v>
+        <v>29.47388990525958</v>
       </c>
       <c r="J29">
-        <v>98.74071601908086</v>
+        <v>18.29948990525959</v>
       </c>
       <c r="K29">
-        <v>95.63224796487297</v>
+        <v>16.49163376977015</v>
       </c>
       <c r="L29">
-        <v>98.74071601908089</v>
+        <v>15.06845327205117</v>
       </c>
       <c r="M29">
-        <v>131.3904261348254</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>133.8171234134158</v>
+        <v>2.04497403329162</v>
       </c>
       <c r="O29">
-        <v>156.0858240039852</v>
+        <v>0.4306286990381487</v>
       </c>
       <c r="P29">
-        <v>262.6903038461538</v>
+        <v>2.677647562304792</v>
       </c>
       <c r="Q29">
-        <v>333.8687653846153</v>
+        <v>13.39455739340011</v>
       </c>
       <c r="R29">
-        <v>420.1997269230768</v>
+        <v>20.94253203997812</v>
       </c>
       <c r="S29">
-        <v>544.8215384615386</v>
+        <v>41.3177423604378</v>
       </c>
       <c r="T29">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30">
-        <v>37.5511737121021</v>
-      </c>
-      <c r="F30">
-        <v>38.08919020720569</v>
-      </c>
-      <c r="G30">
-        <v>47.40563640814317</v>
-      </c>
-      <c r="H30">
-        <v>21.39698427795743</v>
-      </c>
-      <c r="I30">
-        <v>38.25443640814321</v>
-      </c>
-      <c r="J30">
-        <v>27.08003640814319</v>
-      </c>
-      <c r="K30">
-        <v>16.51943640814314</v>
-      </c>
-      <c r="L30">
-        <v>5.95883640814314</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>2.574067508384238</v>
-      </c>
-      <c r="O30">
-        <v>0.5103424752242287</v>
-      </c>
-      <c r="P30">
-        <v>2.708437178103269</v>
-      </c>
-      <c r="Q30">
-        <v>13.44543605572133</v>
-      </c>
-      <c r="R30">
-        <v>21.57813718821487</v>
-      </c>
-      <c r="S30">
-        <v>42.76119748090997</v>
-      </c>
-      <c r="T30">
-        <v>82.2398226593549</v>
+        <v>85.544915347623</v>
       </c>
     </row>
   </sheetData>
@@ -4146,7 +4022,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -4160,7 +4036,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1">
         <v>2007</v>
@@ -4222,7 +4098,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>3911.441860465116</v>
@@ -4234,19 +4110,19 @@
         <v>3911.441860465116</v>
       </c>
       <c r="H2">
-        <v>3715.869767441859</v>
+        <v>3715.86976744186</v>
       </c>
       <c r="I2">
-        <v>3520.297674418604</v>
+        <v>3520.297674418603</v>
       </c>
       <c r="J2">
-        <v>3324.725581395348</v>
+        <v>3324.725581395349</v>
       </c>
       <c r="K2">
         <v>3129.153488372092</v>
       </c>
       <c r="L2">
-        <v>2933.581395348837</v>
+        <v>2933.581395348836</v>
       </c>
       <c r="M2">
         <v>2738.009302325582</v>
@@ -4267,7 +4143,7 @@
         <v>977.8604651162793</v>
       </c>
       <c r="S2">
-        <v>488.9302325581395</v>
+        <v>488.9302325581394</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4284,7 +4160,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>52.15255813953488</v>
@@ -4296,7 +4172,7 @@
         <v>52.15255813953488</v>
       </c>
       <c r="H3">
-        <v>49.54493023255813</v>
+        <v>49.54493023255812</v>
       </c>
       <c r="I3">
         <v>46.93730232558138</v>
@@ -4308,13 +4184,13 @@
         <v>41.72204651162789</v>
       </c>
       <c r="L3">
-        <v>39.11441860465115</v>
+        <v>39.11441860465116</v>
       </c>
       <c r="M3">
-        <v>36.50679069767443</v>
+        <v>36.50679069767442</v>
       </c>
       <c r="N3">
-        <v>33.89916279069768</v>
+        <v>33.89916279069767</v>
       </c>
       <c r="O3">
         <v>32.5953488372093</v>
@@ -4346,7 +4222,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -4361,34 +4237,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1641.410391120507</v>
+        <v>1641.410391120508</v>
       </c>
       <c r="J4">
-        <v>2624.729841437635</v>
+        <v>2624.729841437633</v>
       </c>
       <c r="K4">
         <v>3983.852283298094</v>
       </c>
       <c r="L4">
-        <v>7436.883751536159</v>
+        <v>7436.419104861104</v>
       </c>
       <c r="M4">
-        <v>6981.943674737231</v>
+        <v>6981.479028062177</v>
       </c>
       <c r="N4">
-        <v>6522.730744549133</v>
+        <v>6512.935331095498</v>
       </c>
       <c r="O4">
-        <v>7187.083120536255</v>
+        <v>7189.302945554677</v>
       </c>
       <c r="P4">
-        <v>10710.88250493541</v>
+        <v>10709.78906825241</v>
       </c>
       <c r="Q4">
-        <v>12531.37002521546</v>
+        <v>12533.13208750695</v>
       </c>
       <c r="R4">
-        <v>14028.93554282017</v>
+        <v>14027.45538003398</v>
       </c>
       <c r="S4">
         <v>15827.05726744186</v>
@@ -4408,7 +4284,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4423,40 +4299,40 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>21.88547188160676</v>
+        <v>21.88547188160677</v>
       </c>
       <c r="J5">
-        <v>34.99639788583513</v>
+        <v>34.99639788583512</v>
       </c>
       <c r="K5">
-        <v>53.1180304439746</v>
+        <v>53.11803044397458</v>
       </c>
       <c r="L5">
-        <v>99.15845002048214</v>
+        <v>99.15225473148138</v>
       </c>
       <c r="M5">
-        <v>93.09258232982975</v>
+        <v>93.08638704082902</v>
       </c>
       <c r="N5">
-        <v>86.96974326065511</v>
+        <v>86.83913774793997</v>
       </c>
       <c r="O5">
-        <v>95.82777494048339</v>
+        <v>95.85737260739569</v>
       </c>
       <c r="P5">
-        <v>142.8117667324721</v>
+        <v>142.7971875766988</v>
       </c>
       <c r="Q5">
-        <v>167.0849336695395</v>
+        <v>167.1084278334259</v>
       </c>
       <c r="R5">
-        <v>187.052473904269</v>
+        <v>187.0327384004531</v>
       </c>
       <c r="S5">
-        <v>211.0274302325581</v>
+        <v>211.0274302325582</v>
       </c>
       <c r="T5">
-        <v>237.5</v>
+        <v>237.5000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -4470,16 +4346,16 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>311.1795885509839</v>
+        <v>311.1795885509838</v>
       </c>
       <c r="F6">
         <v>468.3680500894451</v>
       </c>
       <c r="G6">
-        <v>782.7449731663684</v>
+        <v>991.849588550984</v>
       </c>
       <c r="H6">
         <v>1167.34572450805</v>
@@ -4497,25 +4373,25 @@
         <v>1015.470483005367</v>
       </c>
       <c r="M6">
-        <v>947.7724508050087</v>
+        <v>947.7724508050089</v>
       </c>
       <c r="N6">
         <v>880.0744186046511</v>
       </c>
       <c r="O6">
-        <v>846.2254025044722</v>
+        <v>846.2254025044723</v>
       </c>
       <c r="P6">
-        <v>676.9803220035777</v>
+        <v>676.9803220035778</v>
       </c>
       <c r="Q6">
-        <v>507.7352415026835</v>
+        <v>507.7352415026834</v>
       </c>
       <c r="R6">
-        <v>338.490161001789</v>
+        <v>338.4901610017891</v>
       </c>
       <c r="S6">
-        <v>169.2450805008945</v>
+        <v>169.2450805008946</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4532,7 +4408,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>41.49061180679784</v>
@@ -4541,13 +4417,13 @@
         <v>62.44907334525934</v>
       </c>
       <c r="G7">
-        <v>104.3659964221824</v>
+        <v>132.2466118067979</v>
       </c>
       <c r="H7">
         <v>155.6460966010733</v>
       </c>
       <c r="I7">
-        <v>155.6460966010734</v>
+        <v>155.6460966010733</v>
       </c>
       <c r="J7">
         <v>153.4488729874776</v>
@@ -4571,13 +4447,13 @@
         <v>90.26404293381036</v>
       </c>
       <c r="Q7">
-        <v>67.6980322003578</v>
+        <v>67.69803220035777</v>
       </c>
       <c r="R7">
-        <v>45.13202146690521</v>
+        <v>45.1320214669052</v>
       </c>
       <c r="S7">
-        <v>22.5660107334526</v>
+        <v>22.56601073345261</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4594,7 +4470,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4606,19 +4482,19 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.1978253756544</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0.3956507513088</v>
       </c>
       <c r="J8">
-        <v>0.5934761269632002</v>
+        <v>0.5934761269632001</v>
       </c>
       <c r="K8">
-        <v>0.7913015026176001</v>
+        <v>0.5934761269632001</v>
       </c>
       <c r="L8">
-        <v>0.8908225689570139</v>
+        <v>0.86006184576</v>
       </c>
       <c r="M8">
         <v>1.0837002279168</v>
@@ -4627,22 +4503,22 @@
         <v>1.2643169325696</v>
       </c>
       <c r="O8">
-        <v>1.354625284896</v>
+        <v>1.281060969919634</v>
       </c>
       <c r="P8">
+        <v>0.8383682523840001</v>
+      </c>
+      <c r="Q8">
         <v>0.8383682523840003</v>
       </c>
-      <c r="Q8">
-        <v>0.8383682523840001</v>
-      </c>
       <c r="R8">
-        <v>0.8659019607846401</v>
+        <v>0.9029007686400002</v>
       </c>
       <c r="S8">
-        <v>0.8763004003590501</v>
+        <v>0.8661229426055789</v>
       </c>
       <c r="T8">
-        <v>0.8820349298092802</v>
+        <v>0.8857993136844803</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -4656,7 +4532,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4668,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>85.36925826316801</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>170.738516526336</v>
@@ -4677,10 +4553,10 @@
         <v>256.107774789504</v>
       </c>
       <c r="K9">
-        <v>341.477033052672</v>
+        <v>256.107774789504</v>
       </c>
       <c r="L9">
-        <v>384.4242009114499</v>
+        <v>371.1497657472</v>
       </c>
       <c r="M9">
         <v>467.6583291240961</v>
@@ -4689,7 +4565,7 @@
         <v>545.601383978112</v>
       </c>
       <c r="O9">
-        <v>584.5729114051201</v>
+        <v>552.827080096088</v>
       </c>
       <c r="P9">
         <v>361.7881458364801</v>
@@ -4698,13 +4574,13 @@
         <v>361.7881458364801</v>
       </c>
       <c r="R9">
-        <v>373.6700000001408</v>
+        <v>389.6364086208</v>
       </c>
       <c r="S9">
-        <v>378.1573266164824</v>
+        <v>373.7653621551767</v>
       </c>
       <c r="T9">
-        <v>380.6319966330816</v>
+        <v>382.2564730592256</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -4718,7 +4594,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4730,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0.8217361757952001</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>1.6434723515904</v>
@@ -4739,34 +4615,34 @@
         <v>2.465208527385601</v>
       </c>
       <c r="K10">
-        <v>3.286944703180801</v>
+        <v>2.465208527385601</v>
       </c>
       <c r="L10">
-        <v>3.700339901821443</v>
+        <v>3.57256459008</v>
       </c>
       <c r="M10">
         <v>4.501524023654401</v>
       </c>
       <c r="N10">
-        <v>5.2517780275968</v>
+        <v>5.251778027596802</v>
       </c>
       <c r="O10">
-        <v>5.626905029568</v>
+        <v>5.321330182743093</v>
       </c>
       <c r="P10">
         <v>3.482452740672001</v>
       </c>
       <c r="Q10">
-        <v>3.482452740672</v>
+        <v>3.482452740672001</v>
       </c>
       <c r="R10">
-        <v>3.59682352941312</v>
+        <v>3.750510885120001</v>
       </c>
       <c r="S10">
-        <v>3.640017047645284</v>
+        <v>3.597741453900097</v>
       </c>
       <c r="T10">
-        <v>3.66383740074624</v>
+        <v>3.67947407222784</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -4780,7 +4656,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4816,19 +4692,19 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>6.093603181551871</v>
+        <v>6.093603181551852</v>
       </c>
       <c r="Q11">
         <v>6.430143979007999</v>
       </c>
       <c r="R11">
-        <v>6.430143979007999</v>
+        <v>6.390312611018589</v>
       </c>
       <c r="S11">
-        <v>5.723918141914843</v>
+        <v>5.673273924096</v>
       </c>
       <c r="T11">
-        <v>3.50776685549102</v>
+        <v>3.38720102437637</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -4842,7 +4718,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4878,19 +4754,19 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2629.624142192768</v>
+        <v>2629.62414219276</v>
       </c>
       <c r="Q12">
         <v>2774.854440171914</v>
       </c>
       <c r="R12">
-        <v>2774.854440171914</v>
+        <v>2757.665672908791</v>
       </c>
       <c r="S12">
-        <v>2470.09082893402</v>
+        <v>2448.235901090658</v>
       </c>
       <c r="T12">
-        <v>1513.736312254201</v>
+        <v>1461.70751898088</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -4904,7 +4780,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4940,19 +4816,19 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>25.31189013875392</v>
+        <v>25.31189013875385</v>
       </c>
       <c r="Q13">
-        <v>26.70982883587938</v>
+        <v>26.70982883587939</v>
       </c>
       <c r="R13">
-        <v>26.70982883587939</v>
+        <v>26.54437546115414</v>
       </c>
       <c r="S13">
-        <v>23.7762753587232</v>
+        <v>23.56590706932185</v>
       </c>
       <c r="T13">
-        <v>14.57072386127039</v>
+        <v>14.06991194740954</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -4966,7 +4842,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4984,10 +4860,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.9226309536822856</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>1.845261907364572</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>2.005606405028571</v>
@@ -5002,19 +4878,19 @@
         <v>2.481712199794286</v>
       </c>
       <c r="P14">
-        <v>1.955018403668572</v>
+        <v>1.955018403668571</v>
       </c>
       <c r="Q14">
-        <v>1.955018403668572</v>
+        <v>1.955018403668571</v>
       </c>
       <c r="R14">
         <v>1.955018403668571</v>
       </c>
       <c r="S14">
-        <v>2.039289411048685</v>
+        <v>1.955018403668571</v>
       </c>
       <c r="T14">
-        <v>1.927834043178703</v>
+        <v>1.993035630225333</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -5028,7 +4904,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5046,19 +4922,19 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>398.1507423198172</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>796.3014846396345</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>865.4963024777144</v>
       </c>
       <c r="M15">
-        <v>1076.867988509632</v>
+        <v>1076.867988509633</v>
       </c>
       <c r="N15">
-        <v>999.5573137017601</v>
+        <v>999.5573137017602</v>
       </c>
       <c r="O15">
         <v>1070.954264680457</v>
@@ -5073,10 +4949,10 @@
         <v>843.6656341985145</v>
       </c>
       <c r="S15">
-        <v>880.0318150756252</v>
+        <v>843.6656341985145</v>
       </c>
       <c r="T15">
-        <v>831.9345370948095</v>
+        <v>860.0715296587783</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -5090,7 +4966,7 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5108,13 +4984,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>3.832467038372571</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>7.664934076745144</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>8.330980451657144</v>
+        <v>8.330980451657142</v>
       </c>
       <c r="M16">
         <v>10.36557422094833</v>
@@ -5132,13 +5008,13 @@
         <v>8.120845676777144</v>
       </c>
       <c r="R16">
-        <v>8.120845676777146</v>
+        <v>8.120845676777142</v>
       </c>
       <c r="S16">
-        <v>8.470894476663771</v>
+        <v>8.120845676777144</v>
       </c>
       <c r="T16">
-        <v>8.007926025511534</v>
+        <v>8.278763387089846</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -5152,7 +5028,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5170,37 +5046,37 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>11.32223129584008</v>
+        <v>3.139640998034773</v>
       </c>
       <c r="K17">
-        <v>11.09295948627192</v>
+        <v>3.139640998034773</v>
       </c>
       <c r="L17">
-        <v>11.27042800295305</v>
+        <v>3.136578014226493</v>
       </c>
       <c r="M17">
-        <v>12.37324915605593</v>
+        <v>3.152709662137139</v>
       </c>
       <c r="N17">
-        <v>8.944894848879834</v>
+        <v>2.600748917739785</v>
       </c>
       <c r="O17">
-        <v>8.770577400429302</v>
+        <v>2.600748917739785</v>
       </c>
       <c r="P17">
-        <v>7.866675404639901</v>
+        <v>2.048791958198805</v>
       </c>
       <c r="Q17">
-        <v>7.903719877050682</v>
+        <v>2.048791958198806</v>
       </c>
       <c r="R17">
-        <v>8.150086327859128</v>
+        <v>2.020984773324026</v>
       </c>
       <c r="S17">
-        <v>8.847515703148753</v>
+        <v>1.941120554701413</v>
       </c>
       <c r="T17">
-        <v>6.996653288665027</v>
+        <v>1.682983731383933</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -5214,7 +5090,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5232,37 +5108,37 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>4885.978274589448</v>
+        <v>1354.875846075006</v>
       </c>
       <c r="K18">
-        <v>4787.038670614266</v>
+        <v>1354.875846075006</v>
       </c>
       <c r="L18">
-        <v>4863.623161274355</v>
+        <v>1353.554050754663</v>
       </c>
       <c r="M18">
-        <v>5339.532905036442</v>
+        <v>1360.515477276104</v>
       </c>
       <c r="N18">
-        <v>3860.066161708913</v>
+        <v>1122.323186809246</v>
       </c>
       <c r="O18">
-        <v>3784.84147818526</v>
+        <v>1122.323186809246</v>
       </c>
       <c r="P18">
-        <v>3394.773001540757</v>
+        <v>884.1325296534847</v>
       </c>
       <c r="Q18">
-        <v>3410.75911617341</v>
+        <v>884.1325296534847</v>
       </c>
       <c r="R18">
-        <v>3517.075715329977</v>
+        <v>872.1326598729065</v>
       </c>
       <c r="S18">
-        <v>3818.043314974193</v>
+        <v>837.6681778365328</v>
       </c>
       <c r="T18">
-        <v>3019.324996108524</v>
+        <v>726.2722102356818</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -5276,7 +5152,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5294,37 +5170,37 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>47.03080692118187</v>
+        <v>13.04158568414444</v>
       </c>
       <c r="K19">
-        <v>46.07844709682182</v>
+        <v>13.04158568414445</v>
       </c>
       <c r="L19">
-        <v>46.81562401226652</v>
+        <v>13.02886252063312</v>
       </c>
       <c r="M19">
-        <v>51.39657341746309</v>
+        <v>13.09587090426196</v>
       </c>
       <c r="N19">
-        <v>37.15571706457777</v>
+        <v>10.80311088907296</v>
       </c>
       <c r="O19">
-        <v>36.43162920178326</v>
+        <v>10.80311088907296</v>
       </c>
       <c r="P19">
-        <v>32.67695937311959</v>
+        <v>8.510366595595039</v>
       </c>
       <c r="Q19">
-        <v>32.83083641236437</v>
+        <v>8.510366595595039</v>
       </c>
       <c r="R19">
-        <v>33.85420474649177</v>
+        <v>8.394859827653645</v>
       </c>
       <c r="S19">
-        <v>36.75121907461791</v>
+        <v>8.063116150298177</v>
       </c>
       <c r="T19">
-        <v>29.06302135291627</v>
+        <v>6.990855499594798</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -5338,7 +5214,7 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5374,19 +5250,19 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>3.832204701414286</v>
+        <v>4.622811471950958</v>
       </c>
       <c r="Q20">
-        <v>3.832204701414286</v>
+        <v>4.622811471950958</v>
       </c>
       <c r="R20">
-        <v>5.099586609327721</v>
+        <v>10.37931793118742</v>
       </c>
       <c r="S20">
-        <v>5.099586609327722</v>
+        <v>10.37931793118742</v>
       </c>
       <c r="T20">
-        <v>3.577945679091131</v>
+        <v>8.137633219488496</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -5400,7 +5276,7 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5436,19 +5312,19 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1653.74372114878</v>
+        <v>1994.920950588067</v>
       </c>
       <c r="Q21">
-        <v>1653.74372114878</v>
+        <v>1994.920950588067</v>
       </c>
       <c r="R21">
-        <v>2200.667759871424</v>
+        <v>4479.074891843185</v>
       </c>
       <c r="S21">
-        <v>2200.667759871424</v>
+        <v>4479.074891843185</v>
       </c>
       <c r="T21">
-        <v>1544.021173823173</v>
+        <v>3511.701720102344</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -5462,7 +5338,7 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5498,19 +5374,19 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>15.91838875972088</v>
+        <v>19.20244765271936</v>
       </c>
       <c r="Q22">
-        <v>15.91838875972088</v>
+        <v>19.20244765271936</v>
       </c>
       <c r="R22">
-        <v>21.18289822336131</v>
+        <v>43.11408986800927</v>
       </c>
       <c r="S22">
-        <v>21.1828982233613</v>
+        <v>43.11408986800927</v>
       </c>
       <c r="T22">
-        <v>14.86223589776316</v>
+        <v>33.80247645018298</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -5524,7 +5400,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5563,16 +5439,16 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.912976299380086</v>
       </c>
       <c r="R23">
-        <v>6.2485539662144</v>
+        <v>5.46740328643444</v>
       </c>
       <c r="S23">
-        <v>6.2485539662144</v>
+        <v>5.249853727165994</v>
       </c>
       <c r="T23">
-        <v>3.124307873680368</v>
+        <v>2.700956477441352</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -5586,7 +5462,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5625,16 +5501,16 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>825.522849194022</v>
       </c>
       <c r="R24">
-        <v>2696.491365420214</v>
+        <v>2359.394802838247</v>
       </c>
       <c r="S24">
-        <v>2696.491365420214</v>
+        <v>2265.513800723171</v>
       </c>
       <c r="T24">
-        <v>1348.259013180528</v>
+        <v>1165.566602957383</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -5648,7 +5524,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5687,16 +5563,16 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>7.946209243578821</v>
       </c>
       <c r="R25">
-        <v>25.95553185965981</v>
+        <v>22.71075211288152</v>
       </c>
       <c r="S25">
-        <v>25.95553185965981</v>
+        <v>21.80708471284336</v>
       </c>
       <c r="T25">
-        <v>12.97789424451845</v>
+        <v>11.21935767552561</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -5710,40 +5586,40 @@
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26">
-        <v>851.9902777777778</v>
+        <v>851.9902777777779</v>
       </c>
       <c r="F26">
-        <v>567.1026944444445</v>
+        <v>567.1026944444446</v>
       </c>
       <c r="G26">
-        <v>295.1187500000003</v>
+        <v>295.1187500000001</v>
       </c>
       <c r="H26">
-        <v>596.5353472222224</v>
+        <v>596.5353472222222</v>
       </c>
       <c r="I26">
-        <v>495.2666666666664</v>
+        <v>495.2666666666661</v>
       </c>
       <c r="J26">
-        <v>386.4111805555558</v>
+        <v>386.411180555556</v>
       </c>
       <c r="K26">
-        <v>400.0977777777774</v>
+        <v>400.0977777777776</v>
       </c>
       <c r="L26">
-        <v>44.42833333333327</v>
+        <v>44.4283333333332</v>
       </c>
       <c r="M26">
-        <v>72.22638888888881</v>
+        <v>72.22638888888876</v>
       </c>
       <c r="N26">
-        <v>15.11291666666666</v>
+        <v>15.11291666666667</v>
       </c>
       <c r="O26">
-        <v>9.812268518518531</v>
+        <v>9.81226851851854</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5772,7 +5648,7 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27">
         <v>74945.51000000001</v>
@@ -5787,25 +5663,25 @@
         <v>52474.36150000001</v>
       </c>
       <c r="I27">
-        <v>43566.23999999996</v>
+        <v>43566.23999999995</v>
       </c>
       <c r="J27">
-        <v>33990.74350000003</v>
+        <v>33990.74350000005</v>
       </c>
       <c r="K27">
-        <v>35194.68799999997</v>
+        <v>35194.68799999999</v>
       </c>
       <c r="L27">
-        <v>3908.147999999994</v>
+        <v>3908.147999999989</v>
       </c>
       <c r="M27">
-        <v>6353.409999999993</v>
+        <v>6353.409999999991</v>
       </c>
       <c r="N27">
-        <v>1329.410999999999</v>
+        <v>1329.411000000001</v>
       </c>
       <c r="O27">
-        <v>863.1383333333347</v>
+        <v>863.1383333333353</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5834,40 +5710,40 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28">
         <v>1415.044722222222</v>
       </c>
       <c r="F28">
-        <v>941.8836055555555</v>
+        <v>941.8836055555558</v>
       </c>
       <c r="G28">
-        <v>490.1537500000004</v>
+        <v>490.1537500000003</v>
       </c>
       <c r="H28">
-        <v>990.7674027777782</v>
+        <v>990.767402777778</v>
       </c>
       <c r="I28">
-        <v>822.5733333333327</v>
+        <v>822.5733333333326</v>
       </c>
       <c r="J28">
-        <v>641.7785694444451</v>
+        <v>641.7785694444452</v>
       </c>
       <c r="K28">
-        <v>664.5102222222216</v>
+        <v>664.510222222222</v>
       </c>
       <c r="L28">
-        <v>73.78966666666653</v>
+        <v>73.78966666666645</v>
       </c>
       <c r="M28">
-        <v>119.958611111111</v>
+        <v>119.9586111111109</v>
       </c>
       <c r="N28">
-        <v>25.10058333333332</v>
+        <v>25.10058333333335</v>
       </c>
       <c r="O28">
-        <v>16.29689814814817</v>
+        <v>16.29689814814818</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5896,19 +5772,19 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>6.50297619047619</v>
+        <v>6.502976190476192</v>
       </c>
       <c r="G29">
         <v>6.502976190476191</v>
       </c>
       <c r="H29">
-        <v>13.00595238095238</v>
+        <v>13.00595238095237</v>
       </c>
       <c r="I29">
         <v>13.00595238095238</v>
@@ -5935,10 +5811,10 @@
         <v>5.202380952380952</v>
       </c>
       <c r="Q29">
-        <v>3.901785714285713</v>
+        <v>3.901785714285714</v>
       </c>
       <c r="R29">
-        <v>2.601190476190477</v>
+        <v>2.601190476190476</v>
       </c>
       <c r="S29">
         <v>1.300595238095238</v>
@@ -5958,19 +5834,19 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>572.0357142857143</v>
+        <v>572.0357142857142</v>
       </c>
       <c r="G30">
         <v>572.0357142857143</v>
       </c>
       <c r="H30">
-        <v>1144.071428571428</v>
+        <v>1144.071428571427</v>
       </c>
       <c r="I30">
         <v>1144.071428571428</v>
@@ -5988,13 +5864,13 @@
         <v>1716.107142857143</v>
       </c>
       <c r="N30">
-        <v>1716.107142857142</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="O30">
-        <v>1716.107142857142</v>
+        <v>1716.107142857143</v>
       </c>
       <c r="P30">
-        <v>457.6285714285714</v>
+        <v>457.6285714285713</v>
       </c>
       <c r="Q30">
         <v>343.2214285714286</v>
@@ -6020,7 +5896,7 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6032,40 +5908,40 @@
         <v>10.80059523809524</v>
       </c>
       <c r="H31">
-        <v>21.60119047619047</v>
+        <v>21.60119047619045</v>
       </c>
       <c r="I31">
-        <v>21.60119047619047</v>
+        <v>21.60119047619048</v>
       </c>
       <c r="J31">
-        <v>32.40178571428572</v>
+        <v>32.40178571428571</v>
       </c>
       <c r="K31">
         <v>32.40178571428571</v>
       </c>
       <c r="L31">
-        <v>32.40178571428571</v>
+        <v>32.40178571428572</v>
       </c>
       <c r="M31">
         <v>32.40178571428571</v>
       </c>
       <c r="N31">
-        <v>32.40178571428571</v>
+        <v>32.40178571428572</v>
       </c>
       <c r="O31">
         <v>32.40178571428571</v>
       </c>
       <c r="P31">
-        <v>8.640476190476189</v>
+        <v>8.640476190476187</v>
       </c>
       <c r="Q31">
         <v>6.480357142857143</v>
       </c>
       <c r="R31">
-        <v>4.320238095238096</v>
+        <v>4.320238095238095</v>
       </c>
       <c r="S31">
-        <v>2.160119047619047</v>
+        <v>2.160119047619048</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -6082,7 +5958,7 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E32">
         <v>80.66533090909091</v>
@@ -6091,40 +5967,40 @@
         <v>102.7881163636363</v>
       </c>
       <c r="G32">
-        <v>80.70957818181819</v>
+        <v>80.70957818181816</v>
       </c>
       <c r="H32">
-        <v>62.0547293852928</v>
+        <v>62.37844363636363</v>
       </c>
       <c r="I32">
-        <v>41.79004567967649</v>
+        <v>41.7900456796765</v>
       </c>
       <c r="J32">
-        <v>26.56868109808735</v>
+        <v>37.15649620284873</v>
       </c>
       <c r="K32">
-        <v>26.58459478874525</v>
+        <v>43.81485983921243</v>
       </c>
       <c r="L32">
-        <v>35.39269241021745</v>
+        <v>50.29988682170605</v>
       </c>
       <c r="M32">
-        <v>45.84551176011134</v>
+        <v>59.3198932199443</v>
       </c>
       <c r="N32">
-        <v>25.07009965275569</v>
+        <v>34.13043225389828</v>
       </c>
       <c r="O32">
-        <v>27.56690428154585</v>
+        <v>35.67329949541078</v>
       </c>
       <c r="P32">
-        <v>25.06268482213323</v>
+        <v>32.37330007359729</v>
       </c>
       <c r="Q32">
-        <v>24.66758243184219</v>
+        <v>29.35872727272728</v>
       </c>
       <c r="R32">
-        <v>6.429090909090908</v>
+        <v>6.429090909090909</v>
       </c>
       <c r="S32">
         <v>3.214545454545454</v>
@@ -6144,46 +6020,46 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33">
         <v>34810.1928</v>
       </c>
       <c r="F33">
-        <v>44357.0256</v>
+        <v>44357.02559999999</v>
       </c>
       <c r="G33">
-        <v>34829.28720000001</v>
+        <v>34829.28719999999</v>
       </c>
       <c r="H33">
-        <v>26779.00245011482</v>
+        <v>26918.6976</v>
       </c>
       <c r="I33">
-        <v>18034.01202022962</v>
+        <v>18034.01202022963</v>
       </c>
       <c r="J33">
-        <v>11465.40776617462</v>
+        <v>16034.45720753703</v>
       </c>
       <c r="K33">
-        <v>11472.27513575853</v>
+        <v>18907.79720753705</v>
       </c>
       <c r="L33">
-        <v>15273.30803240922</v>
+        <v>21706.33577459776</v>
       </c>
       <c r="M33">
-        <v>19784.10161340189</v>
+        <v>25598.81545876058</v>
       </c>
       <c r="N33">
-        <v>10818.71223476611</v>
+        <v>14728.59422648995</v>
       </c>
       <c r="O33">
-        <v>11896.17946303633</v>
+        <v>15394.40078225034</v>
       </c>
       <c r="P33">
-        <v>10815.51245016673</v>
+        <v>13970.32410868314</v>
       </c>
       <c r="Q33">
-        <v>10645.01057251036</v>
+        <v>12669.42</v>
       </c>
       <c r="R33">
         <v>2774.4</v>
@@ -6206,46 +6082,46 @@
         <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34">
-        <v>335.0713745454545</v>
+        <v>335.0713745454546</v>
       </c>
       <c r="F34">
-        <v>426.966021818182</v>
+        <v>426.9660218181818</v>
       </c>
       <c r="G34">
         <v>335.2551709090909</v>
       </c>
       <c r="H34">
-        <v>257.7657989850624</v>
+        <v>259.1104581818182</v>
       </c>
       <c r="I34">
-        <v>173.5894205155792</v>
+        <v>173.5894205155793</v>
       </c>
       <c r="J34">
-        <v>110.3622137920552</v>
+        <v>154.3423688426024</v>
       </c>
       <c r="K34">
-        <v>110.428316814788</v>
+        <v>182.0001870244209</v>
       </c>
       <c r="L34">
-        <v>147.0157992424417</v>
+        <v>208.9379914132405</v>
       </c>
       <c r="M34">
-        <v>190.4352026958471</v>
+        <v>246.4057102982302</v>
       </c>
       <c r="N34">
-        <v>104.137337019139</v>
+        <v>141.7725647469621</v>
       </c>
       <c r="O34">
-        <v>114.5086793233443</v>
+        <v>148.181397904014</v>
       </c>
       <c r="P34">
-        <v>104.1065369534765</v>
+        <v>134.4737079980195</v>
       </c>
       <c r="Q34">
-        <v>102.4653424091906</v>
+        <v>121.9516363636364</v>
       </c>
       <c r="R34">
         <v>26.70545454545454</v>
@@ -6268,7 +6144,7 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6307,16 +6183,16 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.186272749457279</v>
+        <v>3.516487927205289</v>
       </c>
       <c r="R35">
-        <v>13.30329217972297</v>
+        <v>11.8638783082221</v>
       </c>
       <c r="S35">
-        <v>13.44146509449314</v>
+        <v>12.06260184901313</v>
       </c>
       <c r="T35">
-        <v>4.070424716537508</v>
+        <v>4.184252143479826</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -6330,7 +6206,7 @@
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6369,16 +6245,16 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>1374.999240342718</v>
+        <v>1517.499790124744</v>
       </c>
       <c r="R36">
-        <v>5740.882240634295</v>
+        <v>5119.719793009691</v>
       </c>
       <c r="S36">
-        <v>5800.5091677005</v>
+        <v>5205.47664407413</v>
       </c>
       <c r="T36">
-        <v>1756.544819982725</v>
+        <v>1805.665732686294</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -6392,7 +6268,7 @@
         <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6431,16 +6307,16 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>13.23528680543793</v>
+        <v>14.60694985146812</v>
       </c>
       <c r="R37">
-        <v>55.25982905423386</v>
+        <v>49.2807252803072</v>
       </c>
       <c r="S37">
-        <v>55.83377808481767</v>
+        <v>50.10619229590072</v>
       </c>
       <c r="T37">
-        <v>16.90791805330965</v>
+        <v>17.3807396729162</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -6454,7 +6330,7 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -6463,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>3.810614995950744</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -6496,13 +6372,13 @@
         <v>0</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>5.468529491654345</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>0.7099743134445931</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>23.61615904638872</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -6516,7 +6392,7 @@
         <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6525,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>1644.426932867975</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -6558,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2359.880803706222</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>306.3812229557052</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>10191.28094232621</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -6578,7 +6454,7 @@
         <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6587,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>15.82870844471847</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -6620,13 +6496,13 @@
         <v>0</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>22.71543019610267</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>2.949124071231386</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>98.09789142346085</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -6640,7 +6516,7 @@
         <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6682,13 +6558,13 @@
         <v>0</v>
       </c>
       <c r="R41">
-        <v>1.032789657979821</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>0.1387567216912674</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="T41">
-        <v>24.77511423223991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -6702,7 +6578,7 @@
         <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -6744,13 +6620,13 @@
         <v>0</v>
       </c>
       <c r="R42">
-        <v>445.688460097446</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>59.87886220677002</v>
+        <v>333.9285714285714</v>
       </c>
       <c r="T42">
-        <v>10691.41468022045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -6764,7 +6640,7 @@
         <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -6806,13 +6682,13 @@
         <v>0</v>
       </c>
       <c r="R43">
-        <v>4.290049348531567</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>0.5763740747175724</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="T43">
-        <v>102.9120129646889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -6826,43 +6702,43 @@
         <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>134.92332</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>128.182257</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>120.73698</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>106.1055855</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>97.7949855</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>117.1863855</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>100.405899</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>74.13055199999999</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>73.34104500000001</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>61.79084999999999</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>54.698625</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>19.2375</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -6871,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>0.7738095238095238</v>
+        <v>0</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -6888,43 +6764,43 @@
         <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>13250.8026</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>12588.763635</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>11857.5639</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>10420.61645249999</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>9604.433452499998</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>11508.8604525</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>9860.850944999998</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>7280.352359999999</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>7202.814974999999</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>6068.471749999998</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>5371.945208333334</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1889.3125</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -6933,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>333.9285714285714</v>
+        <v>0</v>
       </c>
       <c r="T45">
         <v>0</v>
@@ -6950,43 +6826,43 @@
         <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>529.6989600000001</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>503.2340459999999</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>474.00444</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>416.5626689999999</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>383.935869</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>460.065069</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>394.186122</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>291.031056</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>287.9315100000001</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>242.5863</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>214.74275</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>75.52500000000002</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -6995,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="S46">
-        <v>3.214285714285714</v>
+        <v>0</v>
       </c>
       <c r="T46">
         <v>0</v>
@@ -7012,52 +6888,52 @@
         <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E47">
-        <v>134.92332</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>128.182257</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>120.73698</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>106.1055855</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>97.79498549999997</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>117.1863855</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>100.405899</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>74.13055199999999</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>73.34104500000001</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>61.79084999999999</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>54.69862499999999</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>19.2375</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>13.57402880549683</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>9.049352536997887</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>4.524676268498942</v>
       </c>
       <c r="T47">
         <v>0</v>
@@ -7074,52 +6950,52 @@
         <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E48">
-        <v>13250.8026</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>12588.763635</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>11857.5639</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>10420.61645249999</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>9604.433452499998</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>11508.8604525</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>9860.850945000002</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>7280.352359999997</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>7202.814975</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>6068.471749999999</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>5371.945208333332</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>1889.3125</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1333.103693181818</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>888.7357954545455</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>444.3678977272725</v>
       </c>
       <c r="T48">
         <v>0</v>
@@ -7136,240 +7012,54 @@
         <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E49">
-        <v>529.6989599999998</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>503.234046</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>474.00444</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>416.562669</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>383.935869</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>460.0650689999999</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>394.1861220000001</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>291.031056</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>287.93151</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>242.5863</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>214.74275</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>75.52500000000001</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>53.29063160676534</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>35.52708773784355</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>17.76354386892177</v>
       </c>
       <c r="T49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
-      <c r="A50" t="s">
-        <v>3</v>
-      </c>
-      <c r="B50" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>13.57402880549683</v>
-      </c>
-      <c r="R50">
-        <v>9.049352536997885</v>
-      </c>
-      <c r="S50">
-        <v>4.524676268498942</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
-      <c r="A51" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" t="s">
-        <v>40</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>1333.103693181818</v>
-      </c>
-      <c r="R51">
-        <v>888.7357954545452</v>
-      </c>
-      <c r="S51">
-        <v>444.3678977272726</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20">
-      <c r="A52" t="s">
-        <v>3</v>
-      </c>
-      <c r="B52" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" t="s">
-        <v>25</v>
-      </c>
-      <c r="D52" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>53.29063160676532</v>
-      </c>
-      <c r="R52">
-        <v>35.52708773784354</v>
-      </c>
-      <c r="S52">
-        <v>17.76354386892177</v>
-      </c>
-      <c r="T52">
         <v>0</v>
       </c>
     </row>

--- a/database_postprocessing.xlsx
+++ b/database_postprocessing.xlsx
@@ -1,22 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Riccardo\PoliTo\anno4\Models and scenarios\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21436BE-6819-4AF9-A2F1-ED7D1958BF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Output_CapacityByPeriodAndTech" sheetId="1" r:id="rId1"/>
     <sheet name="Output_VFlow_Out" sheetId="2" r:id="rId2"/>
     <sheet name="Output_Emissions" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="47">
   <si>
     <t>file</t>
   </si>
@@ -137,12 +178,33 @@
   <si>
     <t>ELC_CO2</t>
   </si>
+  <si>
+    <t>Biogas</t>
+  </si>
+  <si>
+    <t>Natural gas</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t>Nuclear</t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,17 +263,3337 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="it-IT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_CapacityByPeriodAndTech!$C$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nuclear</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$1:$S$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$39:$S$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7.8740052312157616</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.8740052312157616</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.8740052312157616</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.8740052312157616</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.718492466933343</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.6876526468880266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BC0D-4E73-9AD8-0E407ED7D442}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_CapacityByPeriodAndTech!$C$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Biogas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$1:$S$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$33:$S$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.87543281312130117</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87543281312130117</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.87543281312130117</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.87543281312130117</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.34106855612363141</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.75441870803952E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BC0D-4E73-9AD8-0E407ED7D442}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_CapacityByPeriodAndTech!$C$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Natural gas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$1:$S$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$34:$S$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>22.957000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.957000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.957000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.957000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5914000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BC0D-4E73-9AD8-0E407ED7D442}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_CapacityByPeriodAndTech!$C$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Solar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$1:$S$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$35:$S$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.76212092436800227</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76212092436800227</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76212092436800227</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76212092436800227</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36865759542658988</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BC0D-4E73-9AD8-0E407ED7D442}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_CapacityByPeriodAndTech!$C$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Wind</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$1:$S$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$36:$S$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>12.649264959504411</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.26559080584113</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.26559080584113</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.9979701744835801</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-BC0D-4E73-9AD8-0E407ED7D442}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_CapacityByPeriodAndTech!$C$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Coal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$1:$S$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$37:$S$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>11.212999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.212999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.212999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.212999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2425999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-BC0D-4E73-9AD8-0E407ED7D442}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_CapacityByPeriodAndTech!$C$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Oil</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$1:$S$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_CapacityByPeriodAndTech!$N$38:$S$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8.3149999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.3149999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.3149999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.3149999999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.663</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-BC0D-4E73-9AD8-0E407ED7D442}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1284270831"/>
+        <c:axId val="1284271791"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1284270831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1284271791"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1284271791"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Installed capacity (GW)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1284270831"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="it-IT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="it-IT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_VFlow_Out!$D$32</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nuclear</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$1:$T$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$32:$T$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>215.94100000000009</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202.70083333333341</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>136.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>135.625</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>134.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>133.875</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>133</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-315D-403C-8241-16D032026213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_VFlow_Out!$D$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Biogas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-1637-4A8B-ADC9-B42A080B58CD}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$1:$T$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$33:$T$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>10.67823627906977</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.267534883720932</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2140279069767423</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.1605209302325594</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.1070139534883729</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0535069767441865</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-315D-403C-8241-16D032026213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_VFlow_Out!$D$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Natural gas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$1:$T$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$34:$T$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>144.39798261264659</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>150.9254978651995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>136.9639618498347</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>124.21</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-315D-403C-8241-16D032026213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_VFlow_Out!$D$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Solar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$1:$T$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$35:$T$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3.6792000000000011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5320320000000009</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-315D-403C-8241-16D032026213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_VFlow_Out!$D$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Wind</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$1:$T$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$36:$T$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>91.374535654133126</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>84.523832888284062</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.595850000000056</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68.595850000000027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.443350000000009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-315D-403C-8241-16D032026213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_VFlow_Out!$D$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Coal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$1:$T$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$37:$T$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>4.7310000000000034</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.071666666666673</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-315D-403C-8241-16D032026213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output_VFlow_Out!$D$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Oil</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="dashDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$1:$T$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Output_VFlow_Out!$N$38:$T$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>30.513999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.01166666666667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-315D-403C-8241-16D032026213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1284299631"/>
+        <c:axId val="1284316431"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1284299631"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1284316431"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1284316431"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Production (PJ)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1284299631"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="it-IT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Grafico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6687763F-E8E4-1E59-C66D-25E809EB5790}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>71436</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Grafico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09D02FDE-2F81-56B9-B8B2-F66978E8CC5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -249,7 +3631,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -283,6 +3665,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -317,9 +3700,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -492,11 +3876,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,7 +3942,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -566,55 +3953,55 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="E2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="F2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="G2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="H2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="I2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="J2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="K2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="L2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="M2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="N2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="O2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="P2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="Q2">
-        <v>0.2919404283294496</v>
+        <v>0.29194042832944961</v>
       </c>
       <c r="R2">
-        <v>0.08477617133177981</v>
+        <v>8.4776171331779809E-2</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -640,40 +4027,40 @@
         <v>0.1156140475741613</v>
       </c>
       <c r="I3">
-        <v>0.1845041074831422</v>
+        <v>0.18450410748314219</v>
       </c>
       <c r="J3">
         <v>0.2765267107956052</v>
       </c>
       <c r="K3">
-        <v>0.568072954980921</v>
+        <v>0.56807295498092103</v>
       </c>
       <c r="L3">
-        <v>0.5187276692569499</v>
+        <v>0.51872766925694991</v>
       </c>
       <c r="M3">
-        <v>0.4958910540372594</v>
+        <v>0.49589105403725942</v>
       </c>
       <c r="N3">
-        <v>0.5443572975042028</v>
+        <v>0.54435729750420281</v>
       </c>
       <c r="O3">
-        <v>0.8434902016956519</v>
+        <v>0.84349020169565192</v>
       </c>
       <c r="P3">
-        <v>1.002976572934977</v>
+        <v>1.0029765729349771</v>
       </c>
       <c r="Q3">
-        <v>1.115153929707554</v>
+        <v>1.1151539297075539</v>
       </c>
       <c r="R3">
-        <v>1.275111733751409</v>
+        <v>1.2751117337514091</v>
       </c>
       <c r="S3">
         <v>1.50685402533556</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -684,10 +4071,10 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>0.409</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="E4">
-        <v>0.409</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="F4">
         <v>0.4957714493898755</v>
@@ -726,13 +4113,13 @@
         <v>0.5834923847918515</v>
       </c>
       <c r="R4">
-        <v>0.2562923847918516</v>
+        <v>0.25629238479185162</v>
       </c>
       <c r="S4">
-        <v>0.0175441870803952</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+        <v>1.75441870803952E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -755,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="I5">
         <v>0.4</v>
@@ -764,13 +4151,13 @@
         <v>0.4</v>
       </c>
       <c r="K5">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L5">
         <v>0.8</v>
       </c>
       <c r="M5">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -791,7 +4178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -850,7 +4237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -882,13 +4269,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L7">
         <v>0.8</v>
       </c>
       <c r="M7">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -909,7 +4296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -923,22 +4310,22 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.8648733377620116</v>
+        <v>0.86487333776201158</v>
       </c>
       <c r="F8">
-        <v>0.8648733377620116</v>
+        <v>0.86487333776201158</v>
       </c>
       <c r="G8">
-        <v>0.8648733377620116</v>
+        <v>0.86487333776201158</v>
       </c>
       <c r="H8">
-        <v>0.8648733377620116</v>
+        <v>0.86487333776201158</v>
       </c>
       <c r="I8">
-        <v>0.8648733377620116</v>
+        <v>0.86487333776201158</v>
       </c>
       <c r="J8">
-        <v>0.8648733377620116</v>
+        <v>0.86487333776201158</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -968,7 +4355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1012,22 +4399,22 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>3.035394749369558</v>
+        <v>3.0353947493695581</v>
       </c>
       <c r="P9">
-        <v>3.035394749369558</v>
+        <v>3.0353947493695581</v>
       </c>
       <c r="Q9">
-        <v>6.949064499903466</v>
+        <v>6.9490644999034661</v>
       </c>
       <c r="R9">
-        <v>6.949064499903466</v>
+        <v>6.9490644999034661</v>
       </c>
       <c r="S9">
-        <v>5.431367125218687</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>5.4313671252186868</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1074,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0.7122314397278249</v>
+        <v>0.71223143972782488</v>
       </c>
       <c r="Q10">
-        <v>2.035601024190283</v>
+        <v>2.0356010241902829</v>
       </c>
       <c r="R10">
-        <v>2.035601024190283</v>
+        <v>2.0356010241902829</v>
       </c>
       <c r="S10">
-        <v>2.035601024190283</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
+        <v>2.0356010241902829</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1097,55 +4484,55 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="E11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="F11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="G11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="H11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="I11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="J11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="K11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="L11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="M11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="N11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="O11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="P11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="Q11">
-        <v>11.213</v>
+        <v>11.212999999999999</v>
       </c>
       <c r="R11">
-        <v>2.2426</v>
+        <v>2.2425999999999999</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1192,19 +4579,19 @@
         <v>0.3132702002380513</v>
       </c>
       <c r="P12">
-        <v>0.2704860689370892</v>
+        <v>0.27048606893708921</v>
       </c>
       <c r="Q12">
-        <v>0.1436800894185749</v>
+        <v>0.14368008941857491</v>
       </c>
       <c r="R12">
-        <v>0.02038538020810549</v>
+        <v>2.0385380208105489E-2</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1215,46 +4602,46 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="E13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="F13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="G13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="H13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="I13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="J13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="K13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="L13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="M13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="N13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="O13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="P13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="Q13">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="R13">
         <v>0.1062</v>
@@ -1263,7 +4650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1274,55 +4661,55 @@
         <v>17</v>
       </c>
       <c r="D14">
-        <v>16.658</v>
+        <v>16.658000000000001</v>
       </c>
       <c r="E14">
-        <v>16.658</v>
+        <v>16.658000000000001</v>
       </c>
       <c r="F14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="G14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="H14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="I14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="J14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="K14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="L14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="M14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="N14">
-        <v>17.4497687288999</v>
+        <v>17.449768728899901</v>
       </c>
       <c r="O14">
-        <v>28.95452681388147</v>
+        <v>28.954526813881468</v>
       </c>
       <c r="P14">
-        <v>29.43558985099927</v>
+        <v>29.435589850999271</v>
       </c>
       <c r="Q14">
-        <v>31.36736098960356</v>
+        <v>31.367360989603561</v>
       </c>
       <c r="R14">
-        <v>32.0889268983459</v>
+        <v>32.088926898345903</v>
       </c>
       <c r="S14">
-        <v>27.965558169446</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
+        <v>27.965558169445998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1333,55 +4720,55 @@
         <v>18</v>
       </c>
       <c r="D15">
-        <v>1.809</v>
+        <v>1.8089999999999999</v>
       </c>
       <c r="E15">
-        <v>1.809</v>
+        <v>1.8089999999999999</v>
       </c>
       <c r="F15">
-        <v>2.409869185902577</v>
+        <v>2.4098691859025769</v>
       </c>
       <c r="G15">
-        <v>2.409869185902577</v>
+        <v>2.4098691859025769</v>
       </c>
       <c r="H15">
-        <v>2.409869185902577</v>
+        <v>2.4098691859025769</v>
       </c>
       <c r="I15">
-        <v>2.409869185902577</v>
+        <v>2.4098691859025769</v>
       </c>
       <c r="J15">
-        <v>2.409869185902577</v>
+        <v>2.4098691859025769</v>
       </c>
       <c r="K15">
-        <v>2.409869185902577</v>
+        <v>2.4098691859025769</v>
       </c>
       <c r="L15">
-        <v>2.409869185902577</v>
+        <v>2.4098691859025769</v>
       </c>
       <c r="M15">
-        <v>5.533770155920489</v>
+        <v>5.5337701559204886</v>
       </c>
       <c r="N15">
-        <v>8.819308832566001</v>
+        <v>8.8193088325660014</v>
       </c>
       <c r="O15">
-        <v>9.003176815955396</v>
+        <v>9.0031768159553955</v>
       </c>
       <c r="P15">
-        <v>9.003176815955396</v>
+        <v>9.0031768159553955</v>
       </c>
       <c r="Q15">
-        <v>9.003176815955396</v>
+        <v>9.0031768159553955</v>
       </c>
       <c r="R15">
-        <v>7.555976815955395</v>
+        <v>7.5559768159553951</v>
       </c>
       <c r="S15">
-        <v>6.593307630052818</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
+        <v>6.5933076300528182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1440,7 +4827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1487,19 +4874,19 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.01292664006659</v>
+        <v>1.0129266400665899</v>
       </c>
       <c r="Q17">
-        <v>4.023562698678884</v>
+        <v>4.0235626986788837</v>
       </c>
       <c r="R17">
-        <v>4.023562698678884</v>
+        <v>4.0235626986788837</v>
       </c>
       <c r="S17">
-        <v>4.023562698678884</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+        <v>4.0235626986788837</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1516,25 +4903,25 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1.855963194726039</v>
+        <v>1.8559631947260391</v>
       </c>
       <c r="G18">
-        <v>4.112468086760503</v>
+        <v>4.1124680867605026</v>
       </c>
       <c r="H18">
-        <v>4.112468086760503</v>
+        <v>4.1124680867605026</v>
       </c>
       <c r="I18">
-        <v>4.502873388431286</v>
+        <v>4.5028733884312864</v>
       </c>
       <c r="J18">
-        <v>4.502873388431286</v>
+        <v>4.5028733884312864</v>
       </c>
       <c r="K18">
-        <v>4.633408597248515</v>
+        <v>4.6334085972485148</v>
       </c>
       <c r="L18">
-        <v>9.415958929075218</v>
+        <v>9.4159589290752184</v>
       </c>
       <c r="M18">
         <v>15.90951289131835</v>
@@ -1552,13 +4939,13 @@
         <v>12.69964676137163</v>
       </c>
       <c r="R18">
-        <v>12.83424807476145</v>
+        <v>12.834248074761449</v>
       </c>
       <c r="S18">
         <v>13.82499186137159</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1569,55 +4956,55 @@
         <v>22</v>
       </c>
       <c r="D19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="E19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="F19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="G19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="H19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="I19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="J19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="K19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="L19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="M19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="N19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="O19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="P19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="Q19">
-        <v>6.547</v>
+        <v>6.5469999999999997</v>
       </c>
       <c r="R19">
-        <v>1.3094</v>
+        <v>1.3093999999999999</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1628,46 +5015,46 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="E20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="F20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="G20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="H20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="I20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="J20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="K20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="L20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="M20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="N20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="O20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="P20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="Q20">
-        <v>8.315</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="R20">
         <v>1.663</v>
@@ -1676,7 +5063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1723,19 +5110,19 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0.2658962635839847</v>
+        <v>0.26589626358398472</v>
       </c>
       <c r="Q21">
-        <v>0.2658962635839847</v>
+        <v>0.26589626358398472</v>
       </c>
       <c r="R21">
-        <v>0.2658962635839847</v>
+        <v>0.26589626358398472</v>
       </c>
       <c r="S21">
-        <v>0.2658962635839847</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>0.26589626358398472</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1746,55 +5133,55 @@
         <v>25</v>
       </c>
       <c r="D22">
-        <v>7.716</v>
+        <v>7.7160000000000002</v>
       </c>
       <c r="E22">
-        <v>7.716</v>
+        <v>7.7160000000000002</v>
       </c>
       <c r="F22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="G22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="H22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="I22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="J22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="K22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="L22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="M22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="N22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="O22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="P22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="Q22">
-        <v>7.874005231215762</v>
+        <v>7.8740052312157616</v>
       </c>
       <c r="R22">
         <v>4.718492466933343</v>
       </c>
       <c r="S22">
-        <v>4.687652646888027</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
+        <v>4.6876526468880266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1853,7 +5240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1912,7 +5299,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1926,28 +5313,28 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.65577484449026</v>
+        <v>0.65577484449026002</v>
       </c>
       <c r="F25">
-        <v>2.666133590943942</v>
+        <v>2.6661335909439421</v>
       </c>
       <c r="G25">
-        <v>5.110354661171913</v>
+        <v>5.1103546611719128</v>
       </c>
       <c r="H25">
-        <v>5.728218218302898</v>
+        <v>5.7282182183028976</v>
       </c>
       <c r="I25">
-        <v>5.936456649270218</v>
+        <v>5.9364566492702178</v>
       </c>
       <c r="J25">
-        <v>5.936456649270218</v>
+        <v>5.9364566492702178</v>
       </c>
       <c r="K25">
-        <v>9.651165434743177</v>
+        <v>9.6511654347431772</v>
       </c>
       <c r="L25">
-        <v>15.98015258734092</v>
+        <v>15.980152587340919</v>
       </c>
       <c r="M25">
         <v>17.91834212651418</v>
@@ -1959,19 +5346,19 @@
         <v>24.48233196999114</v>
       </c>
       <c r="P25">
-        <v>26.13961211914179</v>
+        <v>26.139612119141791</v>
       </c>
       <c r="Q25">
-        <v>26.87368932578686</v>
+        <v>26.873689325786859</v>
       </c>
       <c r="R25">
         <v>28.9177559773951</v>
       </c>
       <c r="S25">
-        <v>31.11145256659376</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19">
+        <v>31.111452566593758</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1982,55 +5369,55 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>0.3060747959710572</v>
+        <v>0.30607479597105719</v>
       </c>
       <c r="E26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="F26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="G26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="H26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="I26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="J26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="K26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="L26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="M26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="N26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="O26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="P26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="Q26">
-        <v>0.7621209243680023</v>
+        <v>0.76212092436800227</v>
       </c>
       <c r="R26">
-        <v>0.3686575954265899</v>
+        <v>0.36865759542658988</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -2071,7 +5458,7 @@
         <v>13.67449478502083</v>
       </c>
       <c r="N27">
-        <v>12.64926495950441</v>
+        <v>12.649264959504411</v>
       </c>
       <c r="O27">
         <v>10.26559080584113</v>
@@ -2080,7 +5467,7 @@
         <v>10.26559080584113</v>
       </c>
       <c r="Q27">
-        <v>7.99797017448358</v>
+        <v>7.9979701744835801</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2089,7 +5476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -2100,28 +5487,28 @@
         <v>31</v>
       </c>
       <c r="D28">
-        <v>2.830007614791414</v>
+        <v>2.8300076147914139</v>
       </c>
       <c r="E28">
-        <v>5.680053691486149</v>
+        <v>5.6800536914861492</v>
       </c>
       <c r="F28">
-        <v>12.44485831462683</v>
+        <v>12.444858314626829</v>
       </c>
       <c r="G28">
         <v>13.91370480839185</v>
       </c>
       <c r="H28">
-        <v>15.21456554675684</v>
+        <v>15.214565546756839</v>
       </c>
       <c r="I28">
-        <v>15.21456554675684</v>
+        <v>15.214565546756839</v>
       </c>
       <c r="J28">
-        <v>15.21456554675684</v>
+        <v>15.214565546756839</v>
       </c>
       <c r="K28">
-        <v>15.21456554675684</v>
+        <v>15.214565546756839</v>
       </c>
       <c r="L28">
         <v>19.78425849784081</v>
@@ -2130,25 +5517,25 @@
         <v>20.4897523999587</v>
       </c>
       <c r="N28">
-        <v>23.19628458227889</v>
+        <v>23.196284582278889</v>
       </c>
       <c r="O28">
-        <v>39.31245356602022</v>
+        <v>39.312453566020217</v>
       </c>
       <c r="P28">
-        <v>49.96454054129856</v>
+        <v>49.964540541298561</v>
       </c>
       <c r="Q28">
         <v>62.88424814793445</v>
       </c>
       <c r="R28">
-        <v>81.53430529769638</v>
+        <v>81.534305297696378</v>
       </c>
       <c r="S28">
-        <v>92.18639227297471</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
+        <v>92.186392272974715</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -2159,65 +5546,447 @@
         <v>32</v>
       </c>
       <c r="D29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="E29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="F29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="G29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="H29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="I29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="J29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="K29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="L29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="M29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="N29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="O29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="P29">
-        <v>2.546</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="Q29">
         <v>3.262665277411847</v>
       </c>
       <c r="R29">
-        <v>7.270594127561734</v>
+        <v>7.2705941275617336</v>
       </c>
       <c r="S29">
         <v>11.82483959941497</v>
       </c>
     </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" cm="1">
+        <f t="array" ref="D33:S33">D2:S2+D4:S4</f>
+        <v>0.70094042832944958</v>
+      </c>
+      <c r="E33">
+        <v>0.70094042832944958</v>
+      </c>
+      <c r="F33">
+        <v>0.78771187771932505</v>
+      </c>
+      <c r="G33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="H33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="I33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="J33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="K33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="L33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="M33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="N33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="O33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="P33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="Q33">
+        <v>0.87543281312130117</v>
+      </c>
+      <c r="R33">
+        <v>0.34106855612363141</v>
+      </c>
+      <c r="S33">
+        <v>1.75441870803952E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" cm="1">
+        <f t="array" ref="D34:S34">D19:S19+D16:S16</f>
+        <v>22.957000000000001</v>
+      </c>
+      <c r="E34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="F34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="G34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="H34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="I34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="J34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="K34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="L34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="M34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="N34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="O34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="P34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="Q34">
+        <v>22.957000000000001</v>
+      </c>
+      <c r="R34">
+        <v>4.5914000000000001</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" cm="1">
+        <f t="array" ref="D35:S35">D26:S26</f>
+        <v>0.30607479597105719</v>
+      </c>
+      <c r="E35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="F35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="G35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="H35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="I35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="J35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="K35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="L35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="M35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="N35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="O35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="P35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="Q35">
+        <v>0.76212092436800227</v>
+      </c>
+      <c r="R35">
+        <v>0.36865759542658988</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" cm="1">
+        <f t="array" ref="D36:S36">D27:S27</f>
+        <v>11.279</v>
+      </c>
+      <c r="E36">
+        <v>11.279</v>
+      </c>
+      <c r="F36">
+        <v>11.40687415366328</v>
+      </c>
+      <c r="G36">
+        <v>11.40687415366328</v>
+      </c>
+      <c r="H36">
+        <v>11.40687415366328</v>
+      </c>
+      <c r="I36">
+        <v>11.40687415366328</v>
+      </c>
+      <c r="J36">
+        <v>11.40687415366328</v>
+      </c>
+      <c r="K36">
+        <v>13.67449478502083</v>
+      </c>
+      <c r="L36">
+        <v>13.67449478502083</v>
+      </c>
+      <c r="M36">
+        <v>13.67449478502083</v>
+      </c>
+      <c r="N36">
+        <v>12.649264959504411</v>
+      </c>
+      <c r="O36">
+        <v>10.26559080584113</v>
+      </c>
+      <c r="P36">
+        <v>10.26559080584113</v>
+      </c>
+      <c r="Q36">
+        <v>7.9979701744835801</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" cm="1">
+        <f t="array" ref="D37:S37">D11:S11</f>
+        <v>11.212999999999999</v>
+      </c>
+      <c r="E37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="F37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="G37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="H37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="I37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="J37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="K37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="L37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="M37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="N37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="O37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="P37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="Q37">
+        <v>11.212999999999999</v>
+      </c>
+      <c r="R37">
+        <v>2.2425999999999999</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" cm="1">
+        <f t="array" ref="D38:S38">D20:S20</f>
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="E38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="F38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="G38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="H38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="I38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="J38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="K38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="L38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="M38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="N38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="O38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="P38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="Q38">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="R38">
+        <v>1.663</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" cm="1">
+        <f t="array" ref="D39:S39">D22:S22</f>
+        <v>7.7160000000000002</v>
+      </c>
+      <c r="E39">
+        <v>7.7160000000000002</v>
+      </c>
+      <c r="F39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="G39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="H39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="I39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="J39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="K39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="L39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="M39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="N39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="O39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="P39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="Q39">
+        <v>7.8740052312157616</v>
+      </c>
+      <c r="R39">
+        <v>4.718492466933343</v>
+      </c>
+      <c r="S39">
+        <v>4.6876526468880266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:T38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2279,7 +6048,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2293,19 +6062,19 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>4.693730232558141</v>
+        <v>4.6937302325581411</v>
       </c>
       <c r="F2">
-        <v>4.69373023255814</v>
+        <v>4.6937302325581403</v>
       </c>
       <c r="G2">
-        <v>4.69373023255814</v>
+        <v>4.6937302325581403</v>
       </c>
       <c r="H2">
-        <v>4.459043720930232</v>
+        <v>4.4590437209302323</v>
       </c>
       <c r="I2">
-        <v>4.224357209302324</v>
+        <v>4.2243572093023243</v>
       </c>
       <c r="J2">
         <v>3.989670697674419</v>
@@ -2314,7 +6083,7 @@
         <v>3.754984186046511</v>
       </c>
       <c r="L2">
-        <v>3.520297674418604</v>
+        <v>3.5202976744186039</v>
       </c>
       <c r="M2">
         <v>3.285611162790699</v>
@@ -2326,22 +6095,22 @@
         <v>2.933581395348837</v>
       </c>
       <c r="P2">
-        <v>2.34686511627907</v>
+        <v>2.3468651162790701</v>
       </c>
       <c r="Q2">
         <v>1.760148837209303</v>
       </c>
       <c r="R2">
-        <v>1.173432558139535</v>
+        <v>1.1734325581395351</v>
       </c>
       <c r="S2">
-        <v>0.5867162790697675</v>
+        <v>0.58671627906976753</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2370,40 +6139,40 @@
         <v>1.828406511627908</v>
       </c>
       <c r="J3">
-        <v>2.937792558139537</v>
+        <v>2.9377925581395372</v>
       </c>
       <c r="K3">
-        <v>4.491075348837205</v>
+        <v>4.4910753488372048</v>
       </c>
       <c r="L3">
-        <v>8.499918139534888</v>
+        <v>8.4999181395348877</v>
       </c>
       <c r="M3">
-        <v>8.00633093023256</v>
+        <v>8.0063309302325596</v>
       </c>
       <c r="N3">
-        <v>7.512743720930233</v>
+        <v>7.5127437209302332</v>
       </c>
       <c r="O3">
-        <v>8.454115116279075</v>
+        <v>8.4541151162790751</v>
       </c>
       <c r="P3">
         <v>13.16097209302327</v>
       </c>
       <c r="Q3">
-        <v>15.80822906976745</v>
+        <v>15.808229069767449</v>
       </c>
       <c r="R3">
-        <v>18.45548604651163</v>
+        <v>18.455486046511631</v>
       </c>
       <c r="S3">
-        <v>21.10274302325581</v>
+        <v>21.102743023255812</v>
       </c>
       <c r="T3">
         <v>23.75</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2417,55 +6186,55 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>2.69688976744186</v>
+        <v>2.6968897674418599</v>
       </c>
       <c r="F4">
-        <v>4.059189767441858</v>
+        <v>4.0591897674418584</v>
       </c>
       <c r="G4">
-        <v>8.596029767441864</v>
+        <v>8.5960297674418644</v>
       </c>
       <c r="H4">
-        <v>10.11699627906978</v>
+        <v>10.116996279069779</v>
       </c>
       <c r="I4">
         <v>10.11699627906977</v>
       </c>
       <c r="J4">
-        <v>9.974176744186048</v>
+        <v>9.9741767441860478</v>
       </c>
       <c r="K4">
-        <v>9.387460465116281</v>
+        <v>9.3874604651162805</v>
       </c>
       <c r="L4">
         <v>8.800744186046515</v>
       </c>
       <c r="M4">
-        <v>8.214027906976746</v>
+        <v>8.2140279069767459</v>
       </c>
       <c r="N4">
-        <v>7.627311627906979</v>
+        <v>7.6273116279069786</v>
       </c>
       <c r="O4">
-        <v>7.333953488372096</v>
+        <v>7.3339534883720958</v>
       </c>
       <c r="P4">
-        <v>5.867162790697673</v>
+        <v>5.8671627906976731</v>
       </c>
       <c r="Q4">
-        <v>4.400372093023257</v>
+        <v>4.4003720930232566</v>
       </c>
       <c r="R4">
-        <v>2.933581395348838</v>
+        <v>2.9335813953488379</v>
       </c>
       <c r="S4">
-        <v>1.466790697674419</v>
+        <v>1.4667906976744189</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2491,43 +6260,43 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2.739120585984001</v>
+        <v>2.7391205859840011</v>
       </c>
       <c r="J5">
-        <v>4.108680878976</v>
+        <v>4.1086808789760001</v>
       </c>
       <c r="K5">
-        <v>4.108680878976</v>
+        <v>4.1086808789760001</v>
       </c>
       <c r="L5">
-        <v>5.954274316799999</v>
+        <v>5.9542743167999994</v>
       </c>
       <c r="M5">
-        <v>7.502540039424002</v>
+        <v>7.5025400394240016</v>
       </c>
       <c r="N5">
-        <v>8.752963379328003</v>
+        <v>8.7529633793280031</v>
       </c>
       <c r="O5">
-        <v>8.868883637905149</v>
+        <v>8.8688836379051494</v>
       </c>
       <c r="P5">
-        <v>5.804087901119999</v>
+        <v>5.8040879011199991</v>
       </c>
       <c r="Q5">
-        <v>5.804087901120001</v>
+        <v>5.8040879011200008</v>
       </c>
       <c r="R5">
-        <v>6.250851475199999</v>
+        <v>6.2508514751999993</v>
       </c>
       <c r="S5">
-        <v>5.996235756500161</v>
+        <v>5.9962357565001607</v>
       </c>
       <c r="T5">
         <v>6.1324567870464</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2574,10 +6343,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>30.46801590775926</v>
+        <v>30.468015907759259</v>
       </c>
       <c r="Q6">
-        <v>32.15071989504</v>
+        <v>32.150719895039998</v>
       </c>
       <c r="R6">
         <v>31.95156305509294</v>
@@ -2586,10 +6355,10 @@
         <v>28.36636962048</v>
       </c>
       <c r="T6">
-        <v>16.93600512188185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>16.936005121881848</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2624,34 +6393,34 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>12.9593029248</v>
+        <v>12.959302924799999</v>
       </c>
       <c r="M7">
-        <v>16.12422656591963</v>
+        <v>16.124226565919631</v>
       </c>
       <c r="N7">
         <v>14.966633574144</v>
       </c>
       <c r="O7">
-        <v>16.03567882944</v>
+        <v>16.035678829439998</v>
       </c>
       <c r="P7">
-        <v>12.63242660832</v>
+        <v>12.632426608319999</v>
       </c>
       <c r="Q7">
-        <v>12.63242660832</v>
+        <v>12.632426608319999</v>
       </c>
       <c r="R7">
-        <v>12.63242660832</v>
+        <v>12.632426608319999</v>
       </c>
       <c r="S7">
-        <v>12.63242660832</v>
+        <v>12.632426608319999</v>
       </c>
       <c r="T7">
-        <v>12.87807637991754</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>12.878076379917539</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2686,34 +6455,34 @@
         <v>19.3351582628177</v>
       </c>
       <c r="L8">
-        <v>19.33960928195146</v>
+        <v>19.339609281951461</v>
       </c>
       <c r="M8">
-        <v>19.4389543872</v>
+        <v>19.438954387199999</v>
       </c>
       <c r="N8">
-        <v>16.03567882944</v>
+        <v>16.035678829439998</v>
       </c>
       <c r="O8">
-        <v>16.03567882944</v>
+        <v>16.035678829439998</v>
       </c>
       <c r="P8">
-        <v>12.63242660832</v>
+        <v>12.632426608319999</v>
       </c>
       <c r="Q8">
-        <v>12.63242660832</v>
+        <v>12.632426608319999</v>
       </c>
       <c r="R8">
         <v>12.55322332533456</v>
       </c>
       <c r="S8">
-        <v>12.22061239232301</v>
+        <v>12.220612392323011</v>
       </c>
       <c r="T8">
-        <v>10.59932802311156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>10.599328023111561</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2766,16 +6535,16 @@
         <v>29.53555242872131</v>
       </c>
       <c r="R9">
-        <v>67.61705669751635</v>
+        <v>67.617056697516347</v>
       </c>
       <c r="S9">
-        <v>67.61705669751635</v>
+        <v>67.617056697516347</v>
       </c>
       <c r="T9">
-        <v>53.16959587682167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>53.169595876821667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2825,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>9.859185542958906</v>
+        <v>9.8591855429589064</v>
       </c>
       <c r="R10">
-        <v>28.17815539931596</v>
+        <v>28.178155399315958</v>
       </c>
       <c r="S10">
         <v>27.05693844000935</v>
@@ -2837,7 +6606,7 @@
         <v>13.92031415296697</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2851,19 +6620,19 @@
         <v>35</v>
       </c>
       <c r="E11">
-        <v>266.71</v>
+        <v>266.70999999999998</v>
       </c>
       <c r="F11">
-        <v>177.5278</v>
+        <v>177.52780000000001</v>
       </c>
       <c r="G11">
-        <v>92.38500000000006</v>
+        <v>92.385000000000062</v>
       </c>
       <c r="H11">
         <v>186.7415</v>
       </c>
       <c r="I11">
-        <v>155.0399999999998</v>
+        <v>155.03999999999979</v>
       </c>
       <c r="J11">
         <v>120.9635000000002</v>
@@ -2878,7 +6647,7 @@
         <v>22.60999999999996</v>
       </c>
       <c r="N11">
-        <v>4.731000000000003</v>
+        <v>4.7310000000000034</v>
       </c>
       <c r="O11">
         <v>3.071666666666673</v>
@@ -2899,7 +6668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2922,28 +6691,28 @@
         <v>2.375</v>
       </c>
       <c r="H12">
-        <v>4.749999999999994</v>
+        <v>4.7499999999999938</v>
       </c>
       <c r="I12">
         <v>4.75</v>
       </c>
       <c r="J12">
-        <v>7.124999999999999</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="K12">
-        <v>7.124999999999998</v>
+        <v>7.1249999999999982</v>
       </c>
       <c r="L12">
-        <v>7.124999999999999</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="M12">
-        <v>7.124999999999998</v>
+        <v>7.1249999999999982</v>
       </c>
       <c r="N12">
-        <v>7.124999999999999</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="O12">
-        <v>7.124999999999999</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="P12">
         <v>1.9</v>
@@ -2955,13 +6724,13 @@
         <v>0.95</v>
       </c>
       <c r="S12">
-        <v>0.4749999999999999</v>
+        <v>0.47499999999999992</v>
       </c>
       <c r="T12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3008,22 +6777,22 @@
         <v>0.265625</v>
       </c>
       <c r="P13">
-        <v>0.2125</v>
+        <v>0.21249999999999999</v>
       </c>
       <c r="Q13">
-        <v>0.159375</v>
+        <v>0.15937499999999999</v>
       </c>
       <c r="R13">
         <v>0.10625</v>
       </c>
       <c r="S13">
-        <v>0.05312499999999998</v>
+        <v>5.3124999999999978E-2</v>
       </c>
       <c r="T13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -3037,16 +6806,16 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>72.32802628789786</v>
+        <v>72.328026287897856</v>
       </c>
       <c r="F14">
-        <v>56.02920979279438</v>
+        <v>56.029209792794383</v>
       </c>
       <c r="G14">
         <v>110.0203463944904</v>
       </c>
       <c r="H14">
-        <v>62.40370348647316</v>
+        <v>62.403703486473162</v>
       </c>
       <c r="I14">
         <v>110.0203463944904</v>
@@ -3055,13 +6824,13 @@
         <v>110.0203463944904</v>
       </c>
       <c r="K14">
-        <v>108.2110601577593</v>
+        <v>108.21106015775931</v>
       </c>
       <c r="L14">
-        <v>95.50650857339303</v>
+        <v>95.506508573393035</v>
       </c>
       <c r="M14">
-        <v>75.74088043391299</v>
+        <v>75.740880433912992</v>
       </c>
       <c r="N14">
         <v>110.0203463944904</v>
@@ -3070,22 +6839,22 @@
         <v>110.0203463944904</v>
       </c>
       <c r="P14">
-        <v>182.5575524376953</v>
+        <v>182.55755243769531</v>
       </c>
       <c r="Q14">
-        <v>185.5906426065999</v>
+        <v>185.59064260659991</v>
       </c>
       <c r="R14">
-        <v>194.1164835816791</v>
+        <v>194.11648358167909</v>
       </c>
       <c r="S14">
         <v>196.1099103224376</v>
       </c>
       <c r="T14">
-        <v>169.8844483526271</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>169.88444835262709</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -3117,7 +6886,7 @@
         <v>15.19416370025009</v>
       </c>
       <c r="K15">
-        <v>8.250706072470551</v>
+        <v>8.2507060724705514</v>
       </c>
       <c r="L15">
         <v>11.81783815455584</v>
@@ -3126,28 +6895,28 @@
         <v>11.78303956608702</v>
       </c>
       <c r="N15">
-        <v>34.89027957221803</v>
+        <v>34.890279572218027</v>
       </c>
       <c r="O15">
-        <v>55.6055170583382</v>
+        <v>55.605517058338201</v>
       </c>
       <c r="P15">
-        <v>56.76479999999999</v>
+        <v>56.764799999999987</v>
       </c>
       <c r="Q15">
-        <v>56.76480000000002</v>
+        <v>56.764800000000022</v>
       </c>
       <c r="R15">
-        <v>54.44098437834263</v>
+        <v>54.440984378342627</v>
       </c>
       <c r="S15">
-        <v>45.8223473171245</v>
+        <v>45.822347317124503</v>
       </c>
       <c r="T15">
-        <v>41.57063629974991</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>41.570636299749907</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -3161,34 +6930,34 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>341.2764000000001</v>
+        <v>341.27640000000008</v>
       </c>
       <c r="F16">
-        <v>434.8728</v>
+        <v>434.87279999999998</v>
       </c>
       <c r="G16">
-        <v>341.4636</v>
+        <v>341.46359999999999</v>
       </c>
       <c r="H16">
-        <v>263.9088</v>
+        <v>263.90879999999999</v>
       </c>
       <c r="I16">
         <v>176.8040394140159</v>
       </c>
       <c r="J16">
-        <v>157.2005608582062</v>
+        <v>157.20056085820619</v>
       </c>
       <c r="K16">
         <v>185.3705608582064</v>
       </c>
       <c r="L16">
-        <v>212.8072134764487</v>
+        <v>212.80721347644871</v>
       </c>
       <c r="M16">
-        <v>250.9687790074566</v>
+        <v>250.96877900745659</v>
       </c>
       <c r="N16">
-        <v>144.3979826126466</v>
+        <v>144.39798261264659</v>
       </c>
       <c r="O16">
         <v>150.9254978651995</v>
@@ -3209,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -3259,19 +7028,19 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>15.52603883088634</v>
+        <v>15.526038830886341</v>
       </c>
       <c r="R17">
         <v>52.83391106439111</v>
       </c>
       <c r="S17">
-        <v>53.72128810615413</v>
+        <v>53.721288106154127</v>
       </c>
       <c r="T17">
-        <v>18.68429514838492</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>18.684295148384919</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -3324,16 +7093,16 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>14.88026064009495</v>
+        <v>14.880260640094949</v>
       </c>
       <c r="S18">
         <v>1.948545218679582</v>
       </c>
       <c r="T18">
-        <v>65.84765355607043</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>65.847653556070426</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -3395,7 +7164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -3409,34 +7178,34 @@
         <v>35</v>
       </c>
       <c r="E20">
-        <v>66.6288</v>
+        <v>66.628799999999998</v>
       </c>
       <c r="F20">
-        <v>63.29987999999999</v>
+        <v>63.299879999999987</v>
       </c>
       <c r="G20">
-        <v>59.6232</v>
+        <v>59.623199999999997</v>
       </c>
       <c r="H20">
-        <v>52.39781999999997</v>
+        <v>52.397819999999967</v>
       </c>
       <c r="I20">
-        <v>48.29382</v>
+        <v>48.293819999999997</v>
       </c>
       <c r="J20">
         <v>57.86981999999999</v>
       </c>
       <c r="K20">
-        <v>49.58316</v>
+        <v>49.583159999999999</v>
       </c>
       <c r="L20">
-        <v>36.60768</v>
+        <v>36.607680000000002</v>
       </c>
       <c r="M20">
-        <v>36.21780000000001</v>
+        <v>36.217800000000011</v>
       </c>
       <c r="N20">
-        <v>30.514</v>
+        <v>30.513999999999999</v>
       </c>
       <c r="O20">
         <v>27.01166666666667</v>
@@ -3457,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -3519,7 +7288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -3536,34 +7305,34 @@
         <v>198.37</v>
       </c>
       <c r="F22">
-        <v>212.3028</v>
+        <v>212.30279999999999</v>
       </c>
       <c r="G22">
-        <v>223.4045000000002</v>
+        <v>223.40450000000021</v>
       </c>
       <c r="H22">
         <v>221.29</v>
       </c>
       <c r="I22">
-        <v>208.5023220590161</v>
+        <v>208.50232205901611</v>
       </c>
       <c r="J22">
-        <v>223.2995988529451</v>
+        <v>223.29959885294511</v>
       </c>
       <c r="K22">
         <v>200.76</v>
       </c>
       <c r="L22">
-        <v>209.8800000000001</v>
+        <v>209.88000000000011</v>
       </c>
       <c r="M22">
-        <v>223.4045</v>
+        <v>223.40450000000001</v>
       </c>
       <c r="N22">
-        <v>215.9410000000001</v>
+        <v>215.94100000000009</v>
       </c>
       <c r="O22">
-        <v>202.7008333333334</v>
+        <v>202.70083333333341</v>
       </c>
       <c r="P22">
         <v>136.5</v>
@@ -3581,7 +7350,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3625,25 +7394,25 @@
         <v>49.625829926784</v>
       </c>
       <c r="O23">
-        <v>49.62582992678401</v>
+        <v>49.625829926784007</v>
       </c>
       <c r="P23">
-        <v>49.62582992678401</v>
+        <v>49.625829926784007</v>
       </c>
       <c r="Q23">
-        <v>49.62582992678401</v>
+        <v>49.625829926784007</v>
       </c>
       <c r="R23">
-        <v>48.19618648972801</v>
+        <v>48.196186489728007</v>
       </c>
       <c r="S23">
-        <v>49.62582992678401</v>
+        <v>49.625829926784007</v>
       </c>
       <c r="T23">
-        <v>48.72973020596243</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>48.729730205962433</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3705,7 +7474,7 @@
         <v>13.11099952131072</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3722,52 +7491,52 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>4.980633600000001</v>
+        <v>4.9806336000000009</v>
       </c>
       <c r="G25">
-        <v>20.2493808</v>
+        <v>20.249380800000001</v>
       </c>
       <c r="H25">
-        <v>38.813328</v>
+        <v>38.813327999999998</v>
       </c>
       <c r="I25">
-        <v>43.1887752</v>
+        <v>43.188775200000002</v>
       </c>
       <c r="J25">
-        <v>45.08760239999999</v>
+        <v>45.087602399999987</v>
       </c>
       <c r="K25">
-        <v>45.08760239999999</v>
+        <v>45.087602399999987</v>
       </c>
       <c r="L25">
-        <v>70.36879679999998</v>
+        <v>70.368796799999984</v>
       </c>
       <c r="M25">
         <v>118.1991239999999</v>
       </c>
       <c r="N25">
-        <v>129.8375368609536</v>
+        <v>129.83753686095361</v>
       </c>
       <c r="O25">
-        <v>136.343878194287</v>
+        <v>136.34387819428699</v>
       </c>
       <c r="P25">
-        <v>174.7960407647269</v>
+        <v>174.79604076472691</v>
       </c>
       <c r="Q25">
-        <v>183.5467768609535</v>
+        <v>183.54677686095351</v>
       </c>
       <c r="R25">
-        <v>197.318156831872</v>
+        <v>197.31815683187199</v>
       </c>
       <c r="S25">
         <v>210.3881705519052</v>
       </c>
       <c r="T25">
-        <v>223.1592702727268</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>223.15927027272679</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -3781,37 +7550,37 @@
         <v>34</v>
       </c>
       <c r="E26">
-        <v>1.7613</v>
+        <v>1.7613000000000001</v>
       </c>
       <c r="F26">
-        <v>4.385606399999999</v>
+        <v>4.3856063999999986</v>
       </c>
       <c r="G26">
-        <v>4.3267392</v>
+        <v>4.3267391999999996</v>
       </c>
       <c r="H26">
-        <v>4.267872</v>
+        <v>4.2678719999999997</v>
       </c>
       <c r="I26">
-        <v>4.209004800000001</v>
+        <v>4.2090048000000007</v>
       </c>
       <c r="J26">
-        <v>4.1501376</v>
+        <v>4.1501375999999999</v>
       </c>
       <c r="K26">
-        <v>0.7907975999999987</v>
+        <v>0.79079759999999866</v>
       </c>
       <c r="L26">
-        <v>4.032403199999998</v>
+        <v>4.0324031999999983</v>
       </c>
       <c r="M26">
-        <v>3.973536000000001</v>
+        <v>3.9735360000000011</v>
       </c>
       <c r="N26">
-        <v>3.679200000000001</v>
+        <v>3.6792000000000011</v>
       </c>
       <c r="O26">
-        <v>3.532032000000001</v>
+        <v>3.5320320000000009</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -3829,7 +7598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -3843,46 +7612,46 @@
         <v>35</v>
       </c>
       <c r="E27">
-        <v>75.36756595731136</v>
+        <v>75.367565957311356</v>
       </c>
       <c r="F27">
-        <v>75.36756595731134</v>
+        <v>75.367565957311342</v>
       </c>
       <c r="G27">
-        <v>76.22203565413311</v>
+        <v>76.222035654133109</v>
       </c>
       <c r="H27">
-        <v>76.22203565413311</v>
+        <v>76.222035654133109</v>
       </c>
       <c r="I27">
-        <v>76.22203565413312</v>
+        <v>76.222035654133123</v>
       </c>
       <c r="J27">
-        <v>76.13486918761564</v>
+        <v>76.134869187615635</v>
       </c>
       <c r="K27">
-        <v>76.07720951066777</v>
+        <v>76.077209510667771</v>
       </c>
       <c r="L27">
-        <v>91.3745356541331</v>
+        <v>91.374535654133098</v>
       </c>
       <c r="M27">
-        <v>91.3745356541331</v>
+        <v>91.374535654133098</v>
       </c>
       <c r="N27">
-        <v>91.37453565413313</v>
+        <v>91.374535654133126</v>
       </c>
       <c r="O27">
-        <v>84.52383288828406</v>
+        <v>84.523832888284062</v>
       </c>
       <c r="P27">
-        <v>68.59585000000006</v>
+        <v>68.595850000000056</v>
       </c>
       <c r="Q27">
-        <v>68.59585000000003</v>
+        <v>68.595850000000027</v>
       </c>
       <c r="R27">
-        <v>53.44335000000001</v>
+        <v>53.443350000000009</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3891,7 +7660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -3905,55 +7674,55 @@
         <v>35</v>
       </c>
       <c r="E28">
-        <v>18.91043404268865</v>
+        <v>18.910434042688649</v>
       </c>
       <c r="F28">
-        <v>37.95476737602201</v>
+        <v>37.954767376022012</v>
       </c>
       <c r="G28">
-        <v>83.15796434586686</v>
+        <v>83.157964345866858</v>
       </c>
       <c r="H28">
         <v>92.97296434586687</v>
       </c>
       <c r="I28">
-        <v>101.6654643458669</v>
+        <v>101.66546434586689</v>
       </c>
       <c r="J28">
         <v>98.97829016620976</v>
       </c>
       <c r="K28">
-        <v>97.99129048933217</v>
+        <v>97.991290489332172</v>
       </c>
       <c r="L28">
-        <v>101.6654643458669</v>
+        <v>101.66546434586689</v>
       </c>
       <c r="M28">
-        <v>132.2006744616114</v>
+        <v>132.20067446161141</v>
       </c>
       <c r="N28">
         <v>136.9148652764311</v>
       </c>
       <c r="O28">
-        <v>155.0002223795964</v>
+        <v>155.00022237959641</v>
       </c>
       <c r="P28">
-        <v>262.6903038461538</v>
+        <v>262.69030384615382</v>
       </c>
       <c r="Q28">
-        <v>333.8687653846152</v>
+        <v>333.86876538461519</v>
       </c>
       <c r="R28">
-        <v>420.1997269230769</v>
+        <v>420.19972692307692</v>
       </c>
       <c r="S28">
-        <v>544.8215384615384</v>
+        <v>544.82153846153835</v>
       </c>
       <c r="T28">
         <v>616</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -3967,28 +7736,28 @@
         <v>35</v>
       </c>
       <c r="E29">
-        <v>37.55117371210213</v>
+        <v>37.551173712102127</v>
       </c>
       <c r="F29">
-        <v>38.08919020720561</v>
+        <v>38.089190207205611</v>
       </c>
       <c r="G29">
-        <v>38.62508990525956</v>
+        <v>38.625089905259557</v>
       </c>
       <c r="H29">
         <v>22.84020447795741</v>
       </c>
       <c r="I29">
-        <v>29.47388990525958</v>
+        <v>29.473889905259579</v>
       </c>
       <c r="J29">
-        <v>18.29948990525959</v>
+        <v>18.299489905259591</v>
       </c>
       <c r="K29">
         <v>16.49163376977015</v>
       </c>
       <c r="L29">
-        <v>15.06845327205117</v>
+        <v>15.068453272051171</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -3997,7 +7766,7 @@
         <v>2.04497403329162</v>
       </c>
       <c r="O29">
-        <v>0.4306286990381487</v>
+        <v>0.43062869903814871</v>
       </c>
       <c r="P29">
         <v>2.677647562304792</v>
@@ -4006,26 +7775,405 @@
         <v>13.39455739340011</v>
       </c>
       <c r="R29">
-        <v>20.94253203997812</v>
+        <v>20.942532039978119</v>
       </c>
       <c r="S29">
-        <v>41.3177423604378</v>
+        <v>41.317742360437798</v>
       </c>
       <c r="T29">
-        <v>85.544915347623</v>
+        <v>85.544915347623004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" cm="1">
+        <f t="array" ref="E32:T32">E22:T22</f>
+        <v>198.37</v>
+      </c>
+      <c r="F32">
+        <v>212.30279999999999</v>
+      </c>
+      <c r="G32">
+        <v>223.40450000000021</v>
+      </c>
+      <c r="H32">
+        <v>221.29</v>
+      </c>
+      <c r="I32">
+        <v>208.50232205901611</v>
+      </c>
+      <c r="J32">
+        <v>223.29959885294511</v>
+      </c>
+      <c r="K32">
+        <v>200.76</v>
+      </c>
+      <c r="L32">
+        <v>209.88000000000011</v>
+      </c>
+      <c r="M32">
+        <v>223.40450000000001</v>
+      </c>
+      <c r="N32">
+        <v>215.94100000000009</v>
+      </c>
+      <c r="O32">
+        <v>202.70083333333341</v>
+      </c>
+      <c r="P32">
+        <v>136.5</v>
+      </c>
+      <c r="Q32">
+        <v>135.625</v>
+      </c>
+      <c r="R32">
+        <v>134.75</v>
+      </c>
+      <c r="S32">
+        <v>133.875</v>
+      </c>
+      <c r="T32">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="4:20" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" cm="1">
+        <f t="array" ref="E33:T33">E2:T2+E4:T4</f>
+        <v>7.3906200000000011</v>
+      </c>
+      <c r="F33">
+        <v>8.7529199999999996</v>
+      </c>
+      <c r="G33">
+        <v>13.289760000000005</v>
+      </c>
+      <c r="H33">
+        <v>14.576040000000011</v>
+      </c>
+      <c r="I33">
+        <v>14.341353488372095</v>
+      </c>
+      <c r="J33">
+        <v>13.963847441860466</v>
+      </c>
+      <c r="K33">
+        <v>13.142444651162791</v>
+      </c>
+      <c r="L33">
+        <v>12.321041860465119</v>
+      </c>
+      <c r="M33">
+        <v>11.499639069767445</v>
+      </c>
+      <c r="N33">
+        <v>10.67823627906977</v>
+      </c>
+      <c r="O33">
+        <v>10.267534883720932</v>
+      </c>
+      <c r="P33">
+        <v>8.2140279069767423</v>
+      </c>
+      <c r="Q33">
+        <v>6.1605209302325594</v>
+      </c>
+      <c r="R33">
+        <v>4.1070139534883729</v>
+      </c>
+      <c r="S33">
+        <v>2.0535069767441865</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:20" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" cm="1">
+        <f t="array" ref="E34:T34">E19:T19+E16:T16</f>
+        <v>341.27640000000008</v>
+      </c>
+      <c r="F34">
+        <v>434.87279999999998</v>
+      </c>
+      <c r="G34">
+        <v>341.46359999999999</v>
+      </c>
+      <c r="H34">
+        <v>263.90879999999999</v>
+      </c>
+      <c r="I34">
+        <v>176.8040394140159</v>
+      </c>
+      <c r="J34">
+        <v>157.20056085820619</v>
+      </c>
+      <c r="K34">
+        <v>185.3705608582064</v>
+      </c>
+      <c r="L34">
+        <v>212.80721347644871</v>
+      </c>
+      <c r="M34">
+        <v>250.96877900745659</v>
+      </c>
+      <c r="N34">
+        <v>144.39798261264659</v>
+      </c>
+      <c r="O34">
+        <v>150.9254978651995</v>
+      </c>
+      <c r="P34">
+        <v>136.9639618498347</v>
+      </c>
+      <c r="Q34">
+        <v>124.21</v>
+      </c>
+      <c r="R34">
+        <v>27.2</v>
+      </c>
+      <c r="S34">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:20" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" cm="1">
+        <f t="array" ref="E35:T35">E26:T26</f>
+        <v>1.7613000000000001</v>
+      </c>
+      <c r="F35">
+        <v>4.3856063999999986</v>
+      </c>
+      <c r="G35">
+        <v>4.3267391999999996</v>
+      </c>
+      <c r="H35">
+        <v>4.2678719999999997</v>
+      </c>
+      <c r="I35">
+        <v>4.2090048000000007</v>
+      </c>
+      <c r="J35">
+        <v>4.1501375999999999</v>
+      </c>
+      <c r="K35">
+        <v>0.79079759999999866</v>
+      </c>
+      <c r="L35">
+        <v>4.0324031999999983</v>
+      </c>
+      <c r="M35">
+        <v>3.9735360000000011</v>
+      </c>
+      <c r="N35">
+        <v>3.6792000000000011</v>
+      </c>
+      <c r="O35">
+        <v>3.5320320000000009</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:20" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" cm="1">
+        <f t="array" ref="E36:T36">E27:T27</f>
+        <v>75.367565957311356</v>
+      </c>
+      <c r="F36">
+        <v>75.367565957311342</v>
+      </c>
+      <c r="G36">
+        <v>76.222035654133109</v>
+      </c>
+      <c r="H36">
+        <v>76.222035654133109</v>
+      </c>
+      <c r="I36">
+        <v>76.222035654133123</v>
+      </c>
+      <c r="J36">
+        <v>76.134869187615635</v>
+      </c>
+      <c r="K36">
+        <v>76.077209510667771</v>
+      </c>
+      <c r="L36">
+        <v>91.374535654133098</v>
+      </c>
+      <c r="M36">
+        <v>91.374535654133098</v>
+      </c>
+      <c r="N36">
+        <v>91.374535654133126</v>
+      </c>
+      <c r="O36">
+        <v>84.523832888284062</v>
+      </c>
+      <c r="P36">
+        <v>68.595850000000056</v>
+      </c>
+      <c r="Q36">
+        <v>68.595850000000027</v>
+      </c>
+      <c r="R36">
+        <v>53.443350000000009</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:20" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" cm="1">
+        <f t="array" ref="E37:T37">E11:T11</f>
+        <v>266.70999999999998</v>
+      </c>
+      <c r="F37">
+        <v>177.52780000000001</v>
+      </c>
+      <c r="G37">
+        <v>92.385000000000062</v>
+      </c>
+      <c r="H37">
+        <v>186.7415</v>
+      </c>
+      <c r="I37">
+        <v>155.03999999999979</v>
+      </c>
+      <c r="J37">
+        <v>120.9635000000002</v>
+      </c>
+      <c r="K37">
+        <v>125.248</v>
+      </c>
+      <c r="L37">
+        <v>13.90799999999996</v>
+      </c>
+      <c r="M37">
+        <v>22.60999999999996</v>
+      </c>
+      <c r="N37">
+        <v>4.7310000000000034</v>
+      </c>
+      <c r="O37">
+        <v>3.071666666666673</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:20" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" cm="1">
+        <f t="array" ref="E38:T38">E20:T20</f>
+        <v>66.628799999999998</v>
+      </c>
+      <c r="F38">
+        <v>63.299879999999987</v>
+      </c>
+      <c r="G38">
+        <v>59.623199999999997</v>
+      </c>
+      <c r="H38">
+        <v>52.397819999999967</v>
+      </c>
+      <c r="I38">
+        <v>48.293819999999997</v>
+      </c>
+      <c r="J38">
+        <v>57.86981999999999</v>
+      </c>
+      <c r="K38">
+        <v>49.583159999999999</v>
+      </c>
+      <c r="L38">
+        <v>36.607680000000002</v>
+      </c>
+      <c r="M38">
+        <v>36.217800000000011</v>
+      </c>
+      <c r="N38">
+        <v>30.513999999999999</v>
+      </c>
+      <c r="O38">
+        <v>27.01166666666667</v>
+      </c>
+      <c r="P38">
+        <v>9.5</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4087,7 +8235,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4110,25 +8258,25 @@
         <v>3911.441860465116</v>
       </c>
       <c r="H2">
-        <v>3715.86976744186</v>
+        <v>3715.8697674418599</v>
       </c>
       <c r="I2">
         <v>3520.297674418603</v>
       </c>
       <c r="J2">
-        <v>3324.725581395349</v>
+        <v>3324.7255813953489</v>
       </c>
       <c r="K2">
-        <v>3129.153488372092</v>
+        <v>3129.1534883720919</v>
       </c>
       <c r="L2">
-        <v>2933.581395348836</v>
+        <v>2933.5813953488359</v>
       </c>
       <c r="M2">
-        <v>2738.009302325582</v>
+        <v>2738.0093023255822</v>
       </c>
       <c r="N2">
-        <v>2542.437209302326</v>
+        <v>2542.4372093023262</v>
       </c>
       <c r="O2">
         <v>2444.651162790698</v>
@@ -4137,19 +8285,19 @@
         <v>1955.720930232558</v>
       </c>
       <c r="Q2">
-        <v>1466.790697674419</v>
+        <v>1466.7906976744191</v>
       </c>
       <c r="R2">
-        <v>977.8604651162793</v>
+        <v>977.86046511627933</v>
       </c>
       <c r="S2">
-        <v>488.9302325581394</v>
+        <v>488.93023255813938</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4163,55 +8311,55 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>52.15255813953488</v>
+        <v>52.152558139534882</v>
       </c>
       <c r="F3">
-        <v>52.15255813953488</v>
+        <v>52.152558139534882</v>
       </c>
       <c r="G3">
-        <v>52.15255813953488</v>
+        <v>52.152558139534882</v>
       </c>
       <c r="H3">
-        <v>49.54493023255812</v>
+        <v>49.544930232558123</v>
       </c>
       <c r="I3">
-        <v>46.93730232558138</v>
+        <v>46.937302325581378</v>
       </c>
       <c r="J3">
         <v>44.32967441860464</v>
       </c>
       <c r="K3">
-        <v>41.72204651162789</v>
+        <v>41.722046511627887</v>
       </c>
       <c r="L3">
-        <v>39.11441860465116</v>
+        <v>39.114418604651163</v>
       </c>
       <c r="M3">
-        <v>36.50679069767442</v>
+        <v>36.506790697674418</v>
       </c>
       <c r="N3">
-        <v>33.89916279069767</v>
+        <v>33.899162790697673</v>
       </c>
       <c r="O3">
-        <v>32.5953488372093</v>
+        <v>32.595348837209301</v>
       </c>
       <c r="P3">
-        <v>26.07627906976744</v>
+        <v>26.076279069767441</v>
       </c>
       <c r="Q3">
-        <v>19.55720930232558</v>
+        <v>19.557209302325582</v>
       </c>
       <c r="R3">
-        <v>13.03813953488372</v>
+        <v>13.038139534883721</v>
       </c>
       <c r="S3">
-        <v>6.519069767441859</v>
+        <v>6.5190697674418594</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4237,25 +8385,25 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1641.410391120508</v>
+        <v>1641.4103911205079</v>
       </c>
       <c r="J4">
-        <v>2624.729841437633</v>
+        <v>2624.7298414376328</v>
       </c>
       <c r="K4">
-        <v>3983.852283298094</v>
+        <v>3983.8522832980939</v>
       </c>
       <c r="L4">
-        <v>7436.419104861104</v>
+        <v>7436.4191048611037</v>
       </c>
       <c r="M4">
-        <v>6981.479028062177</v>
+        <v>6981.4790280621773</v>
       </c>
       <c r="N4">
-        <v>6512.935331095498</v>
+        <v>6512.9353310954984</v>
       </c>
       <c r="O4">
-        <v>7189.302945554677</v>
+        <v>7189.3029455546766</v>
       </c>
       <c r="P4">
         <v>10709.78906825241</v>
@@ -4273,7 +8421,7 @@
         <v>17812.5</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4299,31 +8447,31 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>21.88547188160677</v>
+        <v>21.885471881606769</v>
       </c>
       <c r="J5">
-        <v>34.99639788583512</v>
+        <v>34.996397885835123</v>
       </c>
       <c r="K5">
-        <v>53.11803044397458</v>
+        <v>53.118030443974583</v>
       </c>
       <c r="L5">
-        <v>99.15225473148138</v>
+        <v>99.152254731481378</v>
       </c>
       <c r="M5">
-        <v>93.08638704082902</v>
+        <v>93.086387040829024</v>
       </c>
       <c r="N5">
-        <v>86.83913774793997</v>
+        <v>86.839137747939972</v>
       </c>
       <c r="O5">
-        <v>95.85737260739569</v>
+        <v>95.857372607395689</v>
       </c>
       <c r="P5">
         <v>142.7971875766988</v>
       </c>
       <c r="Q5">
-        <v>167.1084278334259</v>
+        <v>167.10842783342591</v>
       </c>
       <c r="R5">
         <v>187.0327384004531</v>
@@ -4332,10 +8480,10 @@
         <v>211.0274302325582</v>
       </c>
       <c r="T5">
-        <v>237.5000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+        <v>237.50000000000011</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4349,31 +8497,31 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>311.1795885509838</v>
+        <v>311.17958855098379</v>
       </c>
       <c r="F6">
-        <v>468.3680500894451</v>
+        <v>468.36805008944509</v>
       </c>
       <c r="G6">
-        <v>991.849588550984</v>
+        <v>991.84958855098398</v>
       </c>
       <c r="H6">
-        <v>1167.34572450805</v>
+        <v>1167.3457245080499</v>
       </c>
       <c r="I6">
-        <v>1167.34572450805</v>
+        <v>1167.3457245080499</v>
       </c>
       <c r="J6">
         <v>1150.866547406082</v>
       </c>
       <c r="K6">
-        <v>1083.168515205724</v>
+        <v>1083.1685152057239</v>
       </c>
       <c r="L6">
         <v>1015.470483005367</v>
       </c>
       <c r="M6">
-        <v>947.7724508050089</v>
+        <v>947.77245080500893</v>
       </c>
       <c r="N6">
         <v>880.0744186046511</v>
@@ -4382,13 +8530,13 @@
         <v>846.2254025044723</v>
       </c>
       <c r="P6">
-        <v>676.9803220035778</v>
+        <v>676.98032200357784</v>
       </c>
       <c r="Q6">
-        <v>507.7352415026834</v>
+        <v>507.73524150268338</v>
       </c>
       <c r="R6">
-        <v>338.4901610017891</v>
+        <v>338.49016100178909</v>
       </c>
       <c r="S6">
         <v>169.2450805008946</v>
@@ -4397,7 +8545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4411,28 +8559,28 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>41.49061180679784</v>
+        <v>41.490611806797837</v>
       </c>
       <c r="F7">
-        <v>62.44907334525934</v>
+        <v>62.449073345259343</v>
       </c>
       <c r="G7">
-        <v>132.2466118067979</v>
+        <v>132.24661180679789</v>
       </c>
       <c r="H7">
-        <v>155.6460966010733</v>
+        <v>155.64609660107331</v>
       </c>
       <c r="I7">
-        <v>155.6460966010733</v>
+        <v>155.64609660107331</v>
       </c>
       <c r="J7">
-        <v>153.4488729874776</v>
+        <v>153.44887298747761</v>
       </c>
       <c r="K7">
-        <v>144.4224686940966</v>
+        <v>144.42246869409661</v>
       </c>
       <c r="L7">
-        <v>135.3960644007155</v>
+        <v>135.39606440071549</v>
       </c>
       <c r="M7">
         <v>126.3696601073345</v>
@@ -4444,22 +8592,22 @@
         <v>112.8300536672629</v>
       </c>
       <c r="P7">
-        <v>90.26404293381036</v>
+        <v>90.264042933810359</v>
       </c>
       <c r="Q7">
-        <v>67.69803220035777</v>
+        <v>67.698032200357773</v>
       </c>
       <c r="R7">
-        <v>45.1320214669052</v>
+        <v>45.132021466905201</v>
       </c>
       <c r="S7">
-        <v>22.56601073345261</v>
+        <v>22.566010733452611</v>
       </c>
       <c r="T7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4485,13 +8633,13 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.3956507513088</v>
+        <v>0.39565075130880001</v>
       </c>
       <c r="J8">
-        <v>0.5934761269632001</v>
+        <v>0.59347612696320007</v>
       </c>
       <c r="K8">
-        <v>0.5934761269632001</v>
+        <v>0.59347612696320007</v>
       </c>
       <c r="L8">
         <v>0.86006184576</v>
@@ -4506,22 +8654,22 @@
         <v>1.281060969919634</v>
       </c>
       <c r="P8">
-        <v>0.8383682523840001</v>
+        <v>0.83836825238400015</v>
       </c>
       <c r="Q8">
-        <v>0.8383682523840003</v>
+        <v>0.83836825238400026</v>
       </c>
       <c r="R8">
-        <v>0.9029007686400002</v>
+        <v>0.90290076864000024</v>
       </c>
       <c r="S8">
-        <v>0.8661229426055789</v>
+        <v>0.86612294260557887</v>
       </c>
       <c r="T8">
-        <v>0.8857993136844803</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>0.88579931368448028</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4547,43 +8695,43 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>170.738516526336</v>
+        <v>170.73851652633601</v>
       </c>
       <c r="J9">
-        <v>256.107774789504</v>
+        <v>256.10777478950399</v>
       </c>
       <c r="K9">
-        <v>256.107774789504</v>
+        <v>256.10777478950399</v>
       </c>
       <c r="L9">
-        <v>371.1497657472</v>
+        <v>371.14976574719998</v>
       </c>
       <c r="M9">
         <v>467.6583291240961</v>
       </c>
       <c r="N9">
-        <v>545.601383978112</v>
+        <v>545.60138397811204</v>
       </c>
       <c r="O9">
-        <v>552.827080096088</v>
+        <v>552.82708009608803</v>
       </c>
       <c r="P9">
-        <v>361.7881458364801</v>
+        <v>361.78814583648011</v>
       </c>
       <c r="Q9">
-        <v>361.7881458364801</v>
+        <v>361.78814583648011</v>
       </c>
       <c r="R9">
-        <v>389.6364086208</v>
+        <v>389.63640862080001</v>
       </c>
       <c r="S9">
-        <v>373.7653621551767</v>
+        <v>373.76536215517672</v>
       </c>
       <c r="T9">
-        <v>382.2564730592256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>382.25647305922558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4609,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1.6434723515904</v>
+        <v>1.6434723515903999</v>
       </c>
       <c r="J10">
         <v>2.465208527385601</v>
@@ -4618,7 +8766,7 @@
         <v>2.465208527385601</v>
       </c>
       <c r="L10">
-        <v>3.57256459008</v>
+        <v>3.5725645900799998</v>
       </c>
       <c r="M10">
         <v>4.501524023654401</v>
@@ -4627,25 +8775,25 @@
         <v>5.251778027596802</v>
       </c>
       <c r="O10">
-        <v>5.321330182743093</v>
+        <v>5.3213301827430932</v>
       </c>
       <c r="P10">
-        <v>3.482452740672001</v>
+        <v>3.4824527406720009</v>
       </c>
       <c r="Q10">
-        <v>3.482452740672001</v>
+        <v>3.4824527406720009</v>
       </c>
       <c r="R10">
-        <v>3.750510885120001</v>
+        <v>3.7505108851200011</v>
       </c>
       <c r="S10">
-        <v>3.597741453900097</v>
+        <v>3.5977414539000971</v>
       </c>
       <c r="T10">
-        <v>3.67947407222784</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>3.6794740722278401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -4692,22 +8840,22 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>6.093603181551852</v>
+        <v>6.0936031815518517</v>
       </c>
       <c r="Q11">
-        <v>6.430143979007999</v>
+        <v>6.4301439790079993</v>
       </c>
       <c r="R11">
-        <v>6.390312611018589</v>
+        <v>6.3903126110185893</v>
       </c>
       <c r="S11">
-        <v>5.673273924096</v>
+        <v>5.6732739240959997</v>
       </c>
       <c r="T11">
-        <v>3.38720102437637</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>3.3872010243763699</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -4754,13 +8902,13 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2629.62414219276</v>
+        <v>2629.6241421927598</v>
       </c>
       <c r="Q12">
-        <v>2774.854440171914</v>
+        <v>2774.8544401719141</v>
       </c>
       <c r="R12">
-        <v>2757.665672908791</v>
+        <v>2757.6656729087908</v>
       </c>
       <c r="S12">
         <v>2448.235901090658</v>
@@ -4769,7 +8917,7 @@
         <v>1461.70751898088</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -4816,22 +8964,22 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>25.31189013875385</v>
+        <v>25.311890138753849</v>
       </c>
       <c r="Q13">
-        <v>26.70982883587939</v>
+        <v>26.709828835879389</v>
       </c>
       <c r="R13">
-        <v>26.54437546115414</v>
+        <v>26.544375461154139</v>
       </c>
       <c r="S13">
-        <v>23.56590706932185</v>
+        <v>23.565907069321849</v>
       </c>
       <c r="T13">
         <v>14.06991194740954</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4866,34 +9014,34 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>2.005606405028571</v>
+        <v>2.0056064050285709</v>
       </c>
       <c r="M14">
-        <v>2.495416016154228</v>
+        <v>2.4954160161542278</v>
       </c>
       <c r="N14">
-        <v>2.316264719808</v>
+        <v>2.3162647198080002</v>
       </c>
       <c r="O14">
-        <v>2.481712199794286</v>
+        <v>2.4817121997942859</v>
       </c>
       <c r="P14">
-        <v>1.955018403668571</v>
+        <v>1.9550184036685709</v>
       </c>
       <c r="Q14">
-        <v>1.955018403668571</v>
+        <v>1.9550184036685709</v>
       </c>
       <c r="R14">
-        <v>1.955018403668571</v>
+        <v>1.9550184036685709</v>
       </c>
       <c r="S14">
-        <v>1.955018403668571</v>
+        <v>1.9550184036685709</v>
       </c>
       <c r="T14">
-        <v>1.993035630225333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>1.9930356302253329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -4928,34 +9076,34 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>865.4963024777144</v>
+        <v>865.49630247771438</v>
       </c>
       <c r="M15">
-        <v>1076.867988509633</v>
+        <v>1076.8679885096331</v>
       </c>
       <c r="N15">
-        <v>999.5573137017602</v>
+        <v>999.55731370176022</v>
       </c>
       <c r="O15">
-        <v>1070.954264680457</v>
+        <v>1070.9542646804571</v>
       </c>
       <c r="P15">
-        <v>843.6656341985145</v>
+        <v>843.66563419851445</v>
       </c>
       <c r="Q15">
-        <v>843.6656341985145</v>
+        <v>843.66563419851445</v>
       </c>
       <c r="R15">
-        <v>843.6656341985145</v>
+        <v>843.66563419851445</v>
       </c>
       <c r="S15">
-        <v>843.6656341985145</v>
+        <v>843.66563419851445</v>
       </c>
       <c r="T15">
-        <v>860.0715296587783</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>860.07152965877833</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -4990,34 +9138,34 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>8.330980451657142</v>
+        <v>8.3309804516571422</v>
       </c>
       <c r="M16">
         <v>10.36557422094833</v>
       </c>
       <c r="N16">
-        <v>9.621407297664</v>
+        <v>9.6214072976639997</v>
       </c>
       <c r="O16">
         <v>10.30865067606857</v>
       </c>
       <c r="P16">
-        <v>8.120845676777144</v>
+        <v>8.1208456767771438</v>
       </c>
       <c r="Q16">
-        <v>8.120845676777144</v>
+        <v>8.1208456767771438</v>
       </c>
       <c r="R16">
         <v>8.120845676777142</v>
       </c>
       <c r="S16">
-        <v>8.120845676777144</v>
+        <v>8.1208456767771438</v>
       </c>
       <c r="T16">
         <v>8.278763387089846</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -5055,19 +9203,19 @@
         <v>3.136578014226493</v>
       </c>
       <c r="M17">
-        <v>3.152709662137139</v>
+        <v>3.1527096621371391</v>
       </c>
       <c r="N17">
-        <v>2.600748917739785</v>
+        <v>2.6007489177397849</v>
       </c>
       <c r="O17">
-        <v>2.600748917739785</v>
+        <v>2.6007489177397849</v>
       </c>
       <c r="P17">
-        <v>2.048791958198805</v>
+        <v>2.0487919581988052</v>
       </c>
       <c r="Q17">
-        <v>2.048791958198806</v>
+        <v>2.0487919581988061</v>
       </c>
       <c r="R17">
         <v>2.020984773324026</v>
@@ -5076,10 +9224,10 @@
         <v>1.941120554701413</v>
       </c>
       <c r="T17">
-        <v>1.682983731383933</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>1.6829837313839331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -5108,16 +9256,16 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>1354.875846075006</v>
+        <v>1354.8758460750059</v>
       </c>
       <c r="K18">
-        <v>1354.875846075006</v>
+        <v>1354.8758460750059</v>
       </c>
       <c r="L18">
         <v>1353.554050754663</v>
       </c>
       <c r="M18">
-        <v>1360.515477276104</v>
+        <v>1360.5154772761041</v>
       </c>
       <c r="N18">
         <v>1122.323186809246</v>
@@ -5126,22 +9274,22 @@
         <v>1122.323186809246</v>
       </c>
       <c r="P18">
-        <v>884.1325296534847</v>
+        <v>884.13252965348465</v>
       </c>
       <c r="Q18">
-        <v>884.1325296534847</v>
+        <v>884.13252965348465</v>
       </c>
       <c r="R18">
-        <v>872.1326598729065</v>
+        <v>872.13265987290652</v>
       </c>
       <c r="S18">
-        <v>837.6681778365328</v>
+        <v>837.66817783653278</v>
       </c>
       <c r="T18">
-        <v>726.2722102356818</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>726.27221023568177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -5173,37 +9321,37 @@
         <v>13.04158568414444</v>
       </c>
       <c r="K19">
-        <v>13.04158568414445</v>
+        <v>13.041585684144451</v>
       </c>
       <c r="L19">
-        <v>13.02886252063312</v>
+        <v>13.028862520633121</v>
       </c>
       <c r="M19">
-        <v>13.09587090426196</v>
+        <v>13.095870904261959</v>
       </c>
       <c r="N19">
-        <v>10.80311088907296</v>
+        <v>10.803110889072959</v>
       </c>
       <c r="O19">
-        <v>10.80311088907296</v>
+        <v>10.803110889072959</v>
       </c>
       <c r="P19">
-        <v>8.510366595595039</v>
+        <v>8.5103665955950394</v>
       </c>
       <c r="Q19">
-        <v>8.510366595595039</v>
+        <v>8.5103665955950394</v>
       </c>
       <c r="R19">
-        <v>8.394859827653645</v>
+        <v>8.3948598276536455</v>
       </c>
       <c r="S19">
-        <v>8.063116150298177</v>
+        <v>8.0631161502981765</v>
       </c>
       <c r="T19">
-        <v>6.990855499594798</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>6.9908554995947982</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -5250,22 +9398,22 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>4.622811471950958</v>
+        <v>4.6228114719509579</v>
       </c>
       <c r="Q20">
-        <v>4.622811471950958</v>
+        <v>4.6228114719509579</v>
       </c>
       <c r="R20">
-        <v>10.37931793118742</v>
+        <v>10.379317931187421</v>
       </c>
       <c r="S20">
-        <v>10.37931793118742</v>
+        <v>10.379317931187421</v>
       </c>
       <c r="T20">
-        <v>8.137633219488496</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>8.1376332194884959</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -5312,22 +9460,22 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1994.920950588067</v>
+        <v>1994.9209505880669</v>
       </c>
       <c r="Q21">
-        <v>1994.920950588067</v>
+        <v>1994.9209505880669</v>
       </c>
       <c r="R21">
-        <v>4479.074891843185</v>
+        <v>4479.0748918431846</v>
       </c>
       <c r="S21">
-        <v>4479.074891843185</v>
+        <v>4479.0748918431846</v>
       </c>
       <c r="T21">
-        <v>3511.701720102344</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>3511.7017201023441</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -5374,22 +9522,22 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>19.20244765271936</v>
+        <v>19.202447652719361</v>
       </c>
       <c r="Q22">
-        <v>19.20244765271936</v>
+        <v>19.202447652719361</v>
       </c>
       <c r="R22">
-        <v>43.11408986800927</v>
+        <v>43.114089868009273</v>
       </c>
       <c r="S22">
-        <v>43.11408986800927</v>
+        <v>43.114089868009273</v>
       </c>
       <c r="T22">
-        <v>33.80247645018298</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>33.802476450182979</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -5439,19 +9587,19 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.912976299380086</v>
+        <v>1.9129762993800861</v>
       </c>
       <c r="R23">
-        <v>5.46740328643444</v>
+        <v>5.4674032864344397</v>
       </c>
       <c r="S23">
         <v>5.249853727165994</v>
       </c>
       <c r="T23">
-        <v>2.700956477441352</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>2.7009564774413519</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -5507,13 +9655,13 @@
         <v>2359.394802838247</v>
       </c>
       <c r="S24">
-        <v>2265.513800723171</v>
+        <v>2265.5138007231708</v>
       </c>
       <c r="T24">
-        <v>1165.566602957383</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>1165.5666029573831</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -5563,19 +9711,19 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>7.946209243578821</v>
+        <v>7.9462092435788207</v>
       </c>
       <c r="R25">
-        <v>22.71075211288152</v>
+        <v>22.710752112881519</v>
       </c>
       <c r="S25">
-        <v>21.80708471284336</v>
+        <v>21.807084712843359</v>
       </c>
       <c r="T25">
-        <v>11.21935767552561</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>11.219357675525609</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -5589,37 +9737,37 @@
         <v>37</v>
       </c>
       <c r="E26">
-        <v>851.9902777777779</v>
+        <v>851.99027777777792</v>
       </c>
       <c r="F26">
-        <v>567.1026944444446</v>
+        <v>567.10269444444464</v>
       </c>
       <c r="G26">
-        <v>295.1187500000001</v>
+        <v>295.11875000000009</v>
       </c>
       <c r="H26">
-        <v>596.5353472222222</v>
+        <v>596.53534722222219</v>
       </c>
       <c r="I26">
-        <v>495.2666666666661</v>
+        <v>495.26666666666608</v>
       </c>
       <c r="J26">
-        <v>386.411180555556</v>
+        <v>386.41118055555597</v>
       </c>
       <c r="K26">
-        <v>400.0977777777776</v>
+        <v>400.09777777777759</v>
       </c>
       <c r="L26">
         <v>44.4283333333332</v>
       </c>
       <c r="M26">
-        <v>72.22638888888876</v>
+        <v>72.226388888888764</v>
       </c>
       <c r="N26">
-        <v>15.11291666666667</v>
+        <v>15.112916666666671</v>
       </c>
       <c r="O26">
-        <v>9.81226851851854</v>
+        <v>9.8122685185185397</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5637,7 +9785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -5651,37 +9799,37 @@
         <v>39</v>
       </c>
       <c r="E27">
-        <v>74945.51000000001</v>
+        <v>74945.510000000009</v>
       </c>
       <c r="F27">
         <v>49885.31180000001</v>
       </c>
       <c r="G27">
-        <v>25960.18500000002</v>
+        <v>25960.185000000019</v>
       </c>
       <c r="H27">
-        <v>52474.36150000001</v>
+        <v>52474.361500000014</v>
       </c>
       <c r="I27">
-        <v>43566.23999999995</v>
+        <v>43566.239999999947</v>
       </c>
       <c r="J27">
-        <v>33990.74350000005</v>
+        <v>33990.743500000048</v>
       </c>
       <c r="K27">
-        <v>35194.68799999999</v>
+        <v>35194.687999999987</v>
       </c>
       <c r="L27">
-        <v>3908.147999999989</v>
+        <v>3908.1479999999892</v>
       </c>
       <c r="M27">
-        <v>6353.409999999991</v>
+        <v>6353.4099999999908</v>
       </c>
       <c r="N27">
         <v>1329.411000000001</v>
       </c>
       <c r="O27">
-        <v>863.1383333333353</v>
+        <v>863.13833333333525</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5699,7 +9847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -5713,34 +9861,34 @@
         <v>38</v>
       </c>
       <c r="E28">
-        <v>1415.044722222222</v>
+        <v>1415.0447222222219</v>
       </c>
       <c r="F28">
-        <v>941.8836055555558</v>
+        <v>941.88360555555585</v>
       </c>
       <c r="G28">
-        <v>490.1537500000003</v>
+        <v>490.15375000000029</v>
       </c>
       <c r="H28">
-        <v>990.767402777778</v>
+        <v>990.76740277777799</v>
       </c>
       <c r="I28">
-        <v>822.5733333333326</v>
+        <v>822.57333333333258</v>
       </c>
       <c r="J28">
-        <v>641.7785694444452</v>
+        <v>641.77856944444522</v>
       </c>
       <c r="K28">
-        <v>664.510222222222</v>
+        <v>664.51022222222196</v>
       </c>
       <c r="L28">
-        <v>73.78966666666645</v>
+        <v>73.789666666666449</v>
       </c>
       <c r="M28">
         <v>119.9586111111109</v>
       </c>
       <c r="N28">
-        <v>25.10058333333335</v>
+        <v>25.100583333333351</v>
       </c>
       <c r="O28">
         <v>16.29689814814818</v>
@@ -5761,7 +9909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -5778,52 +9926,52 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>6.502976190476192</v>
+        <v>6.5029761904761916</v>
       </c>
       <c r="G29">
-        <v>6.502976190476191</v>
+        <v>6.5029761904761907</v>
       </c>
       <c r="H29">
-        <v>13.00595238095237</v>
+        <v>13.005952380952371</v>
       </c>
       <c r="I29">
         <v>13.00595238095238</v>
       </c>
       <c r="J29">
-        <v>19.50892857142857</v>
+        <v>19.508928571428569</v>
       </c>
       <c r="K29">
-        <v>19.50892857142857</v>
+        <v>19.508928571428569</v>
       </c>
       <c r="L29">
-        <v>19.50892857142857</v>
+        <v>19.508928571428569</v>
       </c>
       <c r="M29">
-        <v>19.50892857142857</v>
+        <v>19.508928571428569</v>
       </c>
       <c r="N29">
-        <v>19.50892857142857</v>
+        <v>19.508928571428569</v>
       </c>
       <c r="O29">
-        <v>19.50892857142857</v>
+        <v>19.508928571428569</v>
       </c>
       <c r="P29">
-        <v>5.202380952380952</v>
+        <v>5.2023809523809517</v>
       </c>
       <c r="Q29">
         <v>3.901785714285714</v>
       </c>
       <c r="R29">
-        <v>2.601190476190476</v>
+        <v>2.6011904761904758</v>
       </c>
       <c r="S29">
-        <v>1.300595238095238</v>
+        <v>1.3005952380952379</v>
       </c>
       <c r="T29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -5840,40 +9988,40 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>572.0357142857142</v>
+        <v>572.03571428571422</v>
       </c>
       <c r="G30">
-        <v>572.0357142857143</v>
+        <v>572.03571428571433</v>
       </c>
       <c r="H30">
-        <v>1144.071428571427</v>
+        <v>1144.0714285714271</v>
       </c>
       <c r="I30">
         <v>1144.071428571428</v>
       </c>
       <c r="J30">
-        <v>1716.107142857143</v>
+        <v>1716.1071428571429</v>
       </c>
       <c r="K30">
-        <v>1716.107142857143</v>
+        <v>1716.1071428571429</v>
       </c>
       <c r="L30">
-        <v>1716.107142857143</v>
+        <v>1716.1071428571429</v>
       </c>
       <c r="M30">
-        <v>1716.107142857143</v>
+        <v>1716.1071428571429</v>
       </c>
       <c r="N30">
-        <v>1716.107142857143</v>
+        <v>1716.1071428571429</v>
       </c>
       <c r="O30">
-        <v>1716.107142857143</v>
+        <v>1716.1071428571429</v>
       </c>
       <c r="P30">
-        <v>457.6285714285713</v>
+        <v>457.62857142857132</v>
       </c>
       <c r="Q30">
-        <v>343.2214285714286</v>
+        <v>343.22142857142859</v>
       </c>
       <c r="R30">
         <v>228.8142857142858</v>
@@ -5885,7 +10033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -5902,52 +10050,52 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>10.80059523809524</v>
+        <v>10.800595238095241</v>
       </c>
       <c r="G31">
-        <v>10.80059523809524</v>
+        <v>10.800595238095241</v>
       </c>
       <c r="H31">
         <v>21.60119047619045</v>
       </c>
       <c r="I31">
-        <v>21.60119047619048</v>
+        <v>21.601190476190482</v>
       </c>
       <c r="J31">
-        <v>32.40178571428571</v>
+        <v>32.401785714285708</v>
       </c>
       <c r="K31">
-        <v>32.40178571428571</v>
+        <v>32.401785714285708</v>
       </c>
       <c r="L31">
-        <v>32.40178571428572</v>
+        <v>32.401785714285722</v>
       </c>
       <c r="M31">
-        <v>32.40178571428571</v>
+        <v>32.401785714285708</v>
       </c>
       <c r="N31">
-        <v>32.40178571428572</v>
+        <v>32.401785714285722</v>
       </c>
       <c r="O31">
-        <v>32.40178571428571</v>
+        <v>32.401785714285708</v>
       </c>
       <c r="P31">
-        <v>8.640476190476187</v>
+        <v>8.6404761904761873</v>
       </c>
       <c r="Q31">
-        <v>6.480357142857143</v>
+        <v>6.4803571428571427</v>
       </c>
       <c r="R31">
-        <v>4.320238095238095</v>
+        <v>4.3202380952380954</v>
       </c>
       <c r="S31">
-        <v>2.160119047619048</v>
+        <v>2.1601190476190482</v>
       </c>
       <c r="T31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -5961,55 +10109,55 @@
         <v>37</v>
       </c>
       <c r="E32">
-        <v>80.66533090909091</v>
+        <v>80.665330909090912</v>
       </c>
       <c r="F32">
-        <v>102.7881163636363</v>
+        <v>102.78811636363631</v>
       </c>
       <c r="G32">
-        <v>80.70957818181816</v>
+        <v>80.709578181818159</v>
       </c>
       <c r="H32">
-        <v>62.37844363636363</v>
+        <v>62.378443636363627</v>
       </c>
       <c r="I32">
-        <v>41.7900456796765</v>
+        <v>41.790045679676503</v>
       </c>
       <c r="J32">
-        <v>37.15649620284873</v>
+        <v>37.156496202848729</v>
       </c>
       <c r="K32">
-        <v>43.81485983921243</v>
+        <v>43.814859839212431</v>
       </c>
       <c r="L32">
-        <v>50.29988682170605</v>
+        <v>50.299886821706053</v>
       </c>
       <c r="M32">
-        <v>59.3198932199443</v>
+        <v>59.319893219944298</v>
       </c>
       <c r="N32">
-        <v>34.13043225389828</v>
+        <v>34.130432253898277</v>
       </c>
       <c r="O32">
-        <v>35.67329949541078</v>
+        <v>35.673299495410781</v>
       </c>
       <c r="P32">
-        <v>32.37330007359729</v>
+        <v>32.373300073597292</v>
       </c>
       <c r="Q32">
-        <v>29.35872727272728</v>
+        <v>29.358727272727279</v>
       </c>
       <c r="R32">
-        <v>6.429090909090909</v>
+        <v>6.4290909090909087</v>
       </c>
       <c r="S32">
-        <v>3.214545454545454</v>
+        <v>3.2145454545454539</v>
       </c>
       <c r="T32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -6023,37 +10171,37 @@
         <v>39</v>
       </c>
       <c r="E33">
-        <v>34810.1928</v>
+        <v>34810.192799999997</v>
       </c>
       <c r="F33">
-        <v>44357.02559999999</v>
+        <v>44357.025599999994</v>
       </c>
       <c r="G33">
-        <v>34829.28719999999</v>
+        <v>34829.287199999992</v>
       </c>
       <c r="H33">
         <v>26918.6976</v>
       </c>
       <c r="I33">
-        <v>18034.01202022963</v>
+        <v>18034.012020229631</v>
       </c>
       <c r="J33">
-        <v>16034.45720753703</v>
+        <v>16034.457207537031</v>
       </c>
       <c r="K33">
-        <v>18907.79720753705</v>
+        <v>18907.797207537049</v>
       </c>
       <c r="L33">
-        <v>21706.33577459776</v>
+        <v>21706.335774597759</v>
       </c>
       <c r="M33">
-        <v>25598.81545876058</v>
+        <v>25598.815458760579</v>
       </c>
       <c r="N33">
         <v>14728.59422648995</v>
       </c>
       <c r="O33">
-        <v>15394.40078225034</v>
+        <v>15394.400782250341</v>
       </c>
       <c r="P33">
         <v>13970.32410868314</v>
@@ -6071,7 +10219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -6088,37 +10236,37 @@
         <v>335.0713745454546</v>
       </c>
       <c r="F34">
-        <v>426.9660218181818</v>
+        <v>426.96602181818179</v>
       </c>
       <c r="G34">
-        <v>335.2551709090909</v>
+        <v>335.25517090909091</v>
       </c>
       <c r="H34">
-        <v>259.1104581818182</v>
+        <v>259.11045818181822</v>
       </c>
       <c r="I34">
-        <v>173.5894205155793</v>
+        <v>173.58942051557929</v>
       </c>
       <c r="J34">
-        <v>154.3423688426024</v>
+        <v>154.34236884260241</v>
       </c>
       <c r="K34">
-        <v>182.0001870244209</v>
+        <v>182.00018702442091</v>
       </c>
       <c r="L34">
         <v>208.9379914132405</v>
       </c>
       <c r="M34">
-        <v>246.4057102982302</v>
+        <v>246.40571029823019</v>
       </c>
       <c r="N34">
         <v>141.7725647469621</v>
       </c>
       <c r="O34">
-        <v>148.181397904014</v>
+        <v>148.18139790401401</v>
       </c>
       <c r="P34">
-        <v>134.4737079980195</v>
+        <v>134.47370799801951</v>
       </c>
       <c r="Q34">
         <v>121.9516363636364</v>
@@ -6133,7 +10281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -6183,19 +10331,19 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.516487927205289</v>
+        <v>3.5164879272052891</v>
       </c>
       <c r="R35">
         <v>11.8638783082221</v>
       </c>
       <c r="S35">
-        <v>12.06260184901313</v>
+        <v>12.062601849013131</v>
       </c>
       <c r="T35">
-        <v>4.184252143479826</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <v>4.1842521434798261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -6245,19 +10393,19 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>1517.499790124744</v>
+        <v>1517.4997901247441</v>
       </c>
       <c r="R36">
-        <v>5119.719793009691</v>
+        <v>5119.7197930096909</v>
       </c>
       <c r="S36">
-        <v>5205.47664407413</v>
+        <v>5205.4766440741296</v>
       </c>
       <c r="T36">
-        <v>1805.665732686294</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <v>1805.6657326862939</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -6307,19 +10455,19 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>14.60694985146812</v>
+        <v>14.606949851468119</v>
       </c>
       <c r="R37">
-        <v>49.2807252803072</v>
+        <v>49.280725280307202</v>
       </c>
       <c r="S37">
-        <v>50.10619229590072</v>
+        <v>50.106192295900719</v>
       </c>
       <c r="T37">
-        <v>17.3807396729162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <v>17.380739672916199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -6375,13 +10523,13 @@
         <v>5.468529491654345</v>
       </c>
       <c r="S38">
-        <v>0.7099743134445931</v>
+        <v>0.70997431344459305</v>
       </c>
       <c r="T38">
         <v>23.61615904638872</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -6434,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="R39">
-        <v>2359.880803706222</v>
+        <v>2359.8808037062222</v>
       </c>
       <c r="S39">
         <v>306.3812229557052</v>
@@ -6443,7 +10591,7 @@
         <v>10191.28094232621</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -6502,10 +10650,10 @@
         <v>2.949124071231386</v>
       </c>
       <c r="T40">
-        <v>98.09789142346085</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+        <v>98.097891423460851</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -6561,13 +10709,13 @@
         <v>0</v>
       </c>
       <c r="S41">
-        <v>0.7738095238095238</v>
+        <v>0.77380952380952384</v>
       </c>
       <c r="T41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -6623,13 +10771,13 @@
         <v>0</v>
       </c>
       <c r="S42">
-        <v>333.9285714285714</v>
+        <v>333.92857142857139</v>
       </c>
       <c r="T42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -6691,7 +10839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -6705,10 +10853,10 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>134.92332</v>
+        <v>134.92331999999999</v>
       </c>
       <c r="F44">
-        <v>128.182257</v>
+        <v>128.18225699999999</v>
       </c>
       <c r="G44">
         <v>120.73698</v>
@@ -6717,28 +10865,28 @@
         <v>106.1055855</v>
       </c>
       <c r="I44">
-        <v>97.7949855</v>
+        <v>97.794985499999996</v>
       </c>
       <c r="J44">
         <v>117.1863855</v>
       </c>
       <c r="K44">
-        <v>100.405899</v>
+        <v>100.40589900000001</v>
       </c>
       <c r="L44">
-        <v>74.13055199999999</v>
+        <v>74.130551999999994</v>
       </c>
       <c r="M44">
-        <v>73.34104500000001</v>
+        <v>73.341045000000008</v>
       </c>
       <c r="N44">
-        <v>61.79084999999999</v>
+        <v>61.790849999999992</v>
       </c>
       <c r="O44">
         <v>54.698625</v>
       </c>
       <c r="P44">
-        <v>19.2375</v>
+        <v>19.237500000000001</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -6753,7 +10901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -6767,37 +10915,37 @@
         <v>39</v>
       </c>
       <c r="E45">
-        <v>13250.8026</v>
+        <v>13250.802600000001</v>
       </c>
       <c r="F45">
-        <v>12588.763635</v>
+        <v>12588.763634999999</v>
       </c>
       <c r="G45">
-        <v>11857.5639</v>
+        <v>11857.563899999999</v>
       </c>
       <c r="H45">
-        <v>10420.61645249999</v>
+        <v>10420.616452499989</v>
       </c>
       <c r="I45">
-        <v>9604.433452499998</v>
+        <v>9604.4334524999977</v>
       </c>
       <c r="J45">
-        <v>11508.8604525</v>
+        <v>11508.860452499999</v>
       </c>
       <c r="K45">
-        <v>9860.850944999998</v>
+        <v>9860.8509449999983</v>
       </c>
       <c r="L45">
         <v>7280.352359999999</v>
       </c>
       <c r="M45">
-        <v>7202.814974999999</v>
+        <v>7202.8149749999993</v>
       </c>
       <c r="N45">
-        <v>6068.471749999998</v>
+        <v>6068.4717499999979</v>
       </c>
       <c r="O45">
-        <v>5371.945208333334</v>
+        <v>5371.9452083333344</v>
       </c>
       <c r="P45">
         <v>1889.3125</v>
@@ -6815,7 +10963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -6829,34 +10977,34 @@
         <v>38</v>
       </c>
       <c r="E46">
-        <v>529.6989600000001</v>
+        <v>529.69896000000006</v>
       </c>
       <c r="F46">
-        <v>503.2340459999999</v>
+        <v>503.23404599999992</v>
       </c>
       <c r="G46">
-        <v>474.00444</v>
+        <v>474.00443999999999</v>
       </c>
       <c r="H46">
-        <v>416.5626689999999</v>
+        <v>416.56266899999991</v>
       </c>
       <c r="I46">
-        <v>383.935869</v>
+        <v>383.93586900000003</v>
       </c>
       <c r="J46">
-        <v>460.065069</v>
+        <v>460.06506899999999</v>
       </c>
       <c r="K46">
-        <v>394.186122</v>
+        <v>394.18612200000001</v>
       </c>
       <c r="L46">
-        <v>291.031056</v>
+        <v>291.03105599999998</v>
       </c>
       <c r="M46">
-        <v>287.9315100000001</v>
+        <v>287.93151000000012</v>
       </c>
       <c r="N46">
-        <v>242.5863</v>
+        <v>242.58629999999999</v>
       </c>
       <c r="O46">
         <v>214.74275</v>
@@ -6877,7 +11025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>3</v>
       </c>
@@ -6930,16 +11078,16 @@
         <v>13.57402880549683</v>
       </c>
       <c r="R47">
-        <v>9.049352536997887</v>
+        <v>9.0493525369978869</v>
       </c>
       <c r="S47">
-        <v>4.524676268498942</v>
+        <v>4.5246762684989417</v>
       </c>
       <c r="T47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -6995,13 +11143,13 @@
         <v>888.7357954545455</v>
       </c>
       <c r="S48">
-        <v>444.3678977272725</v>
+        <v>444.36789772727252</v>
       </c>
       <c r="T48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -7051,13 +11199,13 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>53.29063160676534</v>
+        <v>53.290631606765338</v>
       </c>
       <c r="R49">
-        <v>35.52708773784355</v>
+        <v>35.527087737843551</v>
       </c>
       <c r="S49">
-        <v>17.76354386892177</v>
+        <v>17.763543868921769</v>
       </c>
       <c r="T49">
         <v>0</v>
